--- a/assets/runs/auto/articles_report.xlsx
+++ b/assets/runs/auto/articles_report.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Citations" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Curated Articles'!$A$1:$L$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tavily Search Results'!$A$1:$G$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Curated Articles'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tavily Search Results'!$A$1:$G$240</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Citations'!$A$1:$F$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -77,7 +77,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -108,12 +108,6 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -141,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -167,9 +161,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -537,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -554,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 14 April 2026</t>
+          <t>Generated: 15 April 2026</t>
         </is>
       </c>
     </row>
@@ -568,7 +559,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>This intelligence briefing consolidates recent developments across India's AMCA program and defence aerospace ecosystem through early-2026. The AMCA propulsion narrative is advancing with GTRE's EOI process for a 120 kN indigenous engine (AHTCE) to power AMCA Mk-2, signaling a strategic push toward self-reliant, high-thrust powerplants capable of stealth and supercruise. Concurrently, propulsion autonomy is framed within broader industry dynamics, including international collaboration on engine tech (e.g., F404/F414 legacy platforms) and leveraged global partnerships to accelerate indigenous capability. Strategic policy movements, notably Rafale procurements under Make in India and localisation targets, underscore India’s balanced approach to achieving air superiority while expanding domestic manufacturing capacity. MRO and sustainment expansion, as seen in HAL Dhruv coast guard deliveries, reinforce a robust Indian aerospace supply chain. Collectively, these developments reflect a synchronized trajectory: AMCA propulsion maturation, sovereign manufacturing ambitions, and expanded domestic industrial participation aligned with Atmanirbhar Bharat and Defence Exports aspirations.</t>
+          <t>India’s AMCA program is rapidly evolving toward private-sector leadership, with three consortia advancing after initial pre-qualification and HAL reportedly excluded for threshold-based reasons. The RFP-to-prototype pathway remains anchored to a multi-year horizon, with a FY30 flight-test target and an anticipated serial-production phase 8–9 years out. Across AMCA, the government is intensifying Make in India and ToT/technology-sharing dynamics, as demonstrated by consortium structures involving Tata Advanced Systems, Larsen &amp; Toubro, Bharat Electronics, Data Patterns, BEML, Kalyani Group, and Dynamatic Technologies. Separately, strategic procurement continues apace with Rafale and P-8I acquisitions, reflecting a balanced approach to expanding indigenous content while leveraging international partnerships. The HAL position appears under pressure, with private partnerships increasingly shaping future air combat capabilities, and engine supply chain resilience (notably GE Aerospace for Tejas) remains a critical risk factor. Collectively, these developments signal a decisive push toward defence self-reliance, expanded domestic manufacturing, and an increasingly diversified industrial ecosystem to support India’s next-generation fighters and existing platforms.</t>
         </is>
       </c>
     </row>
@@ -585,7 +576,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>This section captures developments directly related to India's Advanced Medium Combat Aircraft (AMCA) program, focusing on propulsion strategy for Mk-2, indigenous engine ambitions, and industry realignments surrounding AMCA manufacturing. Key items include GTRE's EOI submissions for an indigenous 120 kN high-thrust aero engine for AMCA Mk-2 and the broader propulsion self-reliance narrative that underpins AMCA plans.</t>
+          <t>India's Advanced Medium Combat Aircraft (AMCA) procurement is accelerating private-sector participation with shortlisted bidders and evolving evaluation criteria. Three private consortia remain in contention after initial screening, while HAL's bid footprint appears constrained by order-book and capacity considerations. Timelines point to RFP issuance and prototype development aligned with a FY30 flight-test horizon, underscoring a rebalanced domestic industrial base for India's next-generation fighter.</t>
         </is>
       </c>
     </row>
@@ -593,14 +584,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>📑 Engine Procurement &amp; Foreign Collaboration (1 articles)</t>
+          <t>📑 Key Player Updates (HAL, DRDO, L&amp;T, TASL, BEL, Tata, Kalyani, etc.) (1 articles)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>This section covers propulsion strategy, sovereign engine development, and international collaboration dynamics impacting AMCA and India's broader fighter propulsion landscape. It highlights the propulsion self-reliance narrative and the interplay between indigenous engine development and foreign technology transfer.</t>
+          <t>Industry dynamics around AMCA and related platforms show a shifting balance toward private sector leadership in high-end defence programmes. HAL faces scrutiny over capacity and order-book pressures, while consortiums led by L&amp;T-BEL and Tata/TASL with Kalyani Group-linked partners vie for leadership roles. The sector-wide trend signals intensified Make in India and domestic capability ambitions with potential ToT and supply-chain realignments.</t>
         </is>
       </c>
     </row>
@@ -608,70 +599,36 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>📑 Strategic &amp; Policy Developments (Make in India, Exports, Rafale) (2 articles)</t>
+          <t>📑 Strategic Procurement &amp; International Collaboration (1 articles)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>This section captures strategic procurement decisions and policy signals shaping India's defence aerospace landscape, including large-scale Rafale acquisitions, localized production, and Make in India-related imperatives that influence AMCA ecosystem and domestic industry participation.</t>
+          <t>India’s strategic defence procurement continues with high-profile international engagements and sizeable indigenous content ambitions. The Rafale deployment trajectory, alongside defense modernization, underpins the Make in India/self-reliance narrative while informing AMCA’s long-term role within a diversified fighter fleet. The government’s approvals highlight the integration of domestic industry with international partners to maintain deterrence capabilities.</t>
         </is>
       </c>
     </row>
     <row r="20"/>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>📑 Defence Manufacturing, MRO &amp; Supply Chain (1 articles)</t>
-        </is>
-      </c>
-    </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>This section highlights sustainment, MRO, and industrial collaboration developments that strengthen India’s defence aerospace backbone, including Dhruv rotorcraft deliveries to the coast guard and broader MRO ecosystem enhancements.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>📑 Strategic Industry Partnerships &amp; Global Collaboration (1 articles)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>This section captures cross-border collaborations and strategic partnerships that influence India’s defence aerospace ecosystem, including indigenous industry participation and international cooperation that supports domestic capabilities.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Total curated articles: 6</t>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Total curated articles: 3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="9">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A5:B8"/>
     <mergeCell ref="A15:B16"/>
-    <mergeCell ref="A23:B24"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B12"/>
     <mergeCell ref="A19:B20"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A27:B28"/>
-    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -683,7 +640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -773,12 +730,12 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>GTRE Concludes EOI Submissions for Development-cum-Production Partner of Indigenous 120kN High Thrust Aero Engine - Defence.in</t>
+          <t>Three private firms shortlisted for AMCA fighter jet, HAL reportedly excluded</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>https://defence.in/threads/gtre-concludes-eoi-submissions-for-development-cum-production-partner-of-indigenous-120kn-high-thrust-aero-engine.17317/</t>
+          <t>https://www.moneycontrol.com/world/three-private-firms-shortlisted-for-amca-fighter-jet-hal-reportedly-excluded-article-13811145.html</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
@@ -788,58 +745,57 @@
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>Defence.in</t>
+          <t>Moneycontrol</t>
         </is>
       </c>
       <c r="G2" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>Sun, 29 Mar 2026 19:15:00 GMT</t>
-        </is>
-      </c>
+      <c r="H2" s="8" t="n"/>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>GTRE has concluded Expressions of Interest for a development-cum-production partner to build an indigenous 120kN high-thrust aero engine, targeting the AMCA Mk-2. The AMCA Mk-1 fleet is expected to use GE-supplied engines, while the Mk-2 would rely on an indigenous powerplant to enable supercruise and high-maneuverability without sacrificing stealth. This marks a pivotal step in advancing India’s self-reliant propulsion ecosystem for fifth-generation and heavy UAV platforms, building on lessons from the Kaveri program and positioning GTRE within the AMCA propulsion ToT framework.</t>
+          <t>The AMCA program is moving toward formal RFPs after pre-qualification, with three private consortia advancing and HAL reportedly excluded for initial thresholds. The shortlisted groups include Tata Advanced Systems Limited; Larsen &amp; Toubro with Bharat Electronics Limited and Dynamatic Technologies; and Bharat Forge with BEML and Data Patterns. The Defence Secretary emphasized a lowest-cost (L1) evaluation, against a Rs 15,000 crore project for five prototypes and a structural test specimen. The outcome reinforces a private-sector-led AMCA push while flagging capacity/risk absorption considerations given HAL’s order-book dynamics.</t>
         </is>
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>• GTRE concludes EOI submissions for Development-cum-Production Partner of Indigenous 120kN High Thrust Aero Engine
-• 120 kN class turbofan intended for AMCA Mk-2; Mk-1 to utilise existing GE engines
-• AMCA Mk-2 aims to achieve supercruise capabilities and enhanced maneuverability without compromising stealth
-• Indigenous powerplant development linked to AMCA and potential powerplants for future UCAVs</t>
+          <t>• The AMCA programme, India’s most ambitious combat aviation project to date, aims to deliver an indigenous fifth-generation stealth fighter to meet the long-term operational requirements of the Indian Air Force (IAF).
+• The project is being led by the Aeronautical Development Agency under the Defence Research and Development Organisation (DRDO).
+• Defence Secretary Rajesh Kumar confirmed that three bidders remain in contention following the initial technical screening.
+• “We were surprised by the private sector response. We’ve done the initial pre-qualification and there are three remaining. Thereafter, you can expect the RFP to be issued to all three companies for submitting cost bids for production of five prototypes of the AMCA aircraft,” he told CNBC-TV18.
+• The shortlisted bidders are private sector-led consortia, including Tata Advanced Systems Limited; Larsen &amp; Toubro in partnership with Bharat Electronics Limited and Dynamatic Technologies; and Bharat Forge, which has teamed up with BEML and Data Patterns.
+• HAL, which had participated as part of a consortium, failed to clear the mandatory technical and financial thresholds.
+• The project is estimated to be around Rs 15,000 crore to develop five AMCA prototypes and one structural test specimen. Final selection is expected on a lowest-cost (L1) basis after meeting minimum technical requirements.</t>
         </is>
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>GTRE, AMCA Mk-2, AMCA Mk-1, GE</t>
+          <t>DRDO, ADA, Tata Advanced Systems Limited, Larsen &amp; Toubro, Bharat Electronics Limited, Dynamatic Technologies, Bharat Forge, BEML, Data Patterns, HAL</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>AMCA Mk-2, 120kN, AHTCE, indigenous engine, Mk-1, ToT</t>
+          <t>AMCA, prototype, RFP, L1, shortlisted, consortia</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Engine Procurement &amp; Foreign Collaboration</t>
+          <t>Key Player Updates (HAL, DRDO, L&amp;T, TASL, BEL, Tata, Kalyani, etc.)</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>India’s Self-Reliance campaign hinges on aircraft propulsion - Airforce Technology</t>
+          <t>Hindustan Aeronautics Reportedly Knocked Out Of AMCA Production Race - Aviation Week Network</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>https://www.airforce-technology.com/features/indias-self-reliance-campaign-hinges-on-aircraft-propulsion/</t>
+          <t>https://aviationweek.com/defense/aircraft-propulsion/hindustan-aeronautics-reportedly-knocked-out-amca-production-race</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
@@ -849,7 +805,7 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>Airforce Technology</t>
+          <t>Aviation Week Network</t>
         </is>
       </c>
       <c r="G3" s="10" t="n">
@@ -857,45 +813,44 @@
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 13:42:07 GMT</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr">
         <is>
-          <t>India’s propulsion autonomy remains central to the AMCA and broader defence aviation goals. The DRDO currently relies on GE F404/F414 for Tejas, while Safran’s M88 technology is being leveraged to bolster a sovereign 120kN engine. The 120kN unit aims to unlock AMCA Mk-2’s supercruise and stealth requirements, illustrating a concerted push toward indigenisation and ToT within a framework of selective foreign collaboration.</t>
+          <t>Aviation Week reports on HAL being pushed out of the AMCA production race, with private-sector contenders—Tata Advanced Systems, Larsen &amp; Toubro, and Kalyani Group—now in the running. The piece notes ongoing uncertainty and that final selection is expected in the coming months, reflecting a broader shift toward private participation and competition in strategic aerospace manufacturing.</t>
         </is>
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>• DRDO relies on imported GE F404/F414 engines for Tejas; indigenous propulsion challenges persist
-• Safran opened M88 engine MRO capability in Oct 2025; plan to support GTRE in developing a 120kN engine
-• India’s AMCA program hinges on sovereign propulsion; 120kN indigenous powerplant to be built using M88 technologies
-• Aatmanirbhar Bharat/self-reliance drive highlighted; sovereign aircraft propulsion remains a core bottleneck and strategic objective</t>
+          <t>• HAL is neither confirming nor denying reports that it has been pushed out of a race to produce India’s Advanced Medium Combat Aircraft (AMCA).
+• Several Indian news outlets have reported that the state-run aerospace company has been knocked out of the race, leaving private-sector bidders Tata Advanced Systems, Larsen &amp; Toubro and Kalyani Group with consortiums in contention.
+• Final selection is expected in coming months.</t>
         </is>
       </c>
       <c r="K3" s="11" t="inlineStr">
         <is>
-          <t>DRDO, GE, Safran, GTRE, AMCA</t>
+          <t>Hindustan Aeronautics Limited, Tata Advanced Systems, Larsen &amp; Toubro, Kalyani Group, DRDO, AMCA</t>
         </is>
       </c>
       <c r="L3" s="11" t="inlineStr">
         <is>
-          <t>AMCA, 120kN, indigenous engine, ToT, M88</t>
+          <t>AMCA, production race, shortlisted, RFP, consortium</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Strategic &amp; Policy Developments (Make in India, Exports, Rafale)</t>
+          <t>Strategic Procurement &amp; International Collaboration</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>India backs $40 billion military upgrade with more Rafale fighters, Boeing P-8Is - Reuters</t>
+          <t>India backs $40 billion military upgrade with more Rafale fighters, Boeing P-8Is</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
@@ -918,222 +873,36 @@
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 09:01:02 GMT</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>New Delhi approved a 3.6 trillion-rupee package for upgrading armed forces, including additional Rafale fighters and P-8I aircraft, as part of a broader domestic manufacturing push. HAL’s Tejas Mk-1A delivery delays are attributed to engine supply constraints at GE, underscoring the criticality of stable propulsion supply in India’s defence industrialization. The move coincides with a visit by French President Macron and reflects strategic emphasis on domestic co-production and export-readiness in defence aerospace.</t>
+          <t>New Delhi has approved a substantial defence upgrade worth 3.6 trillion rupees, chiefly involving additional Rafale jets and P-8I aircraft, signaling a robust mix of domestic manufacturing and foreign collaboration. HAL continues to face engine-related delivery challenges from GE Aerospace, impacting Tejas Mk1A timelines, while Macron’s upcoming visit underscores the broader strategic dialogue with France on aerospace collaboration.</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>• Defence Acquisition Council gave initial nod for a 3.6 trillion-rupee upgrade package
-• Includes procurement of more Rafale fighter jets and Boeing P-8I Neptune aircraft
-• HAL has nearly 180 of the advanced Mk-1A Tejas variants on order domestically but deliveries delayed due to GE engine supply issues
-• Package aligned with Modi government push for higher domestic manufacturing and Make in India</t>
+          <t>• 3.6-trillion-rupee ($40 billion) boost to the country's armed forces, including procurement of more Rafale fighter jets for the air force and Boeing P-8I reconnaissance aircraft for the navy.
+• The defence ministry said the Defence Acquisition Council had given the initial nod for more Rafale fighter jets and missiles for the air force, anti-tank missiles for the army and P-8I reconnaissance aircraft for its navy.
+• The total value of all these proposals stands at 3.6 trillion rupees.
+• HAL has nearly 180 of the advanced Mk-1A variants of the Tejas on order domestically, but has yet to begin deliveries due to engine supply chain issues at GE Aerospace.
+• The approvals come ahead of a visit by French President Emmanuel Macron to India next week.</t>
         </is>
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>DRDO, GE Aerospace, HAL, Rafale, P-8I, Dassault Aviation</t>
-        </is>
-      </c>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t>Rafale, Make in India, domestic manufacturing, ToT</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Strategic &amp; Policy Developments (Make in India, Exports, Rafale)</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>India approves $39 billion purchase of 114 Rafale jets ahead of Macron visit - AeroTime</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>https://aerotime.aero/articles/india-39-billion-purchase-114-rafale-fighter-jet</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>News</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>AeroTime</t>
-        </is>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>Thu, 12 Feb 2026 13:32:35 GMT</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>AeroTime reports India’s AoN to procure 114 Rafale MRFA jets, with a strong emphasis on local production under Make in India. The piece notes a target of increasing in-country localization to around 50% for future Rafale batches and highlights Dassault’s in-country collaboration with Tata Advanced Systems. This procurement signals continuity in India’s multi-year plan to bolster air superiority while expanding domestic industry participation and export potential in the defence aerospace sector.</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>• AoN approved for 114 Rafale MRFA jets; majority to be manufactured in India under Make in India
-• Rafale backlog and 50% localization target discussed; production ramp-up considerations include in-country value
-• Contextual link to defence diplomacy ahead of Macron visit; Rafale orders interwoven with domestic industrial participation</t>
-        </is>
-      </c>
-      <c r="K5" s="11" t="inlineStr">
-        <is>
-          <t>Dassault Aviation, TATA Advanced Systems, Rafale, India (MoD), France</t>
-        </is>
-      </c>
-      <c r="L5" s="11" t="inlineStr">
-        <is>
-          <t>Rafale, Make in India, local production, in-country localization</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Defence Manufacturing, MRO &amp; Supply Chain</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>HAL delivers four Dhruv Mk IIIs to Indian coast guard - FlightGlobal</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>https://www.flightglobal.com/fixed-wing/hal-delivers-four-dhruv-mk-iiis-to-indian-coast-guard/166532.article</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>News</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>FlightGlobal</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>Thu, 05 Mar 2026 08:06:01 GMT</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>Hindustan Aeronautics Limited has delivered four Dhruv Mk IIIs to the Indian Coast Guard under a contract valued at INR 29 billion. The Dhruv is powered by HAL/Safran Shakti-1H1 turboshafts, derived from the Ardiden family, and the contract’s scale reinforces HAL’s rotorcraft sustainment and coast guard mobility capabilities. This expansion supports India’s domestic rotorcraft production and MRO footprint as part of broader defence manufacturing goals.</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>• HAL delivers four Dhruv Mk IIIs to Indian Coast Guard
-• Contract worth INR 29 billion for six additional helicopters; Dhruv is powered by HAL/Safran Shakti-1H1 turboshafts ( Ardiden 1 lineage)
-• Induction aims to enhance safety and protection of offshore infrastructure and maritime environment</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>HAL, Coast Guard, Safran, Shakti-1H1</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>Dhruv Mk III, coast guard, HAL/Safran, turboshaft</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Strategic Industry Partnerships &amp; Global Collaboration</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Missile &amp; Radar Success Fuels India’s Defense Self-Reliance &amp; Exports; Ex-IAF Air Marshal Shares Key Details - EurAsian Times</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>https://eurasiantimes.com/missile-ex-iaf-air-marshal-shares-key-details/</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>News</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>EurAsian Times</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>Sun, 08 Feb 2026 07:03:48 GMT</t>
-        </is>
-      </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>EurAsian Times highlights India’s push toward defence self-reliance through indigenous propulsion, advanced missile technologies, and multi-layered air defense initiatives. Programs like HSTDV, SFDR, QRSAM, and Project Kusha are framed as foundational to future capabilities and exports, reflecting India’s broader Make in India and self-reliance ethos in strategic aerospace tech.</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>• Indigenous propulsion and missile technologies (HSTDV, SFDR) showcased as pillars of self-reliance
-• QRSAM and Project Kusha positioned to create layered air defense capabilities
-• DRDO-driven programs aiming for 2028-2029 induction timelines and export potential</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="inlineStr">
-        <is>
-          <t>DRDO, HSTDV, SFDR, QRSAM, Project Kusha</t>
-        </is>
-      </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>self-reliance, indigenous, DRDO, Kusha</t>
-        </is>
-      </c>
+          <t>HAL, GE Aerospace, Dassault Aviation, Indian Air Force, Emmanuel Macron</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L7"/>
+  <autoFilter ref="A1:L4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1145,7 +914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G137"/>
+  <dimension ref="A1:G240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1200,30 +969,26 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>GTRE Concludes EOI Submissions for Development-cum-Production Partner of Indigenous 120kN High Thrust Aero Engine - Defence.in</t>
+          <t>Three private firms shortlisted for AMCA fighter jet, HAL reportedly excluded</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>https://defence.in/threads/gtre-concludes-eoi-submissions-for-development-cum-production-partner-of-indigenous-120kn-high-thrust-aero-engine.17317/</t>
+          <t>https://www.moneycontrol.com/world/three-private-firms-shortlisted-for-amca-fighter-jet-hal-reportedly-excluded-article-13811145.html</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>defence.in</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>Sun, 29 Mar 2026 19:15:00 GMT</t>
-        </is>
-      </c>
+          <t>moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr"/>
       <c r="F2" s="8" t="n">
-        <v>0.9925</v>
+        <v>0.8055</v>
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>Historically, the Indian aerospace sector has relied heavily on imported powerplants, such as the American GE F404 and F414 engines used in the Tejas fighter fleet.      While the earlier indigenous Kaveri engine programme provided foundational knowledge, it did not achieve the thrust levels required for modern, heavy combat jets.      The new AHTCE programme seeks to overcome this hurdle by developing a robust 120 kN class turbofan engine.      This high-performance engine is specifically inten...</t>
+          <t>The AMCA programme, India’s most ambitious combat aviation project to date, aims to deliver an indigenous fifth-generation stealth fighter to meet the long-term operational requirements of the Indian Air Force (IAF). The project is being led by the Aeronautical Development Agency under the Defence Research and Development Organisation (DRDO).  Defence Secretary Rajesh Kumar confirmed that three bidders remain in contention following the initial technical screening.  “We were surprised by the pri...</t>
         </is>
       </c>
     </row>
@@ -1233,30 +998,26 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>HAL Shares Crash 8% Amid Speculation of Not Being Shortlisted for Manufacturing Fighter Jets - Trade Brains</t>
+          <t>5th Generation Fighter Aircraft: L&amp;T Expects 5th-Gen Fighter Jet Project Award by 2027, ETInfra</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>https://tradebrains.in/hal-shares-crash-8-amid-speculation-of-not-being-shortlisted-for-manufacturing-fighter-jets/</t>
+          <t>https://infra.economictimes.indiatimes.com/news/aviation/lt-expects-5th-gen-fighter-jet-project-award-by-2027/124954751</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>tradebrains.in</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Wed, 04 Feb 2026 07:43:16 GMT</t>
-        </is>
-      </c>
+          <t>infra.economictimes.indiatimes.com</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr"/>
       <c r="F3" s="11" t="n">
-        <v>0.6584</v>
+        <v>0.6459</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
-          <t>In what is being seen as a landmark shift in India’s defence manufacturing landscape, Tata Advanced Systems, Larsen &amp; Toubro (in partnership with Bharat Electronics Limited), and Bharat Forge (along with BEML and Data Patterns) have reportedly emerged as the leading competitors for the Advanced Medium Combat Aircraft (AMCA) programme.  For decades, HAL has been the backbone of India’s military aircraft production, manufacturing platforms such as the Tejas and executing upgrades of legacy fighter...</t>
+          <t>“Based on the shortlist, we expect the customer to issue the Request for Proposal (RFP) sometime in Q4 (Jan-Mar) of the current financial year (2025-26) and the announcement of the winner to build the prototype most likely is going to happen in Q4 (January-March) of the next financial year (2026-27) after the bidding process,” said Ramakrishnan.       In September, the consortium revealed that it will participate in the Expression of Interest notice issued by Government of India's Aeronautical D...</t>
         </is>
       </c>
     </row>
@@ -1266,30 +1027,26 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>India’s Self-Reliance campaign hinges on aircraft propulsion - Airforce Technology</t>
+          <t>Private Heavyweights Battle for India’s Fifth-Gen Fighter; HAL Eliminated</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>https://www.airforce-technology.com/features/indias-self-reliance-campaign-hinges-on-aircraft-propulsion/</t>
+          <t>https://bharatshakti.in/private-heavyweights-battle-for-indias-fifth-gen-fighter-hal-eliminated/</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>airforce-technology.com</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Wed, 18 Feb 2026 13:42:07 GMT</t>
-        </is>
-      </c>
+          <t>bharatshakti.in</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr"/>
       <c r="F4" s="8" t="n">
-        <v>0.9274</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>The DRDO imports General Electric F404 engines for Tejas Mk1 and 1A aircraft, but sourcing these engines has led to severe delays in the development of the 1A due to global supply chain vulnerabilities. In October 2025, French aerospace company Safran opened another maintenance, repair and overhaul workshop for M88 engines, which India uses to power its Dassault Aviation Rafale fighters.  Likewise, India has its eyes set on a sovereign fifth-generation fighter jet known as the Advanced Medium Co...</t>
+          <t>The aircraft is being designed by the Aeronautical Development Agency under DRDO. It will be a twin-engine stealth fighter. It will feature internal weapons bays, sensor fusion, advanced avionics and manned-unmanned teaming.  In May 2025, the Defence Ministry approved a new execution model. It allowed private and public firms to compete on equal terms. Joint ventures and consortia were permitted.  That decision has now reshaped the outcome.  Tata Advanced Systems has bid on its own. The Kalyani...</t>
         </is>
       </c>
     </row>
@@ -1299,30 +1056,30 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>India backs $40 billion military upgrade with more Rafale fighters, Boeing P-8Is - Reuters</t>
+          <t>GTRE Concludes EOI Submissions for Development-cum-Production Partner of Indigenous 120kN High Thrust Aero Engine - Defence.in</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/india/india-clears-proposal-buy-114-rafale-fighter-jets-dassault-reports-say-2026-02-12/</t>
+          <t>https://defence.in/threads/gtre-concludes-eoi-submissions-for-development-cum-production-partner-of-indigenous-120kn-high-thrust-aero-engine.17317/</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>defence.in</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 09:01:02 GMT</t>
+          <t>Sun, 29 Mar 2026 19:15:00 GMT</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.4906</v>
+        <v>0.4683</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>Sign uphere.  The air force's fighter squadron strength has shrunk to 29 in recent months, well below the 42 it had earlier. Its workhorse MiG-21 was retired in September and other early variants of the MiG-29, the Anglo-French Jaguar and the French Mirage 2000, are also set to end service in the coming years.  New Delhi has long relied on importing machinery and weapons for its armed forces, but a recent push by Prime Minister Narendra Modi has helped boost domestic manufacturing.  For the Indi...</t>
+          <t>Historically, the Indian aerospace sector has relied heavily on imported powerplants, such as the American GE F404 and F414 engines used in the Tejas fighter fleet.      While the earlier indigenous Kaveri engine programme provided foundational knowledge, it did not achieve the thrust levels required for modern, heavy combat jets.      The new AHTCE programme seeks to overcome this hurdle by developing a robust 120 kN class turbofan engine.      This high-performance engine is specifically inten...</t>
         </is>
       </c>
     </row>
@@ -1332,30 +1089,26 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Hindustan Aeronautics Reportedly Knocked Out Of AMCA Production Race - Aviation Week Network</t>
+          <t>India opens bids for 5th gen stealth fighter jet, sets 2029 flight target - The Economic Times</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/defense/aircraft-propulsion/hindustan-aeronautics-reportedly-knocked-out-amca-production-race</t>
+          <t>https://m.economictimes.com/news/defence/india-opens-bids-for-5th-gen-stealth-fighter-jet-sets-2029-flight-target/articleshow/121935094.cms</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>aviationweek.com</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Wed, 04 Feb 2026 14:36:39 GMT</t>
-        </is>
-      </c>
+          <t>m.economictimes.com</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr"/>
       <c r="F6" s="8" t="n">
-        <v>0.6847</v>
+        <v>0.7533</v>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>## Share  Tony Osborne February 04, 2026  Hindustan Aeronautics Limited (HAL) is neither confirming nor denying reports that it has been pushed out of a race to produce India’s Advanced Medium Combat Aircraft (AMCA). Several Indian news outlets have reported that the state-run aerospace company has been knocked out of the race, leaving...  Tony Osborne  Based in London, Tony covers European defense programs. Prior to joining Aviation Week in November 2012, Tony was at Shephard Media Group where...</t>
+          <t>India has launched an open call for domestic defence companies to help build its first home-grown fifth-generation stealth fighter jet, the Advanced Medium Combat Aircraft (AMCA). The Aeronautical Development Agency (ADA) formally uploaded an expression of interest (EOI) on Wednesday to identify firms capable of co-developing and manufacturing the aircraft's prototypes, and assisting in its flight testing and certification.      This move comes at a time when the Indian Air Force (IAF) is facing...</t>
         </is>
       </c>
     </row>
@@ -1365,30 +1118,30 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>HAL In Talks With Indian Air Force Over Tejas Mk.1A Handovers - Aviation Week Network</t>
+          <t>HAL Shares Crash 8% Amid Speculation of Not Being Shortlisted for Manufacturing Fighter Jets - Trade Brains</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/defense/aircraft-propulsion/hal-talks-indian-air-force-over-tejas-mk1a-handovers</t>
+          <t>https://tradebrains.in/hal-shares-crash-8-amid-speculation-of-not-being-shortlisted-for-manufacturing-fighter-jets/</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>aviationweek.com</t>
+          <t>tradebrains.in</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 16:06:44 GMT</t>
+          <t>Wed, 04 Feb 2026 07:43:16 GMT</t>
         </is>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.2668</v>
+        <v>0.6584</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>Already a member of AWIN or subscribe to Aerospace Daily &amp; Defense Report through your company? Loginwith your existing email and password.  Not a member?  Learn how you can access the market intelligence and data you need to stay abreast of what's happening in the aerospace and defense community.  |  |  |  --- | | Login | Learn How |  ## Related Content  Hindustan Aeronautics Reportedly Knocked Out Of AMCA Production Race  Indian Tejas Crashes At Dubai Airshow, Killing Pilot  IAF Chief Upbeat A...</t>
+          <t>In what is being seen as a landmark shift in India’s defence manufacturing landscape, Tata Advanced Systems, Larsen &amp; Toubro (in partnership with Bharat Electronics Limited), and Bharat Forge (along with BEML and Data Patterns) have reportedly emerged as the leading competitors for the Advanced Medium Combat Aircraft (AMCA) programme.  For decades, HAL has been the backbone of India’s military aircraft production, manufacturing platforms such as the Tejas and executing upgrades of legacy fighter...</t>
         </is>
       </c>
     </row>
@@ -1398,30 +1151,30 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Missile &amp; Radar Success Fuels India’s Defense Self-Reliance &amp; Exports; Ex-IAF Air Marshal Shares Key Details - EurAsian Times</t>
+          <t>India’s Self-Reliance campaign hinges on aircraft propulsion - Airforce Technology</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>https://www.eurasiantimes.com/missile-ex-iaf-air-marshal-shares-key-details/</t>
+          <t>https://www.airforce-technology.com/features/indias-self-reliance-campaign-hinges-on-aircraft-propulsion/</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>eurasiantimes.com</t>
+          <t>airforce-technology.com</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 07:03:48 GMT</t>
+          <t>Wed, 18 Feb 2026 13:42:07 GMT</t>
         </is>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.9865</v>
+        <v>0.9274</v>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>The HSTDV has demonstrated Mach 6 speed and can reach altitudes of 30–32 km, crucial for high-speed cruise. The vehicle uses an indigenous air-breathing scramjet engine, which compresses air before combustion, making it more efficient and cost-effective than conventional rockets.  The technology is intended for developing long-range cruise missiles (like Brahmos II) and low-cost, reusable satellite launch vehicles. With its successful test, India became the fourth country (after the USA, Russia,...</t>
+          <t>The DRDO imports General Electric F404 engines for Tejas Mk1 and 1A aircraft, but sourcing these engines has led to severe delays in the development of the 1A due to global supply chain vulnerabilities. In October 2025, French aerospace company Safran opened another maintenance, repair and overhaul workshop for M88 engines, which India uses to power its Dassault Aviation Rafale fighters.  Likewise, India has its eyes set on a sovereign fifth-generation fighter jet known as the Advanced Medium Co...</t>
         </is>
       </c>
     </row>
@@ -1431,30 +1184,30 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>India seeks to join sixth-generation fighter programme - Janes</t>
+          <t>India backs $40 billion military upgrade with more Rafale fighters, Boeing P-8Is - Reuters</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>https://www.janes.com/osint-insights/defence-news/defence/india-seeks-to-join-sixth-generation-fighter-programme</t>
+          <t>https://www.reuters.com/world/india/india-clears-proposal-buy-114-rafale-fighter-jets-dassault-reports-say-2026-02-12/</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>janes.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Fri, 20 Mar 2026 12:06:35 GMT</t>
+          <t>Thu, 12 Feb 2026 09:01:02 GMT</t>
         </is>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.6992</v>
+        <v>0.4906</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>skip to main content  Search Janes  # India seeks to join sixth-generation fighter programme  A full-scale model of India's fifth-generation Advanced Medium Combat Aircraft at Aero India 2025. India seeks to acquire an international sixth-generation fighter in tandem with the domestic AMCA. (Janes/Akhil Kadidal )  The Indian Air Force (IAF) has expressed interest in joining a global sixth-generation fighter aircraft programme, to improve its combat air capabilities.  During a parliamentary sessi...</t>
+          <t>Sign uphere.  The air force's fighter squadron strength has shrunk to 29 in recent months, well below the 42 it had earlier. Its workhorse MiG-21 was retired in September and other early variants of the MiG-29, the Anglo-French Jaguar and the French Mirage 2000, are also set to end service in the coming years.  New Delhi has long relied on importing machinery and weapons for its armed forces, but a recent push by Prime Minister Narendra Modi has helped boost domestic manufacturing.  For the Indi...</t>
         </is>
       </c>
     </row>
@@ -1464,30 +1217,30 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Airbus H125 assembly line opens in India - Janes</t>
+          <t>Hindustan Aeronautics Reportedly Knocked Out Of AMCA Production Race - Aviation Week Network</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>https://www.janes.com/osint-insights/defence-news/defence/airbus-h125-assembly-line-opens-in-india</t>
+          <t>https://aviationweek.com/defense/aircraft-propulsion/hindustan-aeronautics-reportedly-knocked-out-amca-production-race</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>janes.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 10:55:30 GMT</t>
+          <t>Wed, 04 Feb 2026 14:36:39 GMT</t>
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.6847</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Bharat Electronics Limited (BEL) and Safran Electronics &amp; Defense also signed a joint venture (JV)-related memorandum of understanding (MoU) to manufacture the Armement Air‐Sol Modulaire (AASM) Highly Agile Modular Munition Extended Range (Hammer) smart precision-guided air-to-ground weapon.  The two companies first announced a plan to create a JV during Aero India 2025. Janes previously reported that BEL aims to manufacture, customise, and sell the system under the JV.  #### Go beyond the headl...</t>
+          <t>## Share  Tony Osborne February 04, 2026  Hindustan Aeronautics Limited (HAL) is neither confirming nor denying reports that it has been pushed out of a race to produce India’s Advanced Medium Combat Aircraft (AMCA). Several Indian news outlets have reported that the state-run aerospace company has been knocked out of the race, leaving...  Tony Osborne  Based in London, Tony covers European defense programs. Prior to joining Aviation Week in November 2012, Tony was at Shephard Media Group where...</t>
         </is>
       </c>
     </row>
@@ -1497,30 +1250,30 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Embraer seeks expanded Indian supply chain role amid partnerships - FlightGlobal</t>
+          <t>Missile &amp; Radar Success Fuels India’s Defense Self-Reliance &amp; Exports; Ex-IAF Air Marshal Shares Key Details - EurAsian Times</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/aerospace/embraer-seeks-expanded-indian-supply-chain-role-amid-partnerships/166248.article</t>
+          <t>https://www.eurasiantimes.com/missile-ex-iaf-air-marshal-shares-key-details/</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>eurasiantimes.com</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 04:56:46 GMT</t>
+          <t>Sun, 08 Feb 2026 07:03:48 GMT</t>
         </is>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.9865</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>“India is a key partner in shaping the future of aerospace, and we are dedicated to building sustainable cooperation that supports both the domestic industrial base and global initiatives.”  The company has looked at several potential suppliers in the country in areas such as aerostructures, machining, metal forming, composites, wiring, as well as hardware and software development.  Chaves’s remarks follow a late January memorandum of understanding between Embraer and India’s Adani Defense &amp; Aer...</t>
+          <t>The HSTDV has demonstrated Mach 6 speed and can reach altitudes of 30–32 km, crucial for high-speed cruise. The vehicle uses an indigenous air-breathing scramjet engine, which compresses air before combustion, making it more efficient and cost-effective than conventional rockets.  The technology is intended for developing long-range cruise missiles (like Brahmos II) and low-cost, reusable satellite launch vehicles. With its successful test, India became the fourth country (after the USA, Russia,...</t>
         </is>
       </c>
     </row>
@@ -1530,30 +1283,30 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>HAL upbeat on meeting Tejas production targets in 2026 - janes.com</t>
+          <t>HAL In Talks With Indian Air Force Over Tejas Mk.1A Handovers - Aviation Week Network</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>https://www.janes.com/osint-insights/defence-news/defence/hal-upbeat-on-meeting-tejas-production-targets-in-2026</t>
+          <t>https://aviationweek.com/defense/aircraft-propulsion/hal-talks-indian-air-force-over-tejas-mk1a-handovers</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>janes.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 11:52:59 GMT</t>
+          <t>Thu, 05 Feb 2026 16:06:44 GMT</t>
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.1272</v>
+        <v>0.5293</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>skip to main content  Search Janes  # HAL upbeat on meeting Tejas production targets in 2026  By Akhil Kadidal |  The first-production Tejas Mk 1A prepares for take-off from the HAL airport in Bangalore on 28 March 2023. (HAL)  Responding to criticism over the Tejas Mk 1A production rate, Hindustan Aeronautics Limited (HAL) has said it expects to complete 16 aircraft by the end of India's fiscal year (FY) 2025 in March 2026.  On 5 February, the state-owned aircraft manufacturer said in a post on...</t>
+          <t>## Share  Robert Wall February 05, 2026  Hindustan Aeronautics Ltd. (HAL) says it is in “active discussions” with the Indian Air Force to start delivering the delayed Tejas Mk.1A light combat aircraft. Five aircraft that meet the agreed specifications are ready for delivery, the company said in a Feb. 5 statement, adding that a further...  Robert Wall  Robert Wall is Executive Editor for Defense and Space. Based in London, he directs a team of military and space journalists across the U.S., Euro...</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1316,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Portugal picks Tecnam P-Mentor as air force elementary trainer - FlightGlobal</t>
+          <t>Indian RFP for 126 fighters approved for release - FlightGlobal</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/fixed-wing/2026/04/portugal-picks-tecnam-p-mentor-as-air-force-elementary-trainer/</t>
+          <t>https://www.flightglobal.com/fixed-wing/2007/06/indian-rfp-for-126-fighters-approved-for-release/</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1576,17 +1329,13 @@
           <t>flightglobal.com</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>Mon, 13 Apr 2026 09:35:38 GMT</t>
-        </is>
-      </c>
+      <c r="E13" s="11" t="inlineStr"/>
       <c r="F13" s="11" t="n">
-        <v>0.7994</v>
+        <v>0.8269</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>#### Author: Dominic Perry  Dominic Perry is Aerospace Editor, Europe contributing extensively to flightglobal.com. Although specialising in the coverage of the helicopter industry, he has written on most topics in aerospace – be they commercial, defence or business aviation. In addition, there has been an increasing focus on the decarbonisation of the industry and zero-emission flight initiatives. He also helps to edit Flight International.  E-mail  ### Related posts  FIXED-WING India to get de...</t>
+          <t>India plans to buy 18 aircraft in fly-away condition and manufacture the remaining 108 under license at Hindustan Aeronautics. The contract is expected to include options for additional aircraft.  The Boeing F/A-18E/F, Dassault Rafale, Eurofighter Typhoon, Lockheed Martin F-16, RSK MiG-35 and Saab Gripen are the likely contenders for the competition to replace the Indian air force’s HAL-built MiG-21s.  Local report says the government will require 50% of the contract value to be placed with Indi...</t>
         </is>
       </c>
     </row>
@@ -1596,30 +1345,30 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Global Combat Air Programme Awards First Contract with Edgewing - The Aviationist</t>
+          <t>India seeks to join sixth-generation fighter programme - Janes</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>https://theaviationist.com/2026/04/02/gcap-awards-first-contract-edgewing/</t>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/india-seeks-to-join-sixth-generation-fighter-programme</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>theaviationist.com</t>
+          <t>janes.com</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 16:40:00 GMT</t>
+          <t>Fri, 20 Mar 2026 12:06:35 GMT</t>
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.6092</v>
+        <v>0.6992</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>India has also expressed an interest in joining GCAP as a development partner, owing to its current lack of a 5th generation fighter capability, and increasing tensions with Pakistan. However, it is unlikely to be able to join in this capacity owing to Japan’s insistence that no more partners are added to the development of the aircraft, in case it leads to delays in the platform entering service.  India’s current program the Advanced Medium Combat Aircraft (AMCA) looks unlikely to meet its curr...</t>
+          <t>skip to main content  Search Janes  # India seeks to join sixth-generation fighter programme  A full-scale model of India's fifth-generation Advanced Medium Combat Aircraft at Aero India 2025. India seeks to acquire an international sixth-generation fighter in tandem with the domestic AMCA. (Janes/Akhil Kadidal )  The Indian Air Force (IAF) has expressed interest in joining a global sixth-generation fighter aircraft programme, to improve its combat air capabilities.  During a parliamentary sessi...</t>
         </is>
       </c>
     </row>
@@ -1629,30 +1378,30 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Airbus Helicopters and GE to continue joint research on next-generation rotorcraft engines - FlightGlobal</t>
+          <t>Airbus H125 assembly line opens in India - Janes</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/helicopters/airbus-helicopters-and-ge-to-continue-joint-research-on-next-generation-rotorcraft-engines/166644.article</t>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/airbus-h125-assembly-line-opens-in-india</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>janes.com</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 00:00:00 GMT</t>
+          <t>Wed, 18 Feb 2026 10:55:30 GMT</t>
         </is>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.0136</v>
+        <v>0.6552</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>weekly  ## Sign-up to the Aerospace Briefing  Keep track of news and trends in the aerospace supply chain and aviation aftermarket, with a focus on interiors, MRO and the emerging role of big data. Sent every Thursday.  Privacy Notice: By signing up to the newsletter you consent to our Terms and Conditions and our  Privacy Policy . This site is protected by reCAPTCHA and the Google Privacy Policy and Terms of Service apply.  ## Topics   Helicopters   Save article    Please Sign in to your accoun...</t>
+          <t>skip to main content  Search Janes  # Airbus H125 assembly line opens in India  By Akhil Kadidal |  A new Airbus final assembly line set up in India could also produce the H125M military helicopter. (Airbus)  With the launch of a new rotary-wing final assembly line (FAL) in the Indian state of Karnataka, Airbus Helicopters and Tata Advanced Systems Limited (TASL) are positioning the H125 single-engine light utility helicopter (LUH) as a high-altitude-capable combat platform for the Indian Armed...</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1411,12 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>HAL delivers four Dhruv Mk IIIs to Indian coast guard - FlightGlobal</t>
+          <t>Leonardo targets Indian helicopter production through Adani pact - FlightGlobal</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/archive/2026/04/hal-delivers-four-dhruv-mk-iiis-to-indian-coast-guard/</t>
+          <t>https://www.flightglobal.com/helicopters/leonardo-targets-indian-helicopter-production-through-adani-pact/166197.article</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -1677,15 +1426,15 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Mon, 13 Apr 2026 02:38:28 GMT</t>
+          <t>Wed, 04 Feb 2026 02:55:43 GMT</t>
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.1019</v>
+        <v>0.9438</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>The fiscal year 2027 budget request from the White House affirms the Trump Administration’s commitment to fielding the US Air Force sixth-generation fighter, with Boeing to fly a prototype in 2028. [...] #### Author: Greg Waldron  Greg Waldron is the Defence Managing Editor at FlightGlobal, leading the publication’s global defence coverage. Based in the Asia-Pacific, he has reported extensively on the rise of Chinese airpower and broader airpower developments across the region and worldwide. Sin...</t>
+          <t>“With the Indian armed forces projecting demand for over 1000 helicopters in the coming decade, this partnership realizes our vision for sovereign manufacturing,”says Ashish Rajvanshi, chief executive, Adani Defence &amp; Aerospace.  The MoU, if finalised, will mark a further significant thawing of relations between Leonardo and India, a market in which it has struggled since a corruption scandal erupted in 2013 related to the sale of VVIP-roled AW101s to the Indian air force.  As a result of the af...</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1444,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Embraer and Adani aim to seek orders which would justify Indian E175 final assembly line - FlightGlobal</t>
+          <t>Fraudulent UK spares firm generated nearly £7m from unapproved CFM56 parts - FlightGlobal</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/aerospace/embraer-and-adani-aim-to-seek-orders-which-would-justify-indian-e175-final-assembly-line/166393.article</t>
+          <t>https://www.flightglobal.com/aerospace/fraudulent-uk-spares-firm-generated-nearly-7m-from-unapproved-cfm56-parts/166418.article</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1710,15 +1459,15 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Sun, 22 Feb 2026 11:00:48 GMT</t>
+          <t>Tue, 24 Feb 2026 09:49:15 GMT</t>
         </is>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.0315</v>
+        <v>0.0106</v>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>2026-02-21T21:04:00Z By Jon Hemmerdinger    Aircraft, engines and components will be excluded from the Trump administration’s revised 15% tariff regime, imposed after the US Supreme Court struck down the president’s earlier duties on 20 February.  In depth    ### Why the Supreme Court’s tariff ruling creates fresh tariff uncertainty for aerospace    2026-02-21T01:34:00Z By Jon Hemmerdinger    The US Supreme Court’s decision to strike down President Donald Trump’s tariffs under emergency powers,...</t>
+          <t>2026-02-22T10:56:00Z By David Kaminski-Morrow    Embraer has reached a provisional agreement with Indian firm Adani Defence &amp; Aerospace covering the possible establishment of an E175 regional jet final assembly line in the country. The memorandum of understanding was exchanged between the two companies’ leaders in the presence of Brazilian president Luiz Inacio Lula da Silva ...  News    ### Aerospace products appear exempt from Trump’s new 15% tariffs    2026-02-21T21:04:00Z By Jon Hemmerdinger...</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1477,12 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Adani Group Combines Air Works, Indamer For Major MRO Expansion - Aviation Week Network</t>
+          <t>GE, HAL Take Step Toward Finalizing F414 Assembly In India - Aviation Week</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/mro/aircraft-propulsion/adani-group-combines-air-works-indamer-major-mro-expansion</t>
+          <t>https://aviationweek.com/defense/aircraft-propulsion/ge-hal-take-step-toward-finalizing-f414-assembly-india</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -1743,15 +1492,15 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 16:01:53 GMT</t>
+          <t>Tue, 14 Apr 2026 22:02:04 GMT</t>
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.5909</v>
+        <v>0.754</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>That acquisition was followed by the purchase of Indamer Technics through Adani Defense Systems and Technologies Ltd (ADSTL), further strengthening the group’s capabilities in commercial and defense aircraft maintenance. ADSTL, in partnership with Prime Aero Services LLP, acquired a 100% stake in Indamer Technics, creating the foundation for a consolidated MRO platform.      The group is also planning to expand its MRO capabilities beyond airframe maintenance into landing gear overhaul, aircraft...</t>
+          <t>## Share  Steve Trimble April 14, 2026  GE Aerospace and Hindustan Aeronautics Ltd. (HAL) say the companies have made progress in nearly three-year-old talks over establishing F414 engine manufacturing in India. The two companies have agreed on “technical matters” associated with the deal. “This agreement marks a significant step forward...  Steve Trimble  Steve covers military aviation, missiles and space for the Aviation Week Network, based in Washington, DC.  ## Subscription Required  GE, HAL...</t>
         </is>
       </c>
     </row>
@@ -1761,30 +1510,30 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>HAL secures contract for six Dhruv coast guard helicopters - FlightGlobal</t>
+          <t>HAL upbeat on meeting Tejas production targets in 2026 - janes.com</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/helicopters/hal-secures-contract-for-six-dhruv-coast-guard-helicopters/166532.article</t>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/hal-upbeat-on-meeting-tejas-production-targets-in-2026</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>janes.com</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 08:06:01 GMT</t>
+          <t>Tue, 10 Feb 2026 11:52:59 GMT</t>
         </is>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.1148</v>
+        <v>0.1272</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>Source: Indian Ministry of Defence  The coast guard order is an important vote of confidence in the Dhruv following a difficult 2025  The contract also includes performance-based logistics support.  The Dhruv is powered by a pair of HAL/Safran Shakti-1H1 turboshafts, a co-developed engine based on the Ardiden 1 turboshaft family.  “The induction will significantly enhance the Indian Coast Guard’s capability for fulfilling the duties of safety and protection of artificial islands, offshore instal...</t>
+          <t>skip to main content  Search Janes  # HAL upbeat on meeting Tejas production targets in 2026  By Akhil Kadidal |  The first-production Tejas Mk 1A prepares for take-off from the HAL airport in Bangalore on 28 March 2023. (HAL)  Responding to criticism over the Tejas Mk 1A production rate, Hindustan Aeronautics Limited (HAL) has said it expects to complete 16 aircraft by the end of India's fiscal year (FY) 2025 in March 2026.  On 5 February, the state-owned aircraft manufacturer said in a post on...</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1543,12 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Embraer, Mahindra plan India MRO for C-390 bid - FlightGlobal</t>
+          <t>Portugal picks Tecnam P-Mentor as air force elementary trainer - FlightGlobal</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/fixed-wing/embraer-mahindra-plan-india-mro-for-c-390-bid/166387.article</t>
+          <t>https://www.flightglobal.com/fixed-wing/2026/04/portugal-picks-tecnam-p-mentor-as-air-force-elementary-trainer/</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -1809,15 +1558,15 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Fri, 20 Feb 2026 08:26:15 GMT</t>
+          <t>Mon, 13 Apr 2026 09:35:38 GMT</t>
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.0363</v>
+        <v>0.7994</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Moreover, the Indian air force already operates 12 C-130J-30s in a variant optimised to support special forces.  Airbus, for its part, produces the C295 locally with Tata. Recently, Airbus and Tata opened a local assembly line for the H125 light single helicopter, the first private sector helicopter production line in the country.  Separately, Embraer also signed a memorandum of understanding with Indian resources company Hindalco, the country’s biggest aluminium producer.  The MOU will see the...</t>
+          <t>#### Author: Dominic Perry  Dominic Perry is Aerospace Editor, Europe contributing extensively to flightglobal.com. Although specialising in the coverage of the helicopter industry, he has written on most topics in aerospace – be they commercial, defence or business aviation. In addition, there has been an increasing focus on the decarbonisation of the industry and zero-emission flight initiatives. He also helps to edit Flight International.  E-mail  ### Related posts  FIXED-WING India to get de...</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1576,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>South Korea launches EW aircraft programme - FlightGlobal</t>
+          <t>Airbus Helicopters and GE to continue joint research on next-generation rotorcraft engines - FlightGlobal</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/fixed-wing/south-korea-launches-ew-aircraft-programme/166011.article</t>
+          <t>https://www.flightglobal.com/helicopters/airbus-helicopters-and-ge-to-continue-joint-research-on-next-generation-rotorcraft-engines/166644.article</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1842,15 +1591,15 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Wed, 21 Jan 2026 06:10:39 GMT</t>
+          <t>Thu, 12 Mar 2026 00:00:00 GMT</t>
         </is>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.0244</v>
+        <v>0.0136</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>2026-01-21T05:10:00Z By Greg Waldron    The US Defense Security Cooperation Agency has approved the potential sale of four Boeing P-8A Poseidon maritime patrol aircraft to Singapore, along with torpedoes, systems and support equipment, marking a significant enhancement of the city-state’s maritime surveillance capabilities.  News    ### NORAD deploys aircraft to Greenland amid international standoff    2026-01-21T02:16:00Z By Ryan Finnerty    North American Aerospace Defense Command is deploying...</t>
+          <t>weekly  ## Sign-up to the Aerospace Briefing  Keep track of news and trends in the aerospace supply chain and aviation aftermarket, with a focus on interiors, MRO and the emerging role of big data. Sent every Thursday.  Privacy Notice: By signing up to the newsletter you consent to our Terms and Conditions and our  Privacy Policy . This site is protected by reCAPTCHA and the Google Privacy Policy and Terms of Service apply.  ## Topics   Helicopters   Save article    Please Sign in to your accoun...</t>
         </is>
       </c>
     </row>
@@ -1860,30 +1609,30 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Adani partners with Leonardo to build helicopters in India - Janes</t>
+          <t>HAL's ₹2.4 trn order book to propel manufacturing revenue, says analysts - Business Standard</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>https://www.janes.com/osint-insights/defence-news/defence/adani-partners-with-leonardo-to-build-helicopters-in-india</t>
+          <t>https://www.business-standard.com/markets/news/hal-hindustan-aeronautics-share-price-target-nse-bse-q3-results-profit-revenue-126021300462_1.html</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>janes.com</t>
+          <t>business-standard.com</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 00:00:00 GMT</t>
+          <t>Fri, 13 Feb 2026 04:24:55 GMT</t>
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0.9353</v>
+        <v>0.79</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>“[The AW169M] is designed with dual-use technology in mind, which brings added high certification and safety standards combined with military-qualified configuration and mission capabilities,” Leonardo said.  The AW109 TrekkerM, however, with its “rugged airframe and skids”, allows to meet military requirements in the light aircraft segment, including for operations on unprepared terrains, Leonardo added.  Adani Defence and Aerospace CEO Ashish Rajvanshi said the collaboration supports domestic...</t>
+          <t>Motilal Oswal said HAL's Q3FY26 results came in line with its estimates. The brokerage highlighted that HAL’s massive ₹2.3 trillion order book is set to propel manufacturing revenue, with the company already prepared to deliver five Tejas Mk1A aircraft this year following the receipt of engines from GE.  While Motilal cut its FY26–28 earnings estimates by 4–5 per cent to account for a more conservative delivery schedule for the Tejas Mk1A, it noted that further scaling of deliveries remains cont...</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1642,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Safran and H55 power up electrification pact with B23 agreement - FlightGlobal</t>
+          <t>UK government continues talks with Leonardo over NMH as it pledges it will not allow AW149 offer to ‘time out’ - FlightGlobal</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/archive/2026/04/safran-and-h55-power-up-electrification-pact-with-b23-agreement/</t>
+          <t>https://www.flightglobal.com/helicopters/uk-government-continues-talks-with-leonardo-over-nmh-as-it-pledges-it-will-not-allow-aw149-offer-to-time-out/166290.article</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -1908,15 +1657,15 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Mon, 13 Apr 2026 10:42:08 GMT</t>
+          <t>Wed, 11 Feb 2026 17:28:22 GMT</t>
         </is>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.2003</v>
+        <v>0.7607</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>It foresees the development of “certified electric propulsion solutions for general aviation”, targeting CS-23-category aircraft.  Safran Electrical &amp; Power in 2025 received European Union Aviation Safety Agency approval for its ENGINeUS 100 electric propulsion unit (EPU), while H55 earlier this year revealed an agreement with the regulator over the certification readiness of its energy storage system.  “ENGINeUS enables the development of both all-electric and hybrid aircraft, making it a key a...</t>
+          <t>## Topics   Defence  Helicopters  ### Related articles   News    ### Lockheed Martin picks Robinson R66 for Flight School Next bid    2026-02-09T11:23:00Z By Dominic Perry    Lockheed Martin has selected the Robinson Helicopter R66 NxG as its platform offer for the US Army’s Flight School Next training competition.  News    ### Embraer seeks expanded Indian supply chain role amid partnerships    2026-02-09T04:52:00Z By Greg Waldron    Embraer is pursuing an expanded role for India in its global...</t>
         </is>
       </c>
     </row>
@@ -1926,30 +1675,30 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>India OKs Plans To Buy Airlifters, S-400s, UAS - Aviation Week</t>
+          <t>UK signs ECRS Mk2 radar production deal for Royal Air Force's Tranche 3 Typhoon upgrade - FlightGlobal</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/defense/aircraft-propulsion/india-oks-plans-buy-airlifters-s-400s-uas</t>
+          <t>https://www.flightglobal.com/defence/uk-signs-ecrs-mk2-radar-production-deal-for-royal-air-forces-tranche-3-typhoon-upgrade/166031.article</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>aviationweek.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Fri, 27 Mar 2026 18:34:17 GMT</t>
+          <t>Thu, 22 Jan 2026 10:55:35 GMT</t>
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.2561</v>
+        <v>0.0973</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>Already a member of AWIN or subscribe to Aerospace Daily &amp; Defense Report through your company? Loginwith your existing email and password.  Not a member?  Learn how you can access the market intelligence and data you need to stay abreast of what's happening in the aerospace and defense community.  |  |  |  --- | | Login | Learn How |  ## Related Content  Nigeria Seeking Airbus C295 Procurement  India Seeks Role In FCAS Or GCAP Fighter Consortia  Dassault Gears Up For Rafale Output Uptick, India...</t>
+          <t>2026-01-21T18:49:00Z By Dominic Perry    At some point in the next 12 months, a freshly-painted A380 will arrive in Toulouse ready for Airbus to begin a series of modifications that will eventually leave it looking like no other superjumbo in existence as it is transformed into a flying testbed for new engines and other advanced technologies.  News    ### Lockheed adds two international C-130J operators to start 2026    2026-01-21T16:43:00Z By Ryan Finnerty    Mexico has become the first Latin A...</t>
         </is>
       </c>
     </row>
@@ -1959,30 +1708,30 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>The SM-39 Razor Is the Mach 4 6th Generation NGAD 'Rocket' Fighter (The Air Force Doesn't Have It) - 19FortyFive</t>
+          <t>Adani Group Combines Air Works, Indamer For Major MRO Expansion - Aviation Week Network</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>https://www.19fortyfive.com/2026/02/the-sm-39-razor-is-the-mach-4-6th-generation-ngad-rocket-fighter-the-air-force-doesnt-have-it/</t>
+          <t>https://aviationweek.com/mro/aircraft-propulsion/adani-group-combines-air-works-indamer-major-mro-expansion</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>19fortyfive.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Sun, 01 Feb 2026 13:12:59 GMT</t>
+          <t>Tue, 20 Jan 2026 16:01:53 GMT</t>
         </is>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.0237</v>
+        <v>0.5909</v>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>-The concept highlights variable-cycle engines, advanced materials (including a titanium diboride cermet structure), and multiple configurations—single-seat, two-seat, and an uncrewed variant with “synthetic intelligence.”  -While internal bays and shaping nod toward stealth, the design also leans on speed as a survivability tool, raising questions about signature growth, external stores, and how realistically cockpit control of unmanned teammates could work in practice.  ## Mach 4? Stavatti Aer...</t>
+          <t>That acquisition was followed by the purchase of Indamer Technics through Adani Defense Systems and Technologies Ltd (ADSTL), further strengthening the group’s capabilities in commercial and defense aircraft maintenance. ADSTL, in partnership with Prime Aero Services LLP, acquired a 100% stake in Indamer Technics, creating the foundation for a consolidated MRO platform.      The group is also planning to expand its MRO capabilities beyond airframe maintenance into landing gear overhaul, aircraft...</t>
         </is>
       </c>
     </row>
@@ -1992,12 +1741,12 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Bird Aerosystems wins Asia-Pacific helicopter self-defence contract - FlightGlobal</t>
+          <t>HAL delivers four Dhruv Mk IIIs to Indian coast guard - FlightGlobal</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/helicopters/bird-aerosystems-wins-asia-pacific-helicopter-self-defence-contract/166171.article</t>
+          <t>https://www.flightglobal.com/archive/2026/04/hal-delivers-four-dhruv-mk-iiis-to-indian-coast-guard/</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -2007,15 +1756,15 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 02:22:39 GMT</t>
+          <t>Mon, 13 Apr 2026 02:38:28 GMT</t>
         </is>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.8129</v>
+        <v>0.2553</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>India is known to be upgrading its air force’s Mi-17s. In April 2025 it signed a INR22 billion ($265 million) contract with Bharat Electronics for helicopter self-protection systems including a new radar warning receiver, missile approach warning system, and countermeasure dispensing system.  Moreover, the Indian government demands significant technology transfer for major international defence acquisitions.  ## Topics   Asia Pacific  Helicopters  Singapore Airshow  ### Related articles   News...</t>
+          <t>Menu  search  Trending now:  ROTORCRAFT  # HAL delivers four Dhruv Mk IIIs to Indian coast guard  By Greg Waldron |  Hindustan Aeronautics (HAL) has handed over four Dhruv Advanced Light Helicopter Mk IIIs to the Indian coast guard.  This brings the coast guard’s fleet to 16 examples since the beginning of deliveries in 2022, says HAL.  The handover follows the coast guard’s follow-on order for six additional Dhruvs signed in March.  The Dhruv is powered by a pair of HAL/Safran Shakti-1H1 turbos...</t>
         </is>
       </c>
     </row>
@@ -2025,30 +1774,30 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>India clears the way for landmark deal to acquire French Rafale jets - Defense News</t>
+          <t>Modified LMS-901 Baikal prototype carries out maiden flight - FlightGlobal</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>https://www.defensenews.com/global/asia-pacific/2026/02/13/india-clears-the-way-for-landmark-deal-to-acquire-french-rafale-jets/</t>
+          <t>https://www.flightglobal.com/aerospace/modified-lms-901-baikal-prototype-carries-out-maiden-flight/166414.article</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>defensenews.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 12:01:00 GMT</t>
+          <t>Tue, 24 Feb 2026 07:53:47 GMT</t>
         </is>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.532</v>
+        <v>0.0534</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>Featured:  Coverage: Singapore Airshow  Coverage: Venezuela  Whitepaper: Modular Open Systems  #### Asia Pacific  # India clears the way for landmark deal to acquire French Rafale jets  By Anjana Pasricha  French Air and Space Force Rafale fighter jets taxi toward the runway at Air Base 120 in Cazaux, south-western France, on Jan. 29, 2026, during the Topaze 2026 exercise. (Philippe Lopez / AFP via Getty Images)  NEW DELHI — India has cleared a proposal to buy 114 Rafale multirole fighter jets f...</t>
+          <t>2026-02-22T10:56:00Z By David Kaminski-Morrow    Embraer has reached a provisional agreement with Indian firm Adani Defence &amp; Aerospace covering the possible establishment of an E175 regional jet final assembly line in the country. The memorandum of understanding was exchanged between the two companies’ leaders in the presence of Brazilian president Luiz Inacio Lula da Silva ...  News    ### Aerospace products appear exempt from Trump’s new 15% tariffs    2026-02-21T21:04:00Z By Jon Hemmerdinger...</t>
         </is>
       </c>
     </row>
@@ -2058,12 +1807,12 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>India to get depot for F404-IN20 engine - FlightGlobal</t>
+          <t>DARPA designates General Atomics LongShot prototype as X-68A - FlightGlobal</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/fixed-wing/2026/04/india-to-get-depot-for-f404-in20-engine/</t>
+          <t>https://www.flightglobal.com/military-uavs/darpa-designates-general-atomics-longshot-prototype-as-x-68a/166348.article</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -2073,15 +1822,15 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Mon, 13 Apr 2026 07:17:35 GMT</t>
+          <t>Wed, 18 Feb 2026 01:21:17 GMT</t>
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>0.4278</v>
+        <v>0.0372</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>In early February, HAL issued a statement stating that five LCA Mk1A variants were ready for delivery. It added that nine additional jets had been “built and flown”, and that these would be readied for delivery pending receipt of engines from GE Aerospace.  At the time HAL indicated that the “supply position from GE is positive, and the future delivery outlook aligns with HAL’s delivery plans.”  At the Paris air show in June 2025, Sunil told FlightGlobal that HAL expected to get 12 F404s by the...</t>
+          <t>### USMC selects GA-ASI YFQ-42A for MUX TACAIR assessment work    2026-02-11T05:26:00Z By Greg Waldron    The US Marine Corps will use the General Atomics Aeronautical Systems (GA-ASI) YFQ-42A uncrewed aircraft to help with the development of future air operations.   Contact us  About us  Advertise with us  Jobs  Conferences and Events  Newsletters  Paid content  Reports  FlightGlobal is the global aviation community’s primary source of news, data, insight, knowledge and expertise. We provide ne...</t>
         </is>
       </c>
     </row>
@@ -2091,12 +1840,12 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>US Navy launches competition to replace T-45 trainer - FlightGlobal</t>
+          <t>Embraer, Mahindra plan India MRO for C-390 bid - FlightGlobal</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/archive/2026/03/us-navy-launches-competition-to-replace-t-45-trainer/</t>
+          <t>https://www.flightglobal.com/fixed-wing/embraer-mahindra-plan-india-mro-for-c-390-bid/166387.article</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -2106,15 +1855,15 @@
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Tue, 31 Mar 2026 01:31:52 GMT</t>
+          <t>Fri, 20 Feb 2026 08:26:15 GMT</t>
         </is>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.1289</v>
+        <v>0.0363</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>Menu  search  Trending now:  Fixed-Wing  # US Navy launches competition to replace T-45 trainer  By Ryan Finnerty |  The milestone comes six years after the navy first began asking for industry input on a possible successor to the aged and maintenance-challenged T-45 Goshawk.  The US Navy has officially launched a competition to select its next fighter trainer after years of delays.  An Request for Proposal (RFP) for the Undergraduate Jet Training System (UJTS) posted to the US government contra...</t>
+          <t>Moreover, the Indian air force already operates 12 C-130J-30s in a variant optimised to support special forces.  Airbus, for its part, produces the C295 locally with Tata. Recently, Airbus and Tata opened a local assembly line for the H125 light single helicopter, the first private sector helicopter production line in the country.  Separately, Embraer also signed a memorandum of understanding with Indian resources company Hindalco, the country’s biggest aluminium producer.  The MOU will see the...</t>
         </is>
       </c>
     </row>
@@ -2124,12 +1873,12 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Lockheed Tests AI-Enhanced Combat Identification on F-35 Fighter - FlightGlobal</t>
+          <t>South Korea launches EW aircraft programme - FlightGlobal</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/fixed-wing/lockheed-tests-ai-enhanced-combat-identification-on-f-35-fighter/166429.article</t>
+          <t>https://www.flightglobal.com/fixed-wing/south-korea-launches-ew-aircraft-programme/166011.article</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -2139,15 +1888,15 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 07:28:22 GMT</t>
+          <t>Wed, 21 Jan 2026 06:10:39 GMT</t>
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>0.0274</v>
+        <v>0.0244</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>2026-02-24T19:57:00Z By Ryan Finnerty    The air force’s top civilian official says he is not currently looking at Embraer’s multi-role tanker as part of a sweeping plan to recapitalise the service’s aerial refuelling fleet.  News    ### BAE demonstrates scalable electronic attack system    2026-02-24T08:27:00Z By Greg Waldron    BAE Systems has successfully demonstrated a scalable electronic attack capability that can be deployed across multiple aircraft platforms, including large uncrewed syst...</t>
+          <t>2026-01-21T05:10:00Z By Greg Waldron    The US Defense Security Cooperation Agency has approved the potential sale of four Boeing P-8A Poseidon maritime patrol aircraft to Singapore, along with torpedoes, systems and support equipment, marking a significant enhancement of the city-state’s maritime surveillance capabilities.  News    ### NORAD deploys aircraft to Greenland amid international standoff    2026-01-21T02:16:00Z By Ryan Finnerty    North American Aerospace Defense Command is deploying...</t>
         </is>
       </c>
     </row>
@@ -2157,30 +1906,30 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Saab plans 2027 unmanned demonstrator for Swedish fighter decision - FlightGlobal</t>
+          <t>Adani partners with Leonardo to build helicopters in India - Janes</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/fixed-wing/saab-plans-2027-unmanned-demonstrator-for-swedish-fighter-decision/166235.article</t>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/adani-partners-with-leonardo-to-build-helicopters-in-india</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>janes.com</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 04:03:02 GMT</t>
+          <t>Wed, 04 Feb 2026 00:00:00 GMT</t>
         </is>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.9353</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>Home  News    + Back to parent navigation item   + News   + Aerospace      - Back to parent navigation item     - Aerospace     - MRO     - Systems &amp; Interiors     - Helicopters     - Space     - Civil UAVs   + Air transport      - Back to parent navigation item     - Air transport     - Airframers     - Engines     - Programmes     - Orders &amp; Deliveries   + Safety   + Business aviation   + Region      - Back to parent navigation item     - Region     - Europe     - Africa     - North America...</t>
+          <t>“[The AW169M] is designed with dual-use technology in mind, which brings added high certification and safety standards combined with military-qualified configuration and mission capabilities,” Leonardo said.  The AW109 TrekkerM, however, with its “rugged airframe and skids”, allows to meet military requirements in the light aircraft segment, including for operations on unprepared terrains, Leonardo added.  Adani Defence and Aerospace CEO Ashish Rajvanshi said the collaboration supports domestic...</t>
         </is>
       </c>
     </row>
@@ -2190,30 +1939,30 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Embraer Ramps Up C-390 India Push With Mahindra MRO Partnership - Aviation Week</t>
+          <t>HAL revenue rises with strong long-term order book - FlightGlobal</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/defense/aircraft-propulsion/embraer-ramps-c-390-india-push-mahindra-mro-partnership</t>
+          <t>https://www.flightglobal.com/archive/2026/04/hal-revenue-rises-with-strong-long-term-order-book/</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>aviationweek.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 11:00:29 GMT</t>
+          <t>Fri, 03 Apr 2026 05:30:50 GMT</t>
         </is>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.6581</v>
+        <v>0.8549</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>+ About Aviation Week Network     - Our Story     - Content and Data Team     - Aviation Week &amp; Space Technology 100-Year   + Contact Us     - Subscriber Services     - Advertising, Marketing Services &amp; List Rentals     - Content Sales     - Events     - PR &amp; Communications     - Content Licensing and Reprints     - FAQ   Log In  Register  My Account    + Profile   + Sign Out  AWIN Access  My cart  ## Share  # Embraer Ramps Up C-390 India Push With Mahindra MRO Partnership  ## Share  Robert Wall...</t>
+          <t>The company’s order book as of 31 March stood at INR2.54 trillion, up from INR1.9 trillion a year earlier.  The company’s improved order book stemmed mostly from an INR624 billion defence ministry order for 97 Mk1A Tejas fighters. HAL’s order book also benefited from two coast guard commitments, which comprise an INR27 billion order for six Dhruvs, and an INR22 billion order for eight Dornier 225s.  The Bengaluru-based airframer says that the strong order book gives it good visibility of its rev...</t>
         </is>
       </c>
     </row>
@@ -2223,30 +1972,30 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>India Expands Airpower Through Israeli Aircraft and Defense Technology Deals - Military.com</t>
+          <t>US Air Force tests Extended Range Attack Munition cruise missile - FlightGlobal</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>https://www.military.com/feature/2026/02/01/india-expands-airpower-through-israeli-aircraft-and-defense-technology-deals.html</t>
+          <t>https://www.flightglobal.com/defence/us-air-force-tests-extended-range-attack-munition-cruise-missile/166179.article</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>military.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 10:00:00 GMT</t>
+          <t>Wed, 04 Feb 2026 11:29:08 GMT</t>
         </is>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.3996</v>
+        <v>0.0159</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>Indian reporting notes that Israel Aerospace Industries has indicated it can meet New Delhi’s “Make in India” requirement by performing part of the work locally rather than abroad, reflecting India’s push for domestic industrial participation alongside foreign technology transfers.  ## Israeli Systems Inside Indian Fighter Jets  The partnership goes well beyond aircraft purchases. Israeli technology is already embedded inside Indian fighters.  India’s domestically built Tejas light combat aircra...</t>
+          <t>2026-02-02T10:46:00Z By Craig Hoyle    Israel wants to modernise its attack helicopter fleet via an order for 30 Boeing AH-64E Apaches, the US Defense Security Cooperation Agency has disclosed.  ### More from Defence   News    ### Saudi Arabia requests $3bn support deal for Boeing F-15 fighter fleet    2026-02-04T10:52:00Z By Craig Hoyle    Riyadh has received approval from the US State Department for a potentially $3 billion package of in-service support for the Royal Saudi Air Force’s Boeing F...</t>
         </is>
       </c>
     </row>
@@ -2256,30 +2005,30 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Uruguay receives first A-29 Super Tucanos to replace A-37 fleet - FlightGlobal</t>
+          <t>Global Combat Air Programme Awards First Contract with Edgewing - The Aviationist</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/fixed-wing/uruguay-receives-first-a-29-super-tucanos-to-replace-a-37-fleet/166353.article</t>
+          <t>https://theaviationist.com/2026/04/02/gcap-awards-first-contract-edgewing/</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>theaviationist.com</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 02:53:02 GMT</t>
+          <t>Thu, 02 Apr 2026 16:40:00 GMT</t>
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>0.3955</v>
+        <v>0.9872</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>2026-02-18T05:27:00Z By Greg Waldron    French President Emmanuel Macron and Indian Prime Minister Narendra Modi have inaugurated an Airbus Helicopters H125 assembly line in India, while a joint statement hinted at progress on New Delhi’s requirement for 114 Dassault Rafale fighters under the Make in India initiative.  News    ### DARPA designates General Atomics LongShot prototype as X-68A    2026-02-18T01:21:00Z By Ryan Finnerty    The US Defense Advanced Research Projects Agency has designate...</t>
+          <t>India has also expressed an interest in joining GCAP as a development partner, owing to its current lack of a 5th generation fighter capability, and increasing tensions with Pakistan. However, it is unlikely to be able to join in this capacity owing to Japan’s insistence that no more partners are added to the development of the aircraft, in case it leads to delays in the platform entering service.  India’s current program the Advanced Medium Combat Aircraft (AMCA) looks unlikely to meet its curr...</t>
         </is>
       </c>
     </row>
@@ -2289,30 +2038,26 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>U.S. Air Force Rounds Out CCA Increment 2 Engine Awards - Aviation Week</t>
+          <t>Defence Ministry receives IAF's proposal for buying 114 'Made in India' Rafale fighter jets - The Economic Times</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/defense/aircraft-propulsion/us-air-force-rounds-out-cca-increment-2-engine-awards</t>
+          <t>https://m.economictimes.com/news/defence/defence-ministry-receives-iafs-proposal-for-buying-114-made-in-india-rafale-fighter-jets/articleshow/123854689.cms</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>aviationweek.com</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>Wed, 25 Feb 2026 09:38:55 GMT</t>
-        </is>
-      </c>
+          <t>m.economictimes.com</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr"/>
       <c r="F35" s="11" t="n">
-        <v>0.0036</v>
+        <v>0.7332</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>+ About Aviation Week Network     - Our Story     - Content and Data Team     - Aviation Week &amp; Space Technology 100-Year   + Contact Us     - Subscriber Services     - Advertising, Marketing Services &amp; List Rentals     - Content Sales     - Events     - PR &amp; Communications     - Content Licensing and Reprints     - FAQ   Log In  Register  My Account    + Profile   + Sign Out  AWIN Access  My cart  This article is published in  Aerospace Daily &amp; Defense Report part of Aviation Week Intelligence...</t>
+          <t>The Defence Ministry has received and started discussions on the proposal from the Indian Air Force for acquiring 114 'Made in India' Rafale fighter jets, which would be built by the French firm Dassault Aviation involving Indian aerospace firms.      The proposal, expected to be worth over Rs 2 lakh crore, including the indigenous content of more than 60 per cent, is expected to be taken up for discussion by the Defence Procurement Board headed by the Defence Secretary in the next few weeks....</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2067,12 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>France edges closer to Eurodrone exit with LPM revision - FlightGlobal</t>
+          <t>Rolls-Royce completes key tests for B-52J F130 engine - FlightGlobal</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/defence/2026/04/france-edges-closer-to-eurodrone-exit-with-lpm-revision/</t>
+          <t>https://www.flightglobal.com/fixed-wing/rolls-royce-completes-key-tests-for-b-52j-f130-engine/166428.article</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -2337,15 +2082,15 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Mon, 13 Apr 2026 15:33:29 GMT</t>
+          <t>Wed, 25 Feb 2026 06:28:17 GMT</t>
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.0481</v>
+        <v>0.7058</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>Portugal has selected the Tecnam P-Mentor as its air force basic trainer, with seven examples of the piston-powered single to be supplied through an agreement with Spanish training provider World Aviation. CONTRACT UK MoD orders Skyhammer counter-drone missiles to guard against Iranian Shahed threat  Cambridge Aerospace is to start deliveries of its Skyhammer counter-drone interceptor within weeks, under a contract announced by the UK Ministry of Defence (MoD). FIXED-WING India to get depot for...</t>
+          <t>“Completing the series of tests at AEDC’s world-class facility gives us confidence in the engine and associated systems as we proceed into test aircraft modification and flight testing.”  The F130 completed its critical design review in late 2024, setting the stage for the first flight test engines.  Ultimately eight F130s, derived from the company’s BR725 commercial engine, will power the B-52J. They will replace legacy Pratt &amp; Whitney TF33 engines under the B-52 Commercial Engine Replacement P...</t>
         </is>
       </c>
     </row>
@@ -2355,30 +2100,30 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>India's Mehair Seaplane Service Orders Hybrid-electric Polaris Aircraft - Aviation International News</t>
+          <t>Safran Could Do Without Russian Titanium, CEO Says - Aviation Week</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>https://www.ainonline.com/aviation-news/air-transport/2026-02-04/indias-mehair-orders-hybrid-electric-polaris-aircraft</t>
+          <t>https://aviationweek.com/aerospace/manufacturing-supply-chain/safran-could-do-without-russian-titanium-ceo-says</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>ainonline.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 12:00:00 GMT</t>
+          <t>Tue, 17 Feb 2026 11:08:23 GMT</t>
         </is>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.0209</v>
+        <v>0.3469</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>By Charles Alcock • Managing Editor  February 4, 2026  ## More In Aircraft  ## Support for the M-346F in Indonesia Gathers Momentum  ### The Indonesian MoD is now discussing a wide-ranging support solution  Aircraft  ## IAI Shows Off Special-mission Gulfstream G600  ### The Ellyon is a multirole AEW/ISR/EA platform  Aircraft  ## Canada’s Fighter Debate Reopens Door for Gripen  ### Targeted rate of 36 units a year dependant on increased industrial collaboration  Aircraft  ## HAL and UAC Plot Indi...</t>
+          <t>## Share  Thierry Dubois February 17, 2026  PARIS—Safran's diversification in suppliers of titanium billets and forgings is sufficiently well underway for the engine and equipment manufacturer to do without Russian titanium, CEO Olivier Andriès said Feb. 13. Titanium is so critical for the European aerospace industry that the metal has so far...  Thierry Dubois  Thierry Dubois has specialized in aerospace journalism since 1997. An engineer in fluid dynamics from Toulouse-based Enseeiht, he cover...</t>
         </is>
       </c>
     </row>
@@ -2388,30 +2133,30 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>OGMA And Axiscades Partner To Strengthen India’s MRO Capabilities - Aviation Week Network</t>
+          <t>US To Develop Next Generation Stealth Fighter Jet: What To Know - Newsweek</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/mro/ogma-axiscades-partner-strengthen-indias-mro-capabilities</t>
+          <t>https://www.newsweek.com/us-develop-next-generation-stealth-fighter-what-know-11570702</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>aviationweek.com</t>
+          <t>newsweek.com</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Fri, 30 Jan 2026 15:31:27 GMT</t>
+          <t>Tue, 24 Feb 2026 15:17:00 GMT</t>
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>0.9992</v>
+        <v>0.2933</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>Axiscades is establishing an integrated aerospace and defense manufacturing and MRO hub near Bengaluru International Airport. The facility will include dedicated aircraft hangars, engine shops, a welding center of excellence and production facilities along with systems integration and certification testing infrastructure. The facility will be designed to support both civil and defense aviation requirements, enabling India to perform complex maintenance, upgrades and certifications domestically r...</t>
+          <t>...  No sixth-generation jets are currently in use. The most sophisticated fighter jets available for militaries at the moment are fifth-generation aircraft, like the U.S.' F-35 and F-22. The new wave of aircraft will be the next major leap forward for fighter jets, and help determine which militaries have the most formidable air forces.  U.S. officials had prioritized the USAF's quest for sixth-generation capabilities over the Navy's F/A-XX carrier-based program, arguing defense companies would...</t>
         </is>
       </c>
     </row>
@@ -2421,30 +2166,30 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>The New U.S. Air Force F-47 NGAD Stealth Fighter Might Have Just Broke Cover - 19FortyFive</t>
+          <t>India OKs Plans To Buy Airlifters, S-400s, UAS - Aviation Week</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>https://www.19fortyfive.com/2026/02/the-new-u-s-air-force-f-47-ngad-stealth-fighter-might-have-just-broke-cover/</t>
+          <t>https://aviationweek.com/defense/aircraft-propulsion/india-oks-plans-buy-airlifters-s-400s-uas</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>19fortyfive.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Fri, 20 Feb 2026 21:08:08 GMT</t>
+          <t>Fri, 27 Mar 2026 18:34:17 GMT</t>
         </is>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.7009</v>
+        <v>0.2561</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>A newly released Pratt &amp; Whitney update on its XA103 adaptive-cycle engine has provided a new look into the propulsion system intended to power the U.S. Air Force’s next-generation F-47 fighter, the centerpiece of the Next Generation Air Dominance (NGAD) program.  In a newly released video about the engine, viewers also got a look at a proposed next-generation fighter design that likely represents the shape and configuration of the next-generation NGAD fighter.  F-47 Fighter from Boeing. Image C...</t>
+          <t>Already a member of AWIN or subscribe to Aerospace Daily &amp; Defense Report through your company? Loginwith your existing email and password.  Not a member?  Learn how you can access the market intelligence and data you need to stay abreast of what's happening in the aerospace and defense community.  |  |  |  --- | | Login | Learn How |  ## Related Content  Nigeria Seeking Airbus C295 Procurement  India Seeks Role In FCAS Or GCAP Fighter Consortia  Dassault Gears Up For Rafale Output Uptick, India...</t>
         </is>
       </c>
     </row>
@@ -2454,30 +2199,30 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>TAKE OFF project spools up as open-fan partners build towards 2029 flight tests - FlightGlobal</t>
+          <t>Safran’s Aneto To Power New-Build Bell 214STs - Aviation Week</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/engines/take-off-project-spools-up-as-open-fan-partners-build-towards-2029-flight-tests/166538.article</t>
+          <t>https://aviationweek.com/aerospace/aircraft-propulsion/safrans-aneto-power-new-build-bell-214sts</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 16:30:00 GMT</t>
+          <t>Thu, 12 Mar 2026 11:20:34 GMT</t>
         </is>
       </c>
       <c r="F40" s="8" t="n">
-        <v>0.2428</v>
+        <v>0.0456</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>Source: Safran  Open-fan architecture is being pursued by Safran-GE joint venture CFM International  Building on the preceding OFELIA project in Clean Aviation’s first phase, TAKE OFF will use the technologies matured through that effort to develop an open-fan engine capable of undertaking a flight-test campaign.  By the end of the project in December 2029, the overall open-fan engine design should have been raised to technology readiness level (TRL) 6, Clean Aviation project documents state.  “...</t>
+          <t>Verticon 2026  Safran  Bell  ## Subscription Required  Safran’s Aneto To Power New-Build Bell 214STs is published in Aerospace Daily &amp; Defense Report, an Aviation Week Intelligence Network (AWIN) Market Briefing and is included with your AWIN membership.  Already a member of AWIN or subscribe to Aerospace Daily &amp; Defense Report through your company? Loginwith your existing email and password.  Not a member?  Learn how you can access the market intelligence and data you need to stay abreast of wh...</t>
         </is>
       </c>
     </row>
@@ -2487,30 +2232,30 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>India’s MoD claims highest ever funding boost in Union Budget 2026-27 - Army Technology</t>
+          <t>Eurofighter wins contract to certificate Typhoon’s aerodynamic modification kit - FlightGlobal</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>https://www.army-technology.com/news/india-defence-budget-2026-27/</t>
+          <t>https://www.flightglobal.com/defence/eurofighter-wins-contract-to-certificate-typhoons-aerodynamic-modification-kit/166233.article</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>army-technology.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:26:32 GMT</t>
+          <t>Thu, 05 Feb 2026 13:58:22 GMT</t>
         </is>
       </c>
       <c r="F41" s="11" t="n">
-        <v>0.1656</v>
+        <v>0.0235</v>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>For research and development, the Defence Research and Development Organisation (DRDO) will receive an increased budget of Rs291bn in FY 2026–27, up from Rs268bn in the previous year, with Rs172bn set aside for capital expenditure.  Since December 2025, several initiatives have sought to promote research and development (R&amp;D) in defence manufacturing. About one-quarter of the DRDO R&amp;D budget has been made available to industry, start-ups, and academia following earlier policy announcements.  Bet...</t>
+          <t>The UK also will introduce an electronic-attack capability with 40 Tranche 3-standard Typhoons slated to receive the ECRS Mk2 active electronically scanned array radar via a recently-contracted upgrade by Leonardo UK and BAE Systems.  The subject of extensive previous flight-testing, the aerodynamic kit incorporates “extensions to the fuselage strakes, the flaperons and the leading-edge root”, and will deliver “a noticeable increase in maximum wing lift”.  This also will “further improve the jet...</t>
         </is>
       </c>
     </row>
@@ -2520,30 +2265,30 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>USMC selects GA-ASI YFQ-42A for MUX TACAIR assessment work - FlightGlobal</t>
+          <t>India clears the way for landmark deal to acquire French Rafale jets - Defense News</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/military-uavs/usmc-selects-ga-asi-yfq-42a-for-mux-tacair-assessment-work/166277.article</t>
+          <t>https://www.defensenews.com/global/asia-pacific/2026/02/13/india-clears-the-way-for-landmark-deal-to-acquire-french-rafale-jets/</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>defensenews.com</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 05:47:21 GMT</t>
+          <t>Fri, 13 Feb 2026 12:01:00 GMT</t>
         </is>
       </c>
       <c r="F42" s="8" t="n">
-        <v>0.0057</v>
+        <v>0.532</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>Home  News    + Back to parent navigation item   + News   + Aerospace      - Back to parent navigation item     - Aerospace     - MRO     - Systems &amp; Interiors     - Helicopters     - Space     - Civil UAVs   + Air transport      - Back to parent navigation item     - Air transport     - Airframers     - Engines     - Programmes     - Orders &amp; Deliveries   + Safety   + Business aviation   + Region      - Back to parent navigation item     - Region     - Europe     - Africa     - North America...</t>
+          <t>Featured:  Coverage: Singapore Airshow  Coverage: Venezuela  Whitepaper: Modular Open Systems  #### Asia Pacific  # India clears the way for landmark deal to acquire French Rafale jets  By Anjana Pasricha  French Air and Space Force Rafale fighter jets taxi toward the runway at Air Base 120 in Cazaux, south-western France, on Jan. 29, 2026, during the Topaze 2026 exercise. (Philippe Lopez / AFP via Getty Images)  NEW DELHI — India has cleared a proposal to buy 114 Rafale multirole fighter jets f...</t>
         </is>
       </c>
     </row>
@@ -2553,30 +2298,30 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Boeing Continuing Some ITEP Apache Work Despite Army Threat - Aviation Week Network</t>
+          <t>India to get depot for F404-IN20 engine - FlightGlobal</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/defense/aircraft-propulsion/boeing-continuing-some-itep-apache-work-despite-army-threat</t>
+          <t>https://www.flightglobal.com/fixed-wing/2026/04/india-to-get-depot-for-f404-in20-engine/</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>aviationweek.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 09:02:28 GMT</t>
+          <t>Mon, 13 Apr 2026 07:17:35 GMT</t>
         </is>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.0036</v>
+        <v>0.4278</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>Brian Everstine  Brian Everstine is the Pentagon Editor for Aviation Week, based in Washington, D.C.   Boeing Defense and Space  Singapore Airshow 2026  Boeing AH-64 Apache  GE Aerospace  ## Related Content  Saab Eyes 2027 Flight Of Future Fighter Demonstrator  Airbus Breathes Easier On A400M Given Demand Signals  Airbus: Sharp Rise In Tanker Interest Amid MRTT+ Rollout  Airbus, Singapore Fully Certify A3R Capability On A330 MRTT  Saab Sees Potential Canada Production Line Serving Other Gripen B...</t>
+          <t>In early February, HAL issued a statement stating that five LCA Mk1A variants were ready for delivery. It added that nine additional jets had been “built and flown”, and that these would be readied for delivery pending receipt of engines from GE Aerospace.  At the time HAL indicated that the “supply position from GE is positive, and the future delivery outlook aligns with HAL’s delivery plans.”  At the Paris air show in June 2025, Sunil told FlightGlobal that HAL expected to get 12 F404s by the...</t>
         </is>
       </c>
     </row>
@@ -2586,30 +2331,30 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Dassault Gears Up For Rafale Output Uptick, Indian Production - Aviation Week</t>
+          <t>India and US maintain momentum in defense ties - Defense News</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/defense/aircraft-propulsion/dassault-gears-rafale-output-uptick-indian-production</t>
+          <t>https://www.defensenews.com/global/asia-pacific/2026/02/04/india-and-us-maintain-momentum-in-defense-ties/</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>aviationweek.com</t>
+          <t>defensenews.com</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 18:07:57 GMT</t>
+          <t>Wed, 04 Feb 2026 11:58:00 GMT</t>
         </is>
       </c>
       <c r="F44" s="8" t="n">
-        <v>0.9963</v>
+        <v>0.1913</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>Rate 5 may take into account production in India. Dassault partnered with Tata Advanced Systems last year to establish local production of two Rafale fuselage sections per month, with the first delivery scheduled for 2028. If the Indian government signs a contract for 114 more Rafales—a proposed order that the country’s Defense Acquisition Council approved—a second final assembly line for the fighter may be created in Hyderabad. A target production rate has yet to be specified, Trappier said, st...</t>
+          <t>“That is significant because for a long time, India has not bought much offensive military equipment from the U.S. except, say, Apache helicopters and howitzers. It has mostly bought support platforms,” he pointed out. “But now over the next 15 to 20 years, an estimated 350 to 400 fighter jets that will be made in India will have American engines at the heart of the planes. That is almost 40 to 50 percent of the sanctioned fighter strength of the Indian Air Force.”  While India is building fight...</t>
         </is>
       </c>
     </row>
@@ -2619,30 +2364,30 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Dassault targets Indian contract for blockbuster Rafale order by year-end - FlightGlobal</t>
+          <t>India's ground-based VUHF Communication Jammer breaks cover - Janes</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/defence/dassault-targets-indian-contract-for-blockbuster-rafale-order-by-year-end/166522.article</t>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/indias-ground-based-vuhf-communication-jammer-breaks-cover</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>janes.com</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 17:26:15 GMT</t>
+          <t>Fri, 23 Jan 2026 00:00:00 GMT</t>
         </is>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0.5622</v>
+        <v>0.1554</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>It has already signed an agreement with Tata Advanced Systems to establish a second source of Rafale fuselage sections in the country – the first time parts for the combat jet have been produced outside France – and will ultimately establish a local final assembly line too.  As a forerunner, it has set up a joint-venture, Dassault-Reliance Aerostructures, to manufacture Falcon 2000 business jets, a step Trappier calls “a form of practice for the Make in India initiative”.  Meanwhile, the airfram...</t>
+          <t>skip to main content    Search Janes     # India's ground-based VUHF Communication Jammer breaks cover  By Akhil Kadidal &amp; Ajay Shankar Pandey |  Bharat Electronics Limited unveiled a scale model of its new Ground Based Very-Ultra High Frequency Communication Jammer in Bangalore, India, on 20 January 2026. (Janes/Akhil Kadidal)  Details have emerged about Bharat Electronics Limited's (BEL's) new Ground Based Very-Ultra High Frequency (GBVU) Communication Jammer, with a company spokesperson telli...</t>
         </is>
       </c>
     </row>
@@ -2652,30 +2397,30 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Why air forces must target their CCA doctrine deficit - FlightGlobal</t>
+          <t>Self-reliance a myth? India’s LCA Tejas Mk1A heavily relies on Israeli radar and EW systems - Zee News</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/defence/why-air-forces-must-target-their-cca-doctrine-deficit/165910.article</t>
+          <t>https://zeenews.india.com/india/self-reliance-a-myth-india-s-lca-tejas-mk1a-fighter-jet-heavily-relies-on-israeli-radar-and-ew-systems-3012866.html</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>zeenews.india.com</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Mon, 26 Jan 2026 09:36:50 GMT</t>
+          <t>Mon, 02 Feb 2026 03:14:05 GMT</t>
         </is>
       </c>
       <c r="F46" s="8" t="n">
-        <v>0.0497</v>
+        <v>0.1523</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>### More from Defence   News    ### Elbit Systems UK takes full ownership of Watchkeeper industrial venture UTacS    2026-01-23T14:59:00Z By Craig Hoyle    Elbit Systems UK has taken full ownership of the company established to deliver the British Army’s fleet of Watchkeeper tactical uncrewed aerial vehicles.  News    ### SOF Week plans aviation demonstration space for 2026 conference    2026-01-23T00:09:00Z By Ryan Finnerty    This year’s edition of the annual special operations conference in T...</t>
+          <t>Stay informed on all the latest news, real-time  breaking news updates, and follow all the important headlines in india news andworld News on Zee News.  ## TAGS  LCA Tejas Mk1A Fighter AircraftIndian Air ForceIsraeli Radar TechnologyFighter Jet Self-Reliance  Advertisement  Live Tv  Advertisement  ### Trending news  women bracelet  Bracelets to Elevate Your Everyday Look  Iran-US tension  Any attack by US will be 'regional war', Iran's supreme leader warns  Full Coverage Concealer  Concealers Th...</t>
         </is>
       </c>
     </row>
@@ -2685,30 +2430,30 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Pratt &amp; Whitney Faces GTF Balancing Act In Airbus Delivery Negotiation - Aviation Week Network</t>
+          <t>Lockheed Tests AI-Enhanced Combat Identification on F-35 Fighter - FlightGlobal</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/aerospace/manufacturing-supply-chain/pratt-whitney-faces-gtf-balancing-act-airbus-delivery</t>
+          <t>https://www.flightglobal.com/fixed-wing/lockheed-tests-ai-enhanced-combat-identification-on-f-35-fighter/166429.article</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>aviationweek.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 08:28:51 GMT</t>
+          <t>Wed, 25 Feb 2026 07:28:22 GMT</t>
         </is>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.0012</v>
+        <v>0.0274</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
-          <t>Although Deurloo says the number of A320neo AOGs is now reduced by around 20% compared to its peak of more than 700, the situation: “will continue on for a couple years. We know that's not going away at the end of 2026 but I think a lot depends on our execution this year and where we end up next year as well. We feel confident by the end of this decade, we're going to be in more of a normalized state,” he adds.  Guy Norris  Guy is a Senior Editor for Aviation Week, covering technology and propul...</t>
+          <t>2026-02-24T19:57:00Z By Ryan Finnerty    The air force’s top civilian official says he is not currently looking at Embraer’s multi-role tanker as part of a sweeping plan to recapitalise the service’s aerial refuelling fleet.  News    ### BAE demonstrates scalable electronic attack system    2026-02-24T08:27:00Z By Greg Waldron    BAE Systems has successfully demonstrated a scalable electronic attack capability that can be deployed across multiple aircraft platforms, including large uncrewed syst...</t>
         </is>
       </c>
     </row>
@@ -2718,30 +2463,30 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>India approves $39 billion purchase of 114 Rafale jets ahead of Macron visit - AeroTime</t>
+          <t>MHI, Shield AI complete autonomous flight tests in Japan - FlightGlobal</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>https://www.aerotime.aero/articles/india-39-billion-purchase-114-rafale-fighter-jet</t>
+          <t>https://www.flightglobal.com/military-uavs/mhi-shield-ai-complete-autonomous-flight-tests-in-japan/166696.article</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>aerotime.aero</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 13:32:35 GMT</t>
+          <t>Wed, 18 Mar 2026 12:14:40 GMT</t>
         </is>
       </c>
       <c r="F48" s="8" t="n">
-        <v>0.3857</v>
+        <v>0.0165</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t># India approves $39 billion purchase of 114 Rafale jets ahead of Macron visit  ByIan Molyneaux  Edited ByAndy Murray  India has approved the $39 billion purchase of 114 Dassault Rafale fighter jets, in an effort to bolster the Indian Air Force’s (IAF) operational readiness and modernize its military fleet.  On February 12, 2026, the Defense Acquisition Council (DAC), chaired under the guidance of Defense Minister Rajnath Singh, backed the deal, along with the purchase of swathe of other militar...</t>
+          <t>Home  News    + - Aerospace        MRO        Systems &amp; Interiors        Helicopters        Space        Civil UAVs     - Air transport        Airframers        Engines        Programmes        Orders &amp; Deliveries   + - Safety     - Business aviation     - Region        Europe        Africa        North America        Latin America        Asia Pacific        Middle East   + - Analysis     - Interviews     - Opinion     - In depth   + - Podcasts  Airlines    + - Strategy     - Networks     - Flee...</t>
         </is>
       </c>
     </row>
@@ -2751,30 +2496,26 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>From Sindoor to Self-Reliance: The ₹7.85 Lakh Crore Blueprint for a Fortified India - Zee News</t>
+          <t>DAC clears record ₹3.60 lakh crore defence procurements, 114 Rafale jets and six P-8I aircraft among major approvals - The Hindu</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/from-sindoor-to-self-reliance-the-7-85-lakh-crore-blueprint-for-a-fortified-india-3012805.html</t>
+          <t>https://www.thehindu.com/news/national/defence-acquisition-council-rafale-jets-acquisition-proposal/article70623645.ece</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>zeenews.india.com</t>
-        </is>
-      </c>
-      <c r="E49" s="11" t="inlineStr">
-        <is>
-          <t>Sun, 01 Feb 2026 13:52:51 GMT</t>
-        </is>
-      </c>
+          <t>thehindu.com</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr"/>
       <c r="F49" s="11" t="n">
-        <v>0.0412</v>
+        <v>0.6942</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>Importantly, ₹1.39 lakh crore (75% of capital purchases) will go to Indian industries, including private companies. This will boost local defence manufacturing, create jobs, build strong supply chains, and attract long-term investment.  Revenue Spending (for daily running, operations, salaries, and maintenance): ₹5,53,668 crore  This covers salaries, allowances, fuel, training, and keeping forces operationally ready.  Pensions: ₹1,71,338 crore (about 21.84% of the total budget) for ex-servicemen...</t>
+          <t>The proposals include 114 Rafale fighter jets from France for the Indian Air Force (IAF) and six P-8I long-range maritime reconnaissance aircraft from the United States for the Indian Navy.  DAC clears proposal for India to procure 114 Rafale fighter jets from France  India has moved closer to acquiring 114 additional Rafale fighter jets after the Defence Acquisition Council cleared the proposal to procure the aircraft from France’s Dassault Aviation. Around 18 jets are expected in fly-away cond...</t>
         </is>
       </c>
     </row>
@@ -2784,30 +2525,30 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Indonesia could obtain fifth KF-21 prototype - FlightGlobal</t>
+          <t>Embraer Ramps Up C-390 India Push With Mahindra MRO Partnership - Aviation Week</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/fixed-wing/2026/04/indonesia-could-obtain-fifth-kf-21-prototype/</t>
+          <t>https://aviationweek.com/defense/aircraft-propulsion/embraer-ramps-c-390-india-push-mahindra-mro-partnership</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>Wed, 08 Apr 2026 06:33:37 GMT</t>
+          <t>Thu, 19 Feb 2026 11:00:29 GMT</t>
         </is>
       </c>
       <c r="F50" s="8" t="n">
-        <v>0.0046</v>
+        <v>0.6581</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>E-mailURL  ### Related posts  Safety Military-support Falcon suffers dual engine malfunction in icing weather  Hungarian investigators are probing a incident involving dual engine malfunction on a Dassault Falcon 20 which was supporting a NATO military exercise. Iran Conflict Iran rescue mission featured 155 aircraft, refuelling over enemy territory and one lost A-10  Some 155 aircraft were involved in the recovery mission, including bombers, fighters, tankers, rescue helicopters and special ope...</t>
+          <t>+ About Aviation Week Network     - Our Story     - Content and Data Team     - Aviation Week &amp; Space Technology 100-Year   + Contact Us     - Subscriber Services     - Advertising, Marketing Services &amp; List Rentals     - Content Sales     - Events     - PR &amp; Communications     - Content Licensing and Reprints     - FAQ   Log In  Register  My Account    + Profile   + Sign Out  AWIN Access  My cart  ## Share  # Embraer Ramps Up C-390 India Push With Mahindra MRO Partnership  ## Share  Robert Wall...</t>
         </is>
       </c>
     </row>
@@ -2817,30 +2558,30 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Stealth aircraft: the technology of staying hidden - ynetnews</t>
+          <t>Safran targets higher 2026 profit as jet engine services prosper - Reuters</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>https://www.ynetnews.com/tech-and-digital/article/ryrthgltbx</t>
+          <t>https://www.reuters.com/business/aerospace-defense/safran-targets-higher-2026-profit-jet-engine-services-prosper-2026-02-13/</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>ynetnews.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 21:19:51 GMT</t>
+          <t>Fri, 13 Feb 2026 06:05:23 GMT</t>
         </is>
       </c>
       <c r="F51" s="11" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.4847</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>One of the strongest sources of radar reflections in jet aircraft is the engine air intakes and other internal cavities, which radar waves can enter and reflect repeatedly off internal surfaces. Exposed compressor blades are especially conspicuous on radar. To reduce these returns, designers may use fine metal meshes that block radio waves without significantly restricting airflow—similar to the mesh on the inside of a microwave-oven door, where the size and spacing of the holes keep microwaves...</t>
+          <t>Sign uphere.  Safran, which co-produces engines for Airbus and Boeing jets with GE Aerospace under their CFM venture, projected 6.1 billion to 6.2 billion euros ($7.2 billion to $7.4 billion) in recurring operating profit for this calendar year.  That was on an estimated percentage rise in revenue in the "low to mid teens" over the period. A French version of its earnings release specified this as an increase of 12% to 15%.  For 2025, Safran posted a 26% rise in recurring operating income on an...</t>
         </is>
       </c>
     </row>
@@ -2850,30 +2591,30 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>GE Aerospace Reveals $300M Boost For Singapore Engine Repair Site - Aviation Week Network</t>
+          <t>India Expands Airpower Through Israeli Aircraft and Defense Technology Deals - Military.com</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/mro/aircraft-propulsion/ge-aerospace-reveals-300m-boost-singapore-engine-repair-site</t>
+          <t>https://www.military.com/feature/2026/02/01/india-expands-airpower-through-israeli-aircraft-and-defense-technology-deals.html</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>aviationweek.com</t>
+          <t>military.com</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:09:21 GMT</t>
+          <t>Sun, 08 Feb 2026 10:00:00 GMT</t>
         </is>
       </c>
       <c r="F52" s="8" t="n">
-        <v>0.3628</v>
+        <v>0.3996</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>Running through 2029, the expansion is aimed at speeding up engine turnaround times and forging closer links with operators as fleets of GE- and CFM-powered aircraft continue to grow. The maintenance, repair and overhaul (MRO) initiative will build on GE’s Flight Deck lean operating model, the engine-maker says.  The expansion phase will add a new module repair capability for the CFM Leap-1A/B high-pressure turbine and a larger component portfolio to enhance regional support as the main service...</t>
+          <t>Indian reporting notes that Israel Aerospace Industries has indicated it can meet New Delhi’s “Make in India” requirement by performing part of the work locally rather than abroad, reflecting India’s push for domestic industrial participation alongside foreign technology transfers.  ## Israeli Systems Inside Indian Fighter Jets  The partnership goes well beyond aircraft purchases. Israeli technology is already embedded inside Indian fighters.  India’s domestically built Tejas light combat aircra...</t>
         </is>
       </c>
     </row>
@@ -2883,30 +2624,30 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>India showcases new hypersonic missile in military parade - Janes</t>
+          <t>Uruguay receives first A-29 Super Tucanos to replace A-37 fleet - FlightGlobal</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>https://www.janes.com/osint-insights/defence-news/weapons/india-showcases-new-hypersonic-missile-in-military-parade</t>
+          <t>https://www.flightglobal.com/fixed-wing/uruguay-receives-first-a-29-super-tucanos-to-replace-a-37-fleet/166353.article</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>janes.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Mon, 26 Jan 2026 10:41:55 GMT</t>
+          <t>Thu, 19 Feb 2026 02:53:02 GMT</t>
         </is>
       </c>
       <c r="F53" s="11" t="n">
-        <v>0.1755</v>
+        <v>0.3955</v>
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>skip to main content  Search Janes  # India showcases new hypersonic missile in military parade  By Jon Grevatt |  India's LR-AShM is pictured during the country's 77th Republic Day parade at Kartavya Path in New Delhi on 26 January. (Sajjad Hussain/AFP via Getty Images)  India's Defence Research and Development Organisation (DRDO) showcased its new Long Range Anti-Ship Hypersonic Missile (LR-AshM) in a military parade to mark the country's 77th Republic Day on 26 January.  The LR-AshM, which is...</t>
+          <t>2026-02-18T05:27:00Z By Greg Waldron    French President Emmanuel Macron and Indian Prime Minister Narendra Modi have inaugurated an Airbus Helicopters H125 assembly line in India, while a joint statement hinted at progress on New Delhi’s requirement for 114 Dassault Rafale fighters under the Make in India initiative.  News    ### DARPA designates General Atomics LongShot prototype as X-68A    2026-02-18T01:21:00Z By Ryan Finnerty    The US Defense Advanced Research Projects Agency has designate...</t>
         </is>
       </c>
     </row>
@@ -2916,12 +2657,12 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Pratt &amp; Whitney’s GTF deliveries increased 6% in 2025, while recall recovery progresses - FlightGlobal</t>
+          <t>France, India inaugurate H125 line as potential Rafale deal looms - FlightGlobal</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/engines/pratt-and-whitneys-gtf-deliveries-increased-6-in-2025-while-recall-recovery-progresses/166092.article</t>
+          <t>https://www.flightglobal.com/helicopters/france-india-inaugurate-h125-line-as-potential-rafale-deal-looms/166349.article</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -2931,15 +2672,15 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 13:58:25 GMT</t>
+          <t>Wed, 18 Feb 2026 05:53:24 GMT</t>
         </is>
       </c>
       <c r="F54" s="8" t="n">
-        <v>0.043</v>
+        <v>0.221</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>Calio says P&amp;W is also making progress introducing product updates. Production has started for the GTF Advantage, an improved PW1100G variant P&amp;W says will be more durable and provide more thrust. That engine should enter service this year, Calio says.  Also in 2026, P&amp;W expects to achieve certification and begin installing its “Hot Section Plus” upgrade package into current-generation PW1100Gs. That retrofit involves equipping engines with 35 new components that are otherwise unique to the GTF...</t>
+          <t>“They expressed their wish to further strengthen their partnership in defence aeronautics, especially in the field of manufacturing of fighter aircraft and combat aircraft engines under the Make in India initiative, and welcomed recent positive developments in this regard,” reads the joint statement.  An AoN from the Defence Acquisition Council is a formal approval that a military purchase is justified, allowing the government to move forward into detailed tendering, vendor selection, and eventu...</t>
         </is>
       </c>
     </row>
@@ -2949,30 +2690,30 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>GE commercial engine deliveries jumped 25% in 2025 amid supply chain recovery - FlightGlobal</t>
+          <t>U.S. Air Force Rounds Out CCA Increment 2 Engine Awards - Aviation Week</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/engines/ge-commercial-engine-deliveries-jumped-25-in-2025-amid-supply-chain-recovery/166035.article</t>
+          <t>https://aviationweek.com/defense/aircraft-propulsion/us-air-force-rounds-out-cca-increment-2-engine-awards</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Thu, 22 Jan 2026 15:15:56 GMT</t>
+          <t>Wed, 25 Feb 2026 09:38:55 GMT</t>
         </is>
       </c>
       <c r="F55" s="11" t="n">
-        <v>0.0291</v>
+        <v>0.0036</v>
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>Skip to navigation   Trending now  FlightGlobal has a new podcast - listen now  2026 World Air Forces directory  Dubai Airshow  Singapore Airshow  Site name  Site name  Search our site  Close menu [...] By Jon Hemmerdinger2026-01-22T15:01:00+00:00  GE Aerospace ramped up its production system last year amid easing supply chain troubles, with the company delivering 2,386 commercial aircraft engines in 2025, a 25% year-on-year bump.  The improvement came as GE and competitors seek to overcome long...</t>
+          <t>+ About Aviation Week Network     - Our Story     - Content and Data Team     - Aviation Week &amp; Space Technology 100-Year   + Contact Us     - Subscriber Services     - Advertising, Marketing Services &amp; List Rentals     - Content Sales     - Events     - PR &amp; Communications     - Content Licensing and Reprints     - FAQ   Log In  Register  My Account    + Profile   + Sign Out  AWIN Access  My cart  This article is published in  Aerospace Daily &amp; Defense Report part of Aviation Week Intelligence...</t>
         </is>
       </c>
     </row>
@@ -2982,30 +2723,26 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Australia explores European weapons integration for Ghost Bat - Janes</t>
+          <t>India approves proposal to acquire 114 Rafale fighter jets – Firstpost</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>https://www.janes.com/osint-insights/defence-news/defence/australia-explores-european-weapons-integration-for-ghost-bat</t>
+          <t>https://www.firstpost.com/india/india-approves-proposal-to-acquire-114-rafale-fighter-jets-13969491.html</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>janes.com</t>
-        </is>
-      </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t>Wed, 25 Feb 2026 12:35:36 GMT</t>
-        </is>
-      </c>
+          <t>firstpost.com</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr"/>
       <c r="F56" s="8" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.7651</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>### More news articles  Defence  ### Australia explores European weapons integration for Ghost Bat  Read Article  Industry  ### Australia signs C-UAS research acceleration agreement with DroneShield  Read Article  Land  ### Thailand receives additional Stryker vehicles  Read Article  ## See how Janes delivers verified defence intelligence for faster, safer decisions   The world's most complete foundational military data asset.  500,000+ analyst hours per year to keep data current.  Easy integrat...</t>
+          <t>Whatsapp Facebook Twitter  ## Proposed acquisition, featuring over 60% indigenous content and technology transfer, could become India’s largest-ever defence deal and significantly boost the IAF’s combat strength  Advertisement  Subscribe Join Us  + Follow us On Google  Choose  Firstpost on Google  Rafale is a tried and tested aircraft for India. Image: Dassault Aviation  The Defence Procurement Board has approved a proposal to acquire 114 Rafale fighter aircraft, according to a News18 report, ci...</t>
         </is>
       </c>
     </row>
@@ -3015,30 +2752,30 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Exclusive: Jet engine maker CFM studies plan B for next fuel-saving design, sources say - Reuters</t>
+          <t>Safran Boosts Forging Capabilities With Engine Facility Investment - Aviation Week</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/aerospace-defense/jet-engine-maker-cfm-studies-plan-b-next-fuel-saving-design-sources-say-2026-02-12/</t>
+          <t>https://aviationweek.com/aerospace/manufacturing-supply-chain/safran-boosts-forging-capabilities-engine-facility-investment</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 13:11:21 GMT</t>
+          <t>Tue, 14 Apr 2026 14:44:06 GMT</t>
         </is>
       </c>
       <c r="F57" s="11" t="n">
-        <v>0.0027</v>
+        <v>0.3088</v>
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>The venture co-owned by GE Aerospace (GE.N), opens new tab and France's Safran (SAF.PA), opens new tab has been championing an open-rotor engine, featuring a large exposed fan instead of a traditional casing, as the most efficient and environmentally friendly architecture for the next series of Airbus (AIR.PA), opens new tab and Boeing (BA.N), opens new tab jets.  Sign uphere.  It says this would generate fuel and emissions savings of 20% under a widely publicised research programme called RISE....</t>
+          <t>- Aerospace     - Air Transport     - MRO     - Defense     - Space     - Business Aviation   + Type View All Products     - Intelligence Bundles         AWIN - Premium        AWIN - Aerospace and Defense        AWIN - Business Aviation        AWIN - Commercial Aviation     - Market Briefings         Aerospace Daily &amp; Defense Report        Aviation Daily        SpeedNews        Business Aviation &amp; AAM Report     - Directories         Air Charter Guide        Aviation Week Marketplace        Rout...</t>
         </is>
       </c>
     </row>
@@ -3048,30 +2785,30 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>India Targets 50% Local Supply Chain For Next Rafales - Aviation Week</t>
+          <t>India's Mehair Seaplane Service Orders Hybrid-electric Polaris Aircraft - Aviation International News</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/defense/supply-chain/india-targets-50-local-supply-chain-next-rafales</t>
+          <t>https://www.ainonline.com/aviation-news/air-transport/2026-02-04/indias-mehair-orders-hybrid-electric-polaris-aircraft</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>aviationweek.com</t>
+          <t>ainonline.com</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 20:43:21 GMT</t>
+          <t>Wed, 04 Feb 2026 12:00:00 GMT</t>
         </is>
       </c>
       <c r="F58" s="8" t="n">
-        <v>0.7476</v>
+        <v>0.2101</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>Market Sector    + Aerospace   + Air Transport   + MRO   + Defense   + Space   + Business Aviation  Markets [...] Already a member of AWIN or subscribe to Aerospace Daily &amp; Defense Report through your company? Loginwith your existing email and password.  Not a member?  Learn how you can access the market intelligence and data you need to stay abreast of what's happening in the aerospace and defense community.  |  |  |  --- | | Login | Learn How |  ## Related Content  Debrief: Hexcel Doubles Down...</t>
+          <t>By Charles Alcock • Managing Editor  February 4, 2026  ## More In Aircraft  ## Support for the M-346F in Indonesia Gathers Momentum  ### The Indonesian MoD is now discussing a wide-ranging support solution  Aircraft  ## IAI Shows Off Special-mission Gulfstream G600  ### The Ellyon is a multirole AEW/ISR/EA platform  Aircraft  ## Canada’s Fighter Debate Reopens Door for Gripen  ### Targeted rate of 36 units a year dependant on increased industrial collaboration  Aircraft  ## HAL and UAC Plot Indi...</t>
         </is>
       </c>
     </row>
@@ -3081,30 +2818,30 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Indonesia, Philippines boost maritime surveillance with twin-turboprops - FlightGlobal</t>
+          <t>Rolls-Royce CEO Says GCAP May Top Eurofighter - Aviation Week</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/fixed-wing/indonesia-philippines-boost-maritime-surveillance-with-twin-turboprops/166385.article</t>
+          <t>https://aviationweek.com/defense/aircraft-propulsion/rolls-royce-ceo-says-gcap-may-top-eurofighter</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Fri, 20 Feb 2026 05:04:54 GMT</t>
+          <t>Thu, 26 Feb 2026 11:38:41 GMT</t>
         </is>
       </c>
       <c r="F59" s="11" t="n">
-        <v>0.3805</v>
+        <v>0.17</v>
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>### India approves INR3.6 trillion arms package including Rafales, P-8Is    2026-02-13T03:31:00Z By Greg Waldron    India’s Defence Acquisition Council has approved INR3.6 trillion ($39.7 billion) in military purchases, including Dassault Aviation Rafale fighters under the Multi-Role Fighter Aircraft requirement and additional Boeing P-8I Neptune maritime patrol aircraft for the navy.  Analysis    ### Non-American defence firms gain as US policies reshape markets    2026-02-05T10:05:00Z By Ryan...</t>
+          <t>## Share  Robert Wall February 26, 2026  LONDON—Rolls-Royce CEO Tufan Erginbilgiç says the company’s involvement in the Global Combat Air Program could generate business that surpasses what the Eurofighter Typhoon has delivered for the engine-maker. “Rolls-Royce will hold a significant share in this program, which will potentially be...  Robert Wall  Robert Wall is Executive Editor for Defense and Space. Based in London, he directs a team of military and space journalists across the U.S., Europe...</t>
         </is>
       </c>
     </row>
@@ -3114,30 +2851,30 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>DARPA designates General Atomics LongShot prototype as X-68A - FlightGlobal</t>
+          <t>India to acquire more air defense systems and drones for modern warfare - Defense News</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/military-uavs/darpa-designates-general-atomics-longshot-prototype-as-x-68a/166348.article</t>
+          <t>https://www.defensenews.com/global/asia-pacific/2026/04/03/india-to-acquire-more-air-defense-systems-and-drones-for-modern-warfare/</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>defensenews.com</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 01:21:17 GMT</t>
+          <t>Fri, 03 Apr 2026 15:43:12 GMT</t>
         </is>
       </c>
       <c r="F60" s="8" t="n">
-        <v>0.0467</v>
+        <v>0.1313</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>Sometimes referred to as a “missile truck”, the concept envisions an uncrewed platform that can be launched from a crewed aircraft and travel onward independently to deploy weapon systems, while the crewed aircraft remains at a safe standoff distance.  The US Defense Advanced Research Projects Agency (DARPA) has been developing the concept since 2021 under the LongShot programme. Uncrewed aircraft manufacturer General Atomics Aeronautical Systems was awarded a contract at the time to begin desig...</t>
+          <t>A chunk of the new funding package will be directed towards acquiring 60 new multirole transport aircraft that will replace the country’s aging fleet. From high mountains to strategic islands that lie far away from the mainland, Indian troops are deployed across a varied geography. The likely contenders for these could be Brazil’s Embraer, US-based Lockheed Martin and Russia’s Ilyushin aircraft, according to media reports.  Experts say the recent budget approvals demonstrate that despite Russia’...</t>
         </is>
       </c>
     </row>
@@ -3147,30 +2884,30 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>MHI, Shield AI partner to test UAV autonomy - Janes</t>
+          <t>India’s MoD claims highest ever funding boost in Union Budget 2026-27 - Army Technology</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>https://www.janes.com/osint-insights/defence-news/air/mhi-shield-ai-partner-to-test-uav-autonomy</t>
+          <t>https://www.army-technology.com/news/india-defence-budget-2026-27/</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>janes.com</t>
+          <t>army-technology.com</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Fri, 20 Mar 2026 09:51:11 GMT</t>
+          <t>Wed, 04 Feb 2026 17:26:32 GMT</t>
         </is>
       </c>
       <c r="F61" s="11" t="n">
-        <v>0.02</v>
+        <v>0.1242</v>
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
-          <t>Read Article  Defence  ### Iran conflict 2026: A-10 and AH-64 aircraft conducting operations across Iran's southern flank  Read Article  ## See how Janes delivers verified defence intelligence for faster, safer decisions   The world's most complete foundational military data asset.  500,000+ analyst hours per year to keep data current.  Easy integration into high and low-side environments. [...] Subscribe to Janes  ## Discover how Janes can support your mission  ### Solutions for defence  Delive...</t>
+          <t>Defence services have also received an allocation of Rs9.75bn for an optical fibre cable network.  The focus on indigenous manufacturing continues under the ‘Aatmanirbhar Bharat’ or ‘self-reliant India’ initiative, with Rs1.39tn allotted for procurement from domestic defence industries in FY 2026–27.  Approximately three-quarters of the capital acquisition budget is reserved for Indian companies, including private sector entities.  The government will exempt basic customs duty on raw materials i...</t>
         </is>
       </c>
     </row>
@@ -3180,12 +2917,12 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Inside the PLA’s push for collaborative combat aircraft - FlightGlobal</t>
+          <t>France edges closer to Eurodrone exit with LPM revision - FlightGlobal</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/military-uavs/inside-the-plas-push-for-collaborative-combat-aircraft/166398.article</t>
+          <t>https://www.flightglobal.com/defence/2026/04/france-edges-closer-to-eurodrone-exit-with-lpm-revision/</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -3195,15 +2932,15 @@
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 03:53:39 GMT</t>
+          <t>Mon, 13 Apr 2026 15:33:29 GMT</t>
         </is>
       </c>
       <c r="F62" s="8" t="n">
-        <v>0.0153</v>
+        <v>0.1209</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>Announcements  FAQs  Topics A-Z  Terms and conditions  Cookie policy  Privacy policy  © ProMedia Group UK Ltd  Follow us on social media   Connect with us on Facebook  Connect with us on Twitter  Connect with us on Linked in  Email us  Connect with us on Youtube  Site powered by Webvision Cloud [...] Skip to navigation   Trending now  Singapore Airshow  2026 World Air Forces directory  FlightGlobal has a new podcast - listen now  Site name  Site name  Search our site  Close menu [...] Home  News...</t>
+          <t>Portugal has selected the Tecnam P-Mentor as its air force basic trainer, with seven examples of the piston-powered single to be supplied through an agreement with Spanish training provider World Aviation. CONTRACT UK MoD orders Skyhammer counter-drone missiles to guard against Iranian Shahed threat  Cambridge Aerospace is to start deliveries of its Skyhammer counter-drone interceptor within weeks, under a contract announced by the UK Ministry of Defence (MoD). FIXED-WING India to get depot for...</t>
         </is>
       </c>
     </row>
@@ -3213,30 +2950,30 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Seair Upgrades Cessna Caravan with Blackhawk XP140 Engine - Aviation International News</t>
+          <t>OGMA And Axiscades Partner To Strengthen India’s MRO Capabilities - Aviation Week Network</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>https://www.ainonline.com/aviation-news/air-transport/2026-01-22/blackhawk-upgrade-targets-faster-seaplane-operations</t>
+          <t>https://aviationweek.com/mro/ogma-axiscades-partner-strengthen-indias-mro-capabilities</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>ainonline.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Fri, 23 Jan 2026 14:19:29 GMT</t>
+          <t>Fri, 30 Jan 2026 15:31:27 GMT</t>
         </is>
       </c>
       <c r="F63" s="11" t="n">
-        <v>0.013</v>
+        <v>0.9992</v>
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>About  Our Writers  History  Contact Us  Advertise  Copyright ©2026AIN Media Group, Inc. All Rights Reserved.  Terms of Use | Privacy Policy | Cookie Policy | Content Policy | Add as a Preferred Source [...] ## Honeywell Reveals Possible $470M Flexjet Lawsuit Cost  ### Complaint was filed in 2023 and alleged breach of engine maintenance agreement  Engines  ## GE’s Latest Passport Engine Receives EASA Approval  ### Move clears the way for European certification of Global 8000  Engines  ## GE Aero...</t>
+          <t>Axiscades is establishing an integrated aerospace and defense manufacturing and MRO hub near Bengaluru International Airport. The facility will include dedicated aircraft hangars, engine shops, a welding center of excellence and production facilities along with systems integration and certification testing infrastructure. The facility will be designed to support both civil and defense aviation requirements, enabling India to perform complex maintenance, upgrades and certifications domestically r...</t>
         </is>
       </c>
     </row>
@@ -3246,30 +2983,26 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>MHI, Shield AI complete autonomous flight tests in Japan - FlightGlobal</t>
+          <t>Medium Transport Aircraft Programme Reflects India’s Push to Diversify Defence Imports</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/military-uavs/mhi-shield-ai-complete-autonomous-flight-tests-in-japan/166696.article</t>
+          <t>https://bharatshakti.in/medium-transport-aircraft-programme-reflects-indias-push-to-diversify-defence-imports/</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
-        </is>
-      </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t>Wed, 18 Mar 2026 12:14:40 GMT</t>
-        </is>
-      </c>
+          <t>bharatshakti.in</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr"/>
       <c r="F64" s="8" t="n">
-        <v>0.0062</v>
+        <v>0.6597</v>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>2026-02-26T18:50:00Z By Ryan Finnerty    Lockheed Martin has begun producing new F-22 external fuel tanks that it says extend the air superiority fighter’s range but do not hinder its stealth characteristics and aerodynamic performance.  ### More from Military UAVs   Analysis    ### New low-cost US attack drone offers strike range of over 400nm for under $55,000    2026-03-13T17:17:00Z By Ryan Finnerty    The Pentagon has disclosed specifications for its LUCAS one-way attack drone, a reverse-eng...</t>
+          <t>The Indian Air Force, which currently operates a mixed fleet of Russian, American, and European transport aircraft, is expected to issue the MTA RFP next month. The platform is intended to replace ageing medium-lift aircraft and streamline logistics capability, with a requirement in the 18–30 tonne payload class and an estimated fleet size of around 80 aircraft.  Beyond performance parameters, officials said the selection process will weigh lifecycle costs, industrial participation, and the abil...</t>
         </is>
       </c>
     </row>
@@ -3279,12 +3012,12 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Leonardo to demonstrate M-346 commanding two Baykar uncrewed fighters by mid-year - FlightGlobal</t>
+          <t>Embraer seeks expanded Indian supply chain role amid partnerships - FlightGlobal</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/defence/leonardo-to-demonstrate-m-346-commanding-two-baykar-uncrewed-fighters-by-mid-year/166638.article</t>
+          <t>https://www.flightglobal.com/aerospace/embraer-seeks-expanded-indian-supply-chain-role-amid-partnerships/166248.article</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
@@ -3294,15 +3027,15 @@
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 00:00:00 GMT</t>
+          <t>Mon, 09 Feb 2026 04:56:46 GMT</t>
         </is>
       </c>
       <c r="F65" s="11" t="n">
-        <v>0.0042</v>
+        <v>0.3455</v>
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>Privacy Notice: By signing up to the newsletter you consent to our Terms and Conditions and our  Privacy Policy . This site is protected by reCAPTCHA and the Google Privacy Policy and Terms of Service apply.  ## Topics   Europe  Fixed-wing  Military UAVs   Save article    Please Sign in to your account to use this feature  Advert  Marketplace Recommendations  Ads Powered By Volantis Digital Media  Become a FlightGlobal member today and enjoy these benefits [...] Skip to main content  Skip to nav...</t>
+          <t>Senior executives with the Brazilian airframer recently completed a visit to the South Asian nation with a focus on commercial and defence aerospace, according to Embraer.  Source: Greg Waldron/FlightGlobal  Embraer has a substantial presence in India, including three ERJ-145-based Netra AEW&amp;C aircraft  “We reaffirm our strong commitment to collaborating with India’s aerospace industry. Our focus is on advancing joint initiatives in defence and civil aviation, contributing to technological innov...</t>
         </is>
       </c>
     </row>
@@ -3312,12 +3045,12 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>United Aircraft agrees to supply Il-114-300s to Indian aerospace firm - FlightGlobal</t>
+          <t>Dassault targets Indian contract for blockbuster Rafale order by year-end - FlightGlobal</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/aerospace/united-aircraft-agrees-to-supply-il-114-300s-to-indian-aerospace-firm/166117.article</t>
+          <t>https://www.flightglobal.com/defence/dassault-targets-indian-contract-for-blockbuster-rafale-order-by-year-end/166522.article</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
@@ -3327,15 +3060,15 @@
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>Thu, 29 Jan 2026 10:47:08 GMT</t>
+          <t>Wed, 04 Mar 2026 17:26:15 GMT</t>
         </is>
       </c>
       <c r="F66" s="8" t="n">
-        <v>0.981</v>
+        <v>0.1151</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>Home  News    + Back to parent navigation item   + News   + Aerospace      - Back to parent navigation item     - Aerospace     - MRO     - Systems &amp; Interiors     - Helicopters     - Space     - Civil UAVs   + Air transport      - Back to parent navigation item     - Air transport     - Airframers     - Engines     - Programmes     - Orders &amp; Deliveries   + Safety   + Business aviation   + Region      - Back to parent navigation item     - Region     - Europe     - Africa     - North America...</t>
+          <t>+ - Helicopters     - Fixed-Wing     - Military UAVs     - 2026 World Air Forces directory   + US bombers strike deep into Iran as Epic Fury intensifies   + UK F-35Bs down Iranian drones in defensive action over Jordan   + Chinese intelligence company tracking US military assets during Iran operations  Flight International    + - Subscribe to Flight International     - Flight International Opinion     - 110 years of Flight     - Airbus at 50     - Honeywell: Shaping the Future     - CAE: Sky's n...</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3078,12 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Airbus Opens Bengaluru Tech Hub To Support Engineering, Maintenance - Aviation Week</t>
+          <t>France’s Onera Tests Active Flow Control For Stealthy UAS - Aviation Week</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/mro/aircraft-propulsion/airbus-opens-bengaluru-tech-hub-support-engineering-maintenance</t>
+          <t>https://aviationweek.com/defense/aircraft-propulsion/frances-onera-tests-active-flow-control-stealthy-uas</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
@@ -3360,15 +3093,15 @@
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Fri, 06 Mar 2026 19:59:16 GMT</t>
+          <t>Tue, 03 Mar 2026 23:27:06 GMT</t>
         </is>
       </c>
       <c r="F67" s="11" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.094</v>
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>Beyond engineering development, the Airbus India Technology Center is also expected to play a role in strengthening India’s aviation talent base, particularly in areas related to aircraft maintenance engineering and technical services. The OEM aims to use the center as a hub where Indian engineers and technical professionals can gain exposure to global aircraft programs, advanced maintenance technologies and complex engineering challenges. [...] Airbus has opened a new technology center in Benga...</t>
+          <t>## Share  Graham Warwick March 03, 2026  French aerospace research agency Onera has conducted wind tunnel tests of an active flow control device intended to increase the effectiveness of ailerons to reduce drag and improve stealth. The device is being developed under the Facelift project funded by the European Defense Agency. Testing was...  Graham Warwick  Graham leads Aviation Week's coverage of technology, focusing on engineering and technology across the aerospace industry, with a special fo...</t>
         </is>
       </c>
     </row>
@@ -3378,30 +3111,30 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>India and US maintain momentum in defense ties - Defense News</t>
+          <t>ITP Aero forecasts continued strong growth after ‘exceptional’ 2025 performance - FlightGlobal</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>https://www.defensenews.com/global/asia-pacific/2026/02/04/india-and-us-maintain-momentum-in-defense-ties/</t>
+          <t>https://www.flightglobal.com/aerospace/itp-aero-forecasts-continued-strong-growth-after-exceptional-2025-performance/166541.article</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>defensenews.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 11:58:00 GMT</t>
+          <t>Thu, 05 Mar 2026 17:36:32 GMT</t>
         </is>
       </c>
       <c r="F68" s="8" t="n">
-        <v>0.2173</v>
+        <v>0.0576</v>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>India is also in the final stages of negotiating a deal to co-produce General Electric’s F414 jet engine inthe country to power a more advanced fighter jet calledthe Tejas Mk2 as well as initial batches of a fifth-generation fighter jet it is developing.  Those deals represent a major milestone in the India-U.S. defense relationship according to Dinakar Peri, an analyst in the Security Studies program at Carnegie Foundation. [...] India’s most ambitious indigenous defense project is developing a...</t>
+          <t>## More from Dominic Perry   ## TAKE OFF project spools up as open-fan partners build towards 2029 flight tests  ## Sluggish supply chain continues to weigh on Dassault Falcon deliveries  ## Dassault targets Indian contract for blockbuster Rafale order by year-end  ## Topics   Aerospace  ### Related articles   News    ### TAKE OFF project spools up as open-fan partners build towards 2029 flight tests    2026-03-05T16:09:00Z By Dominic Perry    Work on a Safran Aircraft Engines-led project that w...</t>
         </is>
       </c>
     </row>
@@ -3411,30 +3144,30 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Airbus: India’s Fleet Boom Will Triple Demand For MRO Engineers And Capacity - Aviation Week Network</t>
+          <t>Saab plans 2027 unmanned demonstrator for Swedish fighter decision - FlightGlobal</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/mro/supply-chain/airbus-indias-fleet-boom-will-triple-demand-mro-engineers-capacity</t>
+          <t>https://www.flightglobal.com/fixed-wing/saab-plans-2027-unmanned-demonstrator-for-swedish-fighter-decision/166235.article</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>aviationweek.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Fri, 30 Jan 2026 18:09:30 GMT</t>
+          <t>Fri, 06 Feb 2026 04:03:02 GMT</t>
         </is>
       </c>
       <c r="F69" s="11" t="n">
-        <v>0.1975</v>
+        <v>0.0057</v>
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>+ Aerospace     - Aircraft &amp; Propulsion     - Connected Aerospace     - Emerging Technologies     - Manufacturing &amp; Supply Chain     - Advanced Air Mobility     - Sustainability   + Air Transport     - Aircraft &amp; Propulsion     - Interiors &amp; Connectivity     - Airports &amp; Networks     - Airlines &amp; Lessors     - Safety, Ops &amp; Regulation     - Maintenance &amp; Training     - Sustainability   + MRO     - Aircraft &amp; Propulsion     - Interiors &amp; Connectivity     - Emerging Technologies     - Supply Chain...</t>
+          <t>Home  News    + Back to parent navigation item   + News   + Aerospace      - Back to parent navigation item     - Aerospace     - MRO     - Systems &amp; Interiors     - Helicopters     - Space     - Civil UAVs   + Air transport      - Back to parent navigation item     - Air transport     - Airframers     - Engines     - Programmes     - Orders &amp; Deliveries   + Safety   + Business aviation   + Region      - Back to parent navigation item     - Region     - Europe     - Africa     - North America...</t>
         </is>
       </c>
     </row>
@@ -3444,30 +3177,30 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Defence, self-reliance, and budgetary priorities: Sectoral opportunities in a shifting strategic landscape - The Economic Times</t>
+          <t>Boeing Continuing Some ITEP Apache Work Despite Army Threat - Aviation Week Network</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/defence-self-reliance-and-budgetary-priorities-sectoral-opportunities-in-a-shifting-strategic-landscape/articleshow/127367486.cms</t>
+          <t>https://aviationweek.com/defense/aircraft-propulsion/boeing-continuing-some-itep-apache-work-despite-army-threat</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>m.economictimes.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>Sat, 24 Jan 2026 05:43:00 GMT</t>
+          <t>Thu, 05 Feb 2026 09:02:28 GMT</t>
         </is>
       </c>
       <c r="F70" s="8" t="n">
-        <v>0.1478</v>
+        <v>0.0036</v>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>India's defence modernisation is a multi-decade transformation aligned with the nation's Viksit Bharat 2047 vision. The government declared 2025 as the "Year of Reforms" for the defence sector, signaling accelerated policy initiatives, streamlined procurement, and enhanced private sector participation.      At HDFC Securities, we believe there is a high probability of the following measures being included in the upcoming budget: [...] Our house view is where we believe that the Atmanirbhar Bhara...</t>
+          <t>Brian Everstine  Brian Everstine is the Pentagon Editor for Aviation Week, based in Washington, D.C.   Boeing Defense and Space  Singapore Airshow 2026  Boeing AH-64 Apache  GE Aerospace  ## Related Content  Saab Eyes 2027 Flight Of Future Fighter Demonstrator  Airbus Breathes Easier On A400M Given Demand Signals  Airbus: Sharp Rise In Tanker Interest Amid MRTT+ Rollout  Airbus, Singapore Fully Certify A3R Capability On A330 MRTT  Saab Sees Potential Canada Production Line Serving Other Gripen B...</t>
         </is>
       </c>
     </row>
@@ -3477,30 +3210,26 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>AH-64 tests proximity-fused ammunition against drones - FlightGlobal</t>
+          <t>Defence Procurement Board clears 114 Rafale jets in biggest ever deal - The Economic Times</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/helicopters/ah-64-tests-proximity-fused-ammunition-against-drones/166339.article</t>
+          <t>https://m.economictimes.com/news/defence/defence-procurement-board-clears-114-rafale-jets-in-largest-ever-deal/articleshow/126580893.cms</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
-        </is>
-      </c>
-      <c r="E71" s="11" t="inlineStr">
-        <is>
-          <t>Tue, 17 Feb 2026 04:49:28 GMT</t>
-        </is>
-      </c>
+          <t>m.economictimes.com</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr"/>
       <c r="F71" s="11" t="n">
-        <v>0.0257</v>
+        <v>0.7594</v>
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>2026-02-12T09:16:00Z By Greg Waldron    The US Marine Corps will retire its VH-3D and VH-60N presidential helicopters by 2030, with HMX-1’s VH-92A fleet expanding to 16 aircraft as the Sikorsky type assumes full Marine One duties.  News    ### UK government continues talks with Leonardo over NMH as it pledges it will not allow AW149 offer to ‘time out’    2026-02-11T17:27:00Z By Dominic Perry    UK defence ministers have met with senior executives from Leonardo twice over the past fortnight as t...</t>
+          <t>AbcMedium  AbcLarge  Save  Print  Comment  Synopsis  India Rafale Jets News: India's Defence Procurement Board has approved the purchase of 114 more Rafale fighter jets. This significant deal, valued at approximately Rs 3.25 lakh crore, will involve France. A substantial portion of these aircraft will be manufactured in India, incorporating about 30% indigenous components. This move aims to boost domestic defence manufacturing capabilities. [...] India's Defence Procurement Board cleared the acq...</t>
         </is>
       </c>
     </row>
@@ -3510,30 +3239,30 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Swedish air force receives first upgraded RM12EP engine for Gripen C/D fleet - FlightGlobal</t>
+          <t>How self-reliant is India in missiles, drones and AI weapons? Expert breakdown before Republic Day parade - India TV News</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/defence/swedish-air-force-receives-first-upgraded-rm12ep-engine-for-gripen-c/d-fleet/166763.article</t>
+          <t>https://www.indiatvnews.com/news/india/how-self-reliant-is-india-in-missiles-drones-ai-weapons-expert-breakdown-before-republic-day-parade-2026-01-25-1027394</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>indiatvnews.com</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 11:40:21 GMT</t>
+          <t>Sun, 25 Jan 2026 08:40:29 GMT</t>
         </is>
       </c>
       <c r="F72" s="8" t="n">
-        <v>0.0208</v>
+        <v>0.0785</v>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>Performed at the company’s Trollhattan site, the work spans “improved turbine hardware and updated engine control software designed to increase engine thrust, extend operating time and reduce life‑cycle costs”, it says.  The Swedish air force operates almost 100 examples of the Gripen C/D, which aviation analytics company Cirium records as aged between 11 and 23 years. They are powered by the RM12 – a derivative of GE Aerospace’s F404 turbofan.  Source: Saab  The Gripen C/D’s upgraded RM12EP eng...</t>
+          <t>Home  Videos  India  Budget 2026  T20 World Cup  World  Sports  Entertainment  Tech  Photos  Lifestyle  Health  Business  Explainer  Advertisement  1. News 2. India 3. How self-reliant is India in missiles, drones and AI weapons? Expert breakdown before Republic Day parade  # How self-reliant is India in missiles, drones and AI weapons? Expert breakdown before Republic Day parade  ## Expert points to India's accelerating progress- ALH took 30 years, LCH halved to 15, and LCA Mk2 speeds ahead wit...</t>
         </is>
       </c>
     </row>
@@ -3543,30 +3272,30 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>ST Engineering Unveils Business Aviation Thrust Reverser Demonstrator - Aviation International News</t>
+          <t>Horizon Aircraft maintains momentum towards Cavorite X7 first flight with key supplier picks - FlightGlobal</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>https://www.ainonline.com/aviation-news/business-aviation/2026-02-01/st-engineering-unveils-business-aviation-thrust-reversal</t>
+          <t>https://www.flightglobal.com/aerospace/horizon-aircraft-maintains-momentum-towards-cavorite-x7-first-flight-with-key-supplier-picks/166273.article</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>ainonline.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 07:07:58 GMT</t>
+          <t>Tue, 10 Feb 2026 18:22:25 GMT</t>
         </is>
       </c>
       <c r="F73" s="11" t="n">
-        <v>0.0133</v>
+        <v>0.0359</v>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>Email  By Charlotte Bailey • Writer  February 2, 2026  ## In this article  ## ST Engineering  Company  ## More In Engines  ## Pratt’s Eagle Services Asia Engine MRO Leverages Automation  ### Robots cut time and man-hours for inspections and engine core and compressor stacking  Engines  ## GE Completes Hybrid-electric Engine Demonstrator Ground Test  ### Work is aimed at developing future narrowbody airliner powertrains  Engines  ## Billion-dollar Settlement Ends Honeywell, Flexjet Fight  ### Agr...</t>
+          <t>2026-02-10T09:08:00Z By David Kaminski-Morrow    Ryanair is to establish its own in-house engine repair facilities, and is assessing around five potential sites with a view to opening the first of two shops by the end of 2028. Chief executive Michael O’Leary detailed the plan during a Paris briefing on 10 February, as the carrier renewed ...  News    ### Embraer seeks expanded Indian supply chain role amid partnerships    2026-02-09T04:52:00Z By Greg Waldron    Embraer is pursuing an expanded ro...</t>
         </is>
       </c>
     </row>
@@ -3576,12 +3305,12 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Safran advances system testing ahead of 2027 ground trials of open-fan engine front module - FlightGlobal</t>
+          <t>P&amp;WC details hybridisation plan for PW127 engine that could power ATR Evo - FlightGlobal</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/engines/safran-advances-system-testing-ahead-of-2027-ground-trials-of-open-fan-engine-front-module/166736.article</t>
+          <t>https://www.flightglobal.com/engines/pandwc-details-hybridisation-plan-for-pw127-engine-that-could-power-atr-evo/166726.article</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
@@ -3591,15 +3320,15 @@
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Fri, 20 Mar 2026 15:43:48 GMT</t>
+          <t>Thu, 19 Mar 2026 20:54:18 GMT</t>
         </is>
       </c>
       <c r="F74" s="8" t="n">
-        <v>0.0073</v>
+        <v>0.0075</v>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>Skip to navigation   Trending now  Singapore Airshow  2026 World Air Forces directory  FlightGlobal has a new podcast - listen now  Site name  Site name  Search our site  Close menu [...] ### Hermeus receives experimental certification for Quarterhorse Mk 2.1    2026-03-19T18:38:00Z By Ryan Finnerty    US hypersonic aircraft developer Hermeus has secured experimental type certification from the Federal Aviation Administration for its Quarterhorse Mk 2.1, enabling the company to proceed with supe...</t>
+          <t>“All these together, plus the batteries, makes something which should be viable. [And] 2035, if we start now, we will be on time.”  Dominic Perry   Follow  Dominic Perry is Aerospace Editor, Europe contributing extensively to flightglobal.com. Although specialising in the coverage of the helicopter industry, he has written on most topics in aerospace – be they commercial, defence or business aviation. In addition, there has been an increasing focus on the decarbonisation of the industry and zero...</t>
         </is>
       </c>
     </row>
@@ -3609,12 +3338,12 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>GA-ASI, Calidus sign UAE co-production pact for MQ-9B, Gambit - FlightGlobal</t>
+          <t>BAE Systems expands UAS technology pact with US partner Survice Engineering - FlightGlobal</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/military-uavs/ga-asi-calidus-sign-uae-co-production-pact-for-mq-9b-gambit/166009.article</t>
+          <t>https://www.flightglobal.com/defence/bae-systems-expands-uas-technology-pact-with-us-partner-survice-engineering/166404.article</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
@@ -3624,7 +3353,7 @@
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Wed, 21 Jan 2026 04:50:39 GMT</t>
+          <t>Mon, 23 Feb 2026 16:52:39 GMT</t>
         </is>
       </c>
       <c r="F75" s="11" t="n">
@@ -3632,7 +3361,7 @@
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>Skip to navigation   Trending now  FlightGlobal has a new podcast - listen now  2026 World Air Forces directory  Dubai Airshow  Singapore Airshow  Site name  Site name  Search our site  Close menu [...] Home  News    + - Aerospace        MRO        Systems &amp; Interiors        Helicopters        Space        Civil UAVs     - Air transport        Airframers        Engines        Programmes        Orders &amp; Deliveries   + - Safety     - Business aviation     - Region        Europe        Africa...</t>
+          <t>2026-02-23T09:45:00Z By David Kaminski-Morrow    Joint liquidators of the Russian-linked leasing firm GTLK Europe have sold three Boeing 777-300ERs to MTU’s Amsterdam-based leasing company. The airframes are set to be broken up for parts and materials while the engines – GE Aerospace GE90 powerplants – are in “full-life condition” and will be leased out, liquidator ...  ### More from Defence   News    ### Airbus bids for central role in revitalised European defence market    2026-02-19T13:35:00Z...</t>
         </is>
       </c>
     </row>
@@ -3642,30 +3371,30 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>New 'MedTech Advance' Sourcing Directory Launches to Streamline Global Medical Device Manufacturing - The Manila Times</t>
+          <t>Pratt &amp; Whitney Faces GTF Balancing Act In Airbus Delivery Negotiation - Aviation Week Network</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>https://www.manilatimes.net/2026/01/27/tmt-newswire/pr-newswire/new-medtech-advance-sourcing-directory-launches-to-streamline-global-medical-device-manufacturing/2265627</t>
+          <t>https://aviationweek.com/aerospace/manufacturing-supply-chain/pratt-whitney-faces-gtf-balancing-act-airbus-delivery</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>manilatimes.net</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 01:16:14 GMT</t>
+          <t>Wed, 04 Feb 2026 08:28:51 GMT</t>
         </is>
       </c>
       <c r="F76" s="8" t="n">
-        <v>0.0036</v>
+        <v>0.0012</v>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>Tuesday, January 27, 2026    Today's Paper  New "MedTech Advance" Sourcing Directory Launches to Streamline Global Medical Device Manufacturing  Sign In  New user? Click Here  Subscribe   Sign In  New user? Click Here  OPINION  NEWS  REGIONS  WORLD  BUSINESS  SPORTS  ENTERTAINMENT  LIFESTYLE  THE SUNDAY TIMES  SPECIAL FEATURES  SPECIAL SECTIONS  TMT NEWSWIRE  Media OutReach Newswire  PR Newswire  GlobeNewswire  Plentisoft  FAST TIMES  LEGAL ADVICE  CAMPUS PRESS  VIDEOS  EXPATS &amp; DIPLOMATS  PHOTO...</t>
+          <t>Although Deurloo says the number of A320neo AOGs is now reduced by around 20% compared to its peak of more than 700, the situation: “will continue on for a couple years. We know that's not going away at the end of 2026 but I think a lot depends on our execution this year and where we end up next year as well. We feel confident by the end of this decade, we're going to be in more of a normalized state,” he adds.  Guy Norris  Guy is a Senior Editor for Aviation Week, covering technology and propul...</t>
         </is>
       </c>
     </row>
@@ -3675,30 +3404,30 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>MRO facility set to boost self-reliance in aircraft maintenance - The Times of India</t>
+          <t>Safran and H55 power up electrification pact with B23 agreement - FlightGlobal</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/lucknow/mro-facility-set-to-boost-self-reliance-in-aircraft-maintenance/amp_articleshow/129871824.cms</t>
+          <t>https://www.flightglobal.com/archive/2026/04/safran-and-h55-power-up-electrification-pact-with-b23-agreement/</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>timesofindia.indiatimes.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 01:09:00 GMT</t>
+          <t>Mon, 13 Apr 2026 10:42:08 GMT</t>
         </is>
       </c>
       <c r="F77" s="11" t="n">
-        <v>0.8103</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
-          <t>Lucknow: The state-of-the-art maintenance, repair and overhaul (MRO) hub, the foundation stone for which was laid by Prime Minister Narendra Modi at Noida International Airport on Saturday, is a step towards making Uttar Pradesh as well as the country self-reliant in the field of aircraft maintenance. "India currently depends heavily on foreign countries for aircraft maintenance. Around 85% of the country's aircraft are sent abroad for MRO, leading to significant outflow of foreign exchange," th...</t>
+          <t>It foresees the development of “certified electric propulsion solutions for general aviation”, targeting CS-23-category aircraft.  Safran Electrical &amp; Power in 2025 received European Union Aviation Safety Agency approval for its ENGINeUS 100 electric propulsion unit (EPU), while H55 earlier this year revealed an agreement with the regulator over the certification readiness of its energy storage system.  “ENGINeUS enables the development of both all-electric and hybrid aircraft, making it a key a...</t>
         </is>
       </c>
     </row>
@@ -3708,30 +3437,30 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Magnetic Boosts Tallinn MRO Capacity - Aviation Week Network</t>
+          <t>India approves $39 billion purchase of 114 Rafale jets ahead of Macron visit - AeroTime</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/mro/aircraft-propulsion/magnetic-boosts-tallinn-mro-capacity</t>
+          <t>https://www.aerotime.aero/articles/india-39-billion-purchase-114-rafale-fighter-jet</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>aviationweek.com</t>
+          <t>aerotime.aero</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>Fri, 23 Jan 2026 11:03:08 GMT</t>
+          <t>Thu, 12 Feb 2026 13:32:35 GMT</t>
         </is>
       </c>
       <c r="F78" s="8" t="n">
-        <v>0.375</v>
+        <v>0.3857</v>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>Saudi-U.S. MRO Training Partnership Takes Off In Tulsa  Adani Group Combines Air Works, Indamer For Major MRO Expansion</t>
+          <t># India approves $39 billion purchase of 114 Rafale jets ahead of Macron visit  ByIan Molyneaux  Edited ByAndy Murray  India has approved the $39 billion purchase of 114 Dassault Rafale fighter jets, in an effort to bolster the Indian Air Force’s (IAF) operational readiness and modernize its military fleet.  On February 12, 2026, the Defense Acquisition Council (DAC), chaired under the guidance of Defense Minister Rajnath Singh, backed the deal, along with the purchase of swathe of other militar...</t>
         </is>
       </c>
     </row>
@@ -3741,30 +3470,30 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>MRO Memo: India, U.S. Regulators And OEMs Seek Streamlined Cooperation - Aviation Week</t>
+          <t>HAL secures contract for six Dhruv coast guard helicopters - FlightGlobal</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/mro/safety-ops-regulation/mro-memo-india-us-regulators-oems-seek-streamlined-cooperation</t>
+          <t>https://www.flightglobal.com/helicopters/hal-secures-contract-for-six-dhruv-coast-guard-helicopters/166532.article</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>aviationweek.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Fri, 06 Mar 2026 21:05:44 GMT</t>
+          <t>Thu, 05 Mar 2026 08:06:01 GMT</t>
         </is>
       </c>
       <c r="F79" s="11" t="n">
-        <v>0.1755</v>
+        <v>0.3594</v>
       </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>The arrangement, announced March 5, has been established under the regulators’ Bilateral Aviation Safety Agreement and complements the existing Implementation Procedures for Airworthiness already in place between the two agencies. The new cooperation is designed to streamline certification processes and enhance transparency in the management of aircraft and engine approvals between India and the U.S.  A notable feature of the new framework is the inclusion of major aerospace manufacturers such a...</t>
+          <t>+ Southwest not ‘copying’ rival US airlines with assigned seating and baggage fees: CEO Jordan   + American expects profit jump in 2026 despite early weather-related setback   + Delta forecasts strong 2026 as demand for air travel rebounds   + Air Transat’s search for profitability continues into 2026  More from navigation items  Helicopters  # Hindustan Aeronautics wins Indian coast guard contract for six Dhruv Advanced Light Helicopters  By Greg Waldron2026-03-05T07:56:00+00:00  Hindustan Aero...</t>
         </is>
       </c>
     </row>
@@ -3774,30 +3503,30 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Pakistan, Venezuela &amp; now Iran: How China has become laughingstock of the global stage - The Times of India</t>
+          <t>Safran spools up hybridisation push ahead of summer Silvercrest tests - FlightGlobal</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/defence/international/china-has-become-the-laughingstock-of-the-international-community/articleshow/129560285.cms</t>
+          <t>https://www.flightglobal.com/engines/2026/03/safran-spools-up-hybridisation-push-ahead-of-summer-silvercrest-tests/</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>timesofindia.indiatimes.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>Sat, 14 Mar 2026 15:24:00 GMT</t>
+          <t>Thu, 26 Mar 2026 13:12:20 GMT</t>
         </is>
       </c>
       <c r="F80" s="8" t="n">
-        <v>0.1619</v>
+        <v>0.2074</v>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>under such conditions.Another possibility is that the air defence network itself was degraded early in the attack.Electronic warfare, cyber operations and stealth aircraft can disable radar systems and command nodes before the main strike begins. [...] ## Venezuela operation exposes radar vulnerabilities  The doubts surrounding Chinese defence technology deepened further during a dramatic American military operation in Venezuela.During the mission, US forces carried out a large-scale operation i...</t>
+          <t>Pratt &amp; Whitney Canada parent RTX has provided more details on the advanced hybrid-electric PW127 turboprop engine it is developing under an EU Clean Aviation project that could eventually go on to power ATR’s planned Evo aircraft. Fixed-Wing Hermeus receives experimental certification for Quarterhorse Mk 2.1  US hypersonic aircraft developer Hermeus has secured experimental type certification from the Federal Aviation Administration for its Quarterhorse Mk 2.1, enabling the company to proceed w...</t>
         </is>
       </c>
     </row>
@@ -3807,30 +3536,30 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>E-7 Wedgetail Radar Jet The Pentagon Tried To Cancel Gets Over $1B In New Defense Bill - The War Zone</t>
+          <t>RMC lays keel, starts construction of Finland's third and fourth Pohjanmaa-class corvettes - Janes</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>https://www.twz.com/air/e-7-wedgetail-radar-jet-the-pentagon-tried-to-cancel-gets-over-1b-in-new-defense-bill</t>
+          <t>https://www.janes.com/osint-insights/defence-news/sea/rmc-lays-keel-starts-construction-of-finlands-third-and-fourth-pohjanmaa-class-corvettes</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>twz.com</t>
+          <t>janes.com</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Wed, 21 Jan 2026 00:23:12 GMT</t>
+          <t>Thu, 29 Jan 2026 13:53:24 GMT</t>
         </is>
       </c>
       <c r="F81" s="11" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0445</v>
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t># E-7 Wedgetail Radar Jet The Pentagon Tried To Cancel Gets Over $1B In New Defense Bill  Lawmakers already shot down Pentagon plans to buy E-2 Hawkeyes instead of E-7s Wedgetails.  By Joseph Trevithick  Published  The TWZ Newsletter  Weekly insights and analysis on the latest developments in military technology, strategy, and foreign policy.  Terms of Service and Privacy Policy [...] “The agreement emphasizes the importance of the E-7 Wedgetail platform and the airborne early warning and battle...</t>
+          <t>### Solutions for defence  Delivering trusted intelligence to warfighters to protect national interests, support readiness, and deter aggression.  ### Solutions for the intelligence community  Providing mission users with faster access to quality data to pre-empt threats and protect national security.  ### Describe the operating environment  A trusted holistic view of threat, stability, and capability across the globe.  ### Inform decision making  Assured interconnected OSINT to deliver informed...</t>
         </is>
       </c>
     </row>
@@ -3840,30 +3569,30 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Design Flaws in B-21 Raider? China Claims Its Software Exposed Issues in U.S. $203B Stealth Bomber – Reality Check - EurAsian Times</t>
+          <t>GE Aerospace Reveals $300M Boost For Singapore Engine Repair Site - Aviation Week Network</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>https://www.eurasiantimes.com/design-flaws-in-b-21-raider-china/</t>
+          <t>https://aviationweek.com/mro/aircraft-propulsion/ge-aerospace-reveals-300m-boost-singapore-engine-repair-site</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>eurasiantimes.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 15:24:48 GMT</t>
+          <t>Tue, 03 Feb 2026 09:09:21 GMT</t>
         </is>
       </c>
       <c r="F82" s="8" t="n">
-        <v>0.6549</v>
+        <v>0.9941</v>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>“PADJ-X, which boasts full intellectual property rights, integrates five major disciplines: aerodynamics, propulsion, electromagnetics, infrared signature, and sonic boom. It enables comprehensive optimisation of aircraft aerodynamic configurations,” the Hong Kong-based South China Morning Post reported, quoting the paper.  Similarly, the team ran simulations on the US Navy’s X-47B stealth drone, which was cancelled in 2015 but remains classified, like the B-21.  The paper claimed that the PADJ-...</t>
+          <t>Running through 2029, the expansion is aimed at speeding up engine turnaround times and forging closer links with operators as fleets of GE- and CFM-powered aircraft continue to grow. The maintenance, repair and overhaul (MRO) initiative will build on GE’s Flight Deck lean operating model, the engine-maker says.  The expansion phase will add a new module repair capability for the CFM Leap-1A/B high-pressure turbine and a larger component portfolio to enhance regional support as the main service...</t>
         </is>
       </c>
     </row>
@@ -3873,30 +3602,30 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>India progresses ramjet booster testing for air-to-air missile - Janes</t>
+          <t>Stealth aircraft: the technology of staying hidden - ynetnews</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>https://www.janes.com/osint-insights/defence-news/defence/india-progresses-ramjet-booster-testing-for-air-to-air-missile</t>
+          <t>https://www.ynetnews.com/tech-and-digital/article/ryrthgltbx</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>janes.com</t>
+          <t>ynetnews.com</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 08:51:03 GMT</t>
+          <t>Wed, 04 Mar 2026 21:19:51 GMT</t>
         </is>
       </c>
       <c r="F83" s="11" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>The SFDR is intended to power India's domestically developed Astra Mk III (Gandiva) beyond-visual-range air-to-air missile (BVRAAM). According to information previously presented by DRDO, the Astra Mk III aims to have a maximum range of 340 km at an operating altitude of 65,600 ft. Models of the Astra Mk III previously displayed by DRDO reveal the missile's resemblance to the MBDA Meteor BVRAAM, with two asymmetric ramjet motor air intakes mounted below the body.  #### Go beyond the headlines —...</t>
+          <t>One of the strongest sources of radar reflections in jet aircraft is the engine air intakes and other internal cavities, which radar waves can enter and reflect repeatedly off internal surfaces. Exposed compressor blades are especially conspicuous on radar. To reduce these returns, designers may use fine metal meshes that block radio waves without significantly restricting airflow—similar to the mesh on the inside of a microwave-oven door, where the size and spacing of the holes keep microwaves...</t>
         </is>
       </c>
     </row>
@@ -3906,30 +3635,30 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Navy seeks new anti-radar missile compatible with F-18, F-35 aircraft - Defense News</t>
+          <t>India Seeks Role In FCAS Or GCAP Fighter Consortia - Aviation Week</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>https://www.defensenews.com/industry/techwatch/2026/02/19/navy-seeks-new-anti-radar-missile-compatible-with-f-18-f-35-aircraft/</t>
+          <t>https://aviationweek.com/defense/aircraft-propulsion/india-seeks-role-fcas-or-gcap-fighter-consortia</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>defensenews.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 15:28:45 GMT</t>
+          <t>Wed, 18 Mar 2026 21:44:41 GMT</t>
         </is>
       </c>
       <c r="F84" s="8" t="n">
-        <v>0.024</v>
+        <v>0.8568</v>
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>###### Featured Video  ###### Lifting more with lighter drones: DARPA’s challenge | Defense News Weekly Full Episode 2.17.26  ###### Decode Your College Aid Offer in 60 Seconds — Money Minute  ###### Do you owe taxes on your ‘Warrior Dividend’?  ###### Can ‘garage innovators’ transform military drone resupply? DARPA hopes so  ###### Trending Now  1. ###### Germany won’t build nukes but could flash French, UK weapons to deter foes, Merz says 2. ###### Pentagon official blesses Europe’s push to sp...</t>
+          <t>## Share  Steve Trimble March 18, 2026  India’s Defense Ministry is seeking to join one of the foreign government-industry consortia developing competing sixth-generation fighters, opening a parallel acquisition track to a more indigenous alternative, according to a government report tabled in parliament on March 18. The 152-p. report on...  Steve Trimble  Steve covers military aviation, missiles and space for the Aviation Week Network, based in Washington, DC.  ## Subscription Required  India S...</t>
         </is>
       </c>
     </row>
@@ -3939,30 +3668,30 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>How self-reliant is India in missiles, drones and AI weapons? Expert breakdown before Republic Day parade - India TV News</t>
+          <t>GE Aerospace unveils $1 billion investment to boost production - FlightGlobal</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/news/india/how-self-reliant-is-india-in-missiles-drones-ai-weapons-expert-breakdown-before-republic-day-parade-2026-01-25-1027394</t>
+          <t>https://www.flightglobal.com/engines/ge-aerospace-unveils-1-billion-investment-to-boost-production/166577.article</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>indiatvnews.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Sun, 25 Jan 2026 08:40:29 GMT</t>
+          <t>Mon, 09 Mar 2026 13:45:43 GMT</t>
         </is>
       </c>
       <c r="F85" s="11" t="n">
-        <v>0.0077</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>### Indigenous weapons that deter enemies  Narang highlights India's upward trajectory- from 30 years for Advanced Light Helicopter (ALH) to 15 for Light Combat Helicopter (LCH). Light Combat Aircraft (LCA) followed suit, with LCA-2 accelerating sans foreign hurdles. Land systems like ATAGS gun, Pinaka rockets, and unmanned systems shine. Echoing Dr APJ Abdul Kalam, he stresses original research over low-tech assembly- projects like TAPAS UAV, Naval LCA, Kaveri engine, and Rustom-1 hit 70-90 per...</t>
+          <t>The $1 billion will “help accelerate engine deliveries, ramp production of parts that safely extend time between maintenance shop visits, and strengthen defence production to keep pace with military demand”, GE says.  The company, based near Cincinnati, will divide the funding among facilities in 30 communities and in 17 US states.  Of the $1 billion, it plans to spend $200 million “to expand manufacturing capacity for Leap high-pressure turbine durability kits that will improve time-on-wing for...</t>
         </is>
       </c>
     </row>
@@ -3972,30 +3701,30 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>GA-ASI Pauses Flight Ops Following YFQ-42A CCA Test Incident &amp; Investigation Launch - Unmanned Systems Technology</t>
+          <t>TAKE OFF project spools up as open-fan partners build towards 2029 flight tests - FlightGlobal</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>https://www.unmannedsystemstechnology.com/2026/04/ga-asi-pauses-flight-ops-following-yfq-42a-cca-test-incident-investigation-launch/</t>
+          <t>https://www.flightglobal.com/engines/take-off-project-spools-up-as-open-fan-partners-build-towards-2029-flight-tests/166538.article</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>unmannedsystemstechnology.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>Wed, 08 Apr 2026 05:09:00 GMT</t>
+          <t>Thu, 05 Mar 2026 16:30:00 GMT</t>
         </is>
       </c>
       <c r="F86" s="8" t="n">
-        <v>0.005</v>
+        <v>0.3311</v>
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>Share this  Posted by Olivia Hannam Olivia is a Junior Editor and Copywriter at Unmanned Systems Technology. She graduated with First-Class Honours in History from the University of Exeter, where she developed a passion for research and clear communication. Since joining UST in 2025, Olivia’s focus lies in creating well-crafted content that highlights the latest innovations and technologies shaping the unmanned sector. Connect   E:  T:  LinkedIn  General Atomics Aeronautical Systems, Inc  Leadin...</t>
+          <t>Source: Safran  Open-fan architecture is being pursued by Safran-GE joint venture CFM International  Building on the preceding OFELIA project in Clean Aviation’s first phase, TAKE OFF will use the technologies matured through that effort to develop an open-fan engine capable of undertaking a flight-test campaign.  By the end of the project in December 2029, the overall open-fan engine design should have been raised to technology readiness level (TRL) 6, Clean Aviation project documents state.  “...</t>
         </is>
       </c>
     </row>
@@ -4005,30 +3734,30 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>India unveils ground-based directed energy weapon - Janes</t>
+          <t>GE Aerospace Boosts CFM56 Turbine Blade Manufacturing - Aviation Week</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>https://www.janes.com/osint-insights/defence-news/defence/india-unveils-ground-based-directed-energy-weapon</t>
+          <t>https://aviationweek.com/air-transport/aircraft-propulsion/ge-aerospace-boosts-cfm56-turbine-blade-manufacturing</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>janes.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Wed, 21 Jan 2026 11:21:39 GMT</t>
+          <t>Thu, 12 Mar 2026 16:55:36 GMT</t>
         </is>
       </c>
       <c r="F87" s="11" t="n">
-        <v>0.0042</v>
+        <v>0.1953</v>
       </c>
       <c r="G87" s="11" t="inlineStr">
         <is>
-          <t>Read Article  Weapons  ### IAV 2026: Ajax Nemo mortar carrier unveiled  Read Article  ## See how Janes delivers verified defence intelligence for faster, safer decisions   The world's most complete foundational military data asset.  500,000+ analyst hours per year to keep data current.  Easy integration into high and low-side environments. [...] “Our goal is to achieve a kill range of up to 5 km,” the project member added. “The plan is to conclude all testing by June 2026.”  According to informa...</t>
+          <t>Sean Broderick  Senior Air Transport &amp; Safety Editor Sean Broderick covers aviation safety, MRO, and the airline business from Aviation Week Network's Washington, D.C. office.   GE Aerospace  CFM International CFM56  CFM International Leap-X  ## Related Content  Flight Friday: The Engines Powering Asia-Pacific Carriers’ Narrowbodies  Safran Counts On Engine Lessor SES To Ease Leap Disk Durability Issue  Disk Durability Has Southwest Concerned Over CFM Leap Availability  GE Aerospace To Establish...</t>
         </is>
       </c>
     </row>
@@ -4038,30 +3767,30 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>MTU snaps UAV engine maker AeroDesignWorks - FlightGlobal</t>
+          <t>India showcases new hypersonic missile in military parade - Janes</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/archive/2026/04/mtu-snaps-uav-engine-maker-aerodesignworks/</t>
+          <t>https://www.janes.com/osint-insights/defence-news/weapons/india-showcases-new-hypersonic-missile-in-military-parade</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>janes.com</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Wed, 08 Apr 2026 14:07:50 GMT</t>
+          <t>Mon, 26 Jan 2026 10:41:55 GMT</t>
         </is>
       </c>
       <c r="F88" s="8" t="n">
-        <v>0.0019</v>
+        <v>0.1755</v>
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>#### Author: Dominic Perry  Dominic Perry is Aerospace Editor, Europe contributing extensively to flightglobal.com. Although specialising in the coverage of the helicopter industry, he has written on most topics in aerospace – be they commercial, defence or business aviation. In addition, there has been an increasing focus on the decarbonisation of the industry and zero-emission flight initiatives. He also helps to edit Flight International.  E-mail  ### Related posts  BAE Systems test fires APK...</t>
+          <t>skip to main content  Search Janes  # India showcases new hypersonic missile in military parade  By Jon Grevatt |  India's LR-AShM is pictured during the country's 77th Republic Day parade at Kartavya Path in New Delhi on 26 January. (Sajjad Hussain/AFP via Getty Images)  India's Defence Research and Development Organisation (DRDO) showcased its new Long Range Anti-Ship Hypersonic Missile (LR-AshM) in a military parade to mark the country's 77th Republic Day on 26 January.  The LR-AshM, which is...</t>
         </is>
       </c>
     </row>
@@ -4071,30 +3800,30 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>Capital goods: 4 stocks converting record orders into real profits - The Financial Express</t>
+          <t>Beyond Aero hails windtunnel success for BYA-1 business jet - FlightGlobal</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/market/stock-insights/capital-goods-4-stocks-converting-record-orders-into-real-profits/4118250/</t>
+          <t>https://www.flightglobal.com/business-aviation/beyond-aero-hails-windtunnel-success-for-bya-1-business-jet/165989.article</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>financialexpress.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Sun, 25 Jan 2026 00:00:00 GMT</t>
+          <t>Mon, 19 Jan 2026 00:00:00 GMT</t>
         </is>
       </c>
       <c r="F89" s="11" t="n">
-        <v>0.1766</v>
+        <v>0.1176</v>
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
-          <t>#1 Larsen &amp; Toubro: Massive Order Book vs. Execution Lag  Larsen &amp; Toubro (L&amp;T) is a multinational conglomerate which is primarily engaged in providing engineering, procurement and construction (EPC) solutions in key sectors such as infrastructure, hydrocarbon, power, process industries and defence, information technology, and financial services in domestic and international markets.  Larsen &amp; Toubro reported a steady Q2 FY26, with execution holding up across most businesses.  Consolidated reven...</t>
+          <t>Advert  “The results confirmed the robustness of Beyond Aero’s aerodynamic design choices,” it states. Such activity also reduces “residual aerodynamic uncertainty ahead of geometry freeze and subsequent development phases.”  Testing took place at the low-speed facility of the German-Dutch Wind Tunnels in Marknesse in the Netherlands using a one-eighth scale model of the BYA-1 at speeds up to 155kt (288 km/h).  Beyond Aero is now focused on completing the preliminary design review phase of the p...</t>
         </is>
       </c>
     </row>
@@ -4104,30 +3833,30 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>P&amp;WC details hybridisation plan for PW127 engine that could power ATR Evo - FlightGlobal</t>
+          <t>From Sindoor to Self-Reliance: The ₹7.85 Lakh Crore Blueprint for a Fortified India - Zee News</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/engines/pandwc-details-hybridisation-plan-for-pw127-engine-that-could-power-atr-evo/166726.article</t>
+          <t>https://zeenews.india.com/india/from-sindoor-to-self-reliance-the-7-85-lakh-crore-blueprint-for-a-fortified-india-3012805.html</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>zeenews.india.com</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 20:54:18 GMT</t>
+          <t>Sun, 01 Feb 2026 13:52:51 GMT</t>
         </is>
       </c>
       <c r="F90" s="8" t="n">
-        <v>0.0164</v>
+        <v>0.0834</v>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>2026-03-16T18:08:00Z By Dominic Perry    Collins Aerospace has begun initial tests of the integrated electric elements – including a pair of 1MW-class motors – that will be used to hybridise a Pratt &amp; Whitney PW1100G engine as part of an EU Clean Aviation-backed project.  News    ### GE Aerospace unveils $1 billion investment to boost production    2026-03-09T13:42:00Z By Jon Hemmerdinger    GE Aerospace will invest $1 billion this year to support suppliers and ramp production of commercial and...</t>
+          <t>Success depends on fast and smart spending, avoiding delays in projects, and ensuring private companies deliver on time.  In short, this is a strong, forward-looking defence budget. It gives the armed forces more power to protect the nation while pushing for self-reliance and jobs in defence manufacturing. As Rajnath Singh said, it is a "Yuva Shakti-driven Budget" that supports PM Modi's dream of a strong, self-reliant, and developed India.  Key Highlights:  Capital Acquisition: ₹1.85 lakh crore...</t>
         </is>
       </c>
     </row>
@@ -4137,30 +3866,30 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>Airbus closes on key milestones for A380 flying testbed as COMPANION project nears design freeze - FlightGlobal</t>
+          <t>Australia explores European weapons integration for Ghost Bat - Janes</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/engines/airbus-closes-on-key-milestones-for-a380-flying-testbed-as-companion-project-nears-design-freeze/166018.article</t>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/australia-explores-european-weapons-integration-for-ghost-bat</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>janes.com</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Wed, 21 Jan 2026 18:53:10 GMT</t>
+          <t>Wed, 25 Feb 2026 12:35:36 GMT</t>
         </is>
       </c>
       <c r="F91" s="11" t="n">
-        <v>0.0107</v>
+        <v>0.0432</v>
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>The superjumbo will also make its first flight post-modification with four Trent 900s installed as Airbus seeks to capture baseline performance data prior to embarking on the RISE tests.  “Then we will be able to compare, back to back, the demonstrator configuration versus the reference,” says Perrin Decroux.  Dominic Perry   Follow  Dominic Perry is Aerospace Editor, Europe contributing extensively to flightglobal.com. Although specialising in the coverage of the helicopter industry, he has wri...</t>
+          <t>#### Go beyond the headlines — with direct links to interconnected entities  Get full access to validated equipment, military capabilities, and market insights.  Subscribe to Janes  ## Discover how Janes can support your mission  ### Solutions for defence  Delivering trusted intelligence to warfighters to protect national interests, support readiness, and deter aggression.  ### Solutions for the intelligence community  Providing mission users with faster access to quality data to pre-empt threat...</t>
         </is>
       </c>
     </row>
@@ -4170,30 +3899,30 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Sonair to debut ultrasonic 3D sensor at Modex event - Robotics &amp; Automation News</t>
+          <t>Pratt &amp; Whitney’s GTF deliveries increased 6% in 2025, while recall recovery progresses - FlightGlobal</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>https://roboticsandautomationnews.com/2026/03/26/sonair-to-debut-ultrasonic-3d-sensor-at-modex-event/100148/</t>
+          <t>https://www.flightglobal.com/engines/pratt-and-whitneys-gtf-deliveries-increased-6-in-2025-while-recall-recovery-progresses/166092.article</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>roboticsandautomationnews.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 08:41:47 GMT</t>
+          <t>Wed, 28 Jan 2026 13:58:25 GMT</t>
         </is>
       </c>
       <c r="F92" s="8" t="n">
-        <v>0.0058</v>
+        <v>0.043</v>
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>Key technical advantages include:   Full 180° x 180° field of view: Provides total spatial awareness to eliminate blind spots.  Enhanced operational uptime: By detecting obstacles at all heights and reducing “false positives” from environmental factors, the sensor minimizes unnecessary stops.  Safe human-robot interaction: Designed specifically for dynamic environments where humans and autonomous mobile robots (AMRs) must share space closely and safely.  Privacy-first operation in secure environ...</t>
+          <t>Calio says P&amp;W is also making progress introducing product updates. Production has started for the GTF Advantage, an improved PW1100G variant P&amp;W says will be more durable and provide more thrust. That engine should enter service this year, Calio says.  Also in 2026, P&amp;W expects to achieve certification and begin installing its “Hot Section Plus” upgrade package into current-generation PW1100Gs. That retrofit involves equipping engines with 35 new components that are otherwise unique to the GTF...</t>
         </is>
       </c>
     </row>
@@ -4203,30 +3932,30 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>SNC, Specter Detail Low-Cost Plasma Ramjet Missile Plan - Aviation Week</t>
+          <t>First production KF-21 rolled out - Janes</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/defense/missile-defense-weapons/snc-specter-detail-low-cost-plasma-ramjet-missile-plan</t>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/first-production-kf-21-rolled-out</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>aviationweek.com</t>
+          <t>janes.com</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 01:08:42 GMT</t>
+          <t>Wed, 25 Mar 2026 13:51:16 GMT</t>
         </is>
       </c>
       <c r="F93" s="11" t="n">
-        <v>0.0029</v>
+        <v>0.018</v>
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>+ Services     - Advertising     - Marketing Services     - Fleet, Data &amp; APIs     - Research &amp; Consulting     - Network and Route Planning     - Marketplace  Store    + ## Market Sector [...] Market Sector    + Aerospace   + Air Transport   + MRO   + Defense   + Space   + Business Aviation  Markets [...] Jon Piatt, executive vice president of SNC’s intelligence, surveillance and reconnaissance (ISR), Aviation and Security business area, adds that the collaboration targets low cost and mass prod...</t>
+          <t>skip to main content  Search Janes  # First production KF-21 rolled out  By Akhil Kadidal |  KAI's twin-seat KF-21 prototype No 06 was built to train pilots and test weapons and avionics. The first production KF-21 is also a two-seat variant. The aircraft will almost certainly be used to train additional RoKAF personnel to operate the platform. (DAPA)  Korea Aerospace Industries (KAI) has rolled out the first production KF-21 ‘Boramae' 4.5-generation fighter aircraft, which will enter service wi...</t>
         </is>
       </c>
     </row>
@@ -4236,30 +3965,30 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>GKN Aerospace delivers first upgraded Gripen engine to Swedish Armed Forces - Janes</t>
+          <t>Dash 8 excursion at Nairobi Wilson spurs politician to demand airport’s closure - FlightGlobal</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>https://www.janes.com/osint-insights/defence-news/defence/gkn-aerospace-delivers-first-upgraded-gripen-engine-to-swedish-armed-forces</t>
+          <t>https://www.flightglobal.com/safety/dash-8-excursion-at-nairobi-wilson-spurs-politician-to-demand-airports-closure/166739.article</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>janes.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 14:21:14 GMT</t>
+          <t>Sun, 22 Mar 2026 17:05:03 GMT</t>
         </is>
       </c>
       <c r="F94" s="8" t="n">
-        <v>0.002</v>
+        <v>0.0114</v>
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>### More news articles  Defence  ### GKN Aerospace delivers first upgraded Gripen engine to Swedish Armed Forces  Read Article  Defence  ### First production KF-21 rolled out  Read Article  Defence  ### US officials tout USS Nimitz presence in Southern Command for Western Hemisphere defence  Read Article  ## See how Janes delivers verified defence intelligence for faster, safer decisions   The world's most complete foundational military data asset.  500,000+ analyst hours per year to keep data c...</t>
+          <t>2026-03-20T15:30:00Z By Dominic Perry    Safran Aircraft Engines is ramping up system-level testing for a future open-fan engine as it builds towards full-scale ground tests next year of the front module – including the 4m (13ft)-diameter fan – and ultimately flight tests of a complete powerplant in 2029.  News    ### P&amp;WC details hybridisation plan for PW127 engine that could power ATR Evo    2026-03-19T20:52:00Z By Dominic Perry    Pratt &amp; Whitney Canada parent RTX has provided more details on...</t>
         </is>
       </c>
     </row>
@@ -4269,30 +3998,30 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>Liebherr-Aerospace Plans Lindenberg MRO Expansion - Aviation Week</t>
+          <t>Safran advances system testing ahead of 2027 ground trials of open-fan engine front module - FlightGlobal</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/mro/aircraft-propulsion/liebherr-aerospace-plans-lindenberg-mro-expansion</t>
+          <t>https://www.flightglobal.com/engines/safran-advances-system-testing-ahead-of-2027-ground-trials-of-open-fan-engine-front-module/166736.article</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>aviationweek.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Fri, 27 Mar 2026 11:55:19 GMT</t>
+          <t>Fri, 20 Mar 2026 15:43:48 GMT</t>
         </is>
       </c>
       <c r="F95" s="11" t="n">
-        <v>0.5747</v>
+        <v>0.0103</v>
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
-          <t>The company said the expansion is primarily driven by rising MRO demand across the aviation industry and is tied to factors such as maturing aircraft fleets, increased demand for aftermarket services and more complex, advanced aircraft systems requiring specialized services.  Among the cited programs is the Airbus A350, for which Liebherr provides critical systems, including the slat actuation and nose landing gear—the largest produced at Lindenberg. As the global A350 fleet ages, demand for ser...</t>
+          <t>### Hermeus receives experimental certification for Quarterhorse Mk 2.1    2026-03-19T18:38:00Z By Ryan Finnerty    US hypersonic aircraft developer Hermeus has secured experimental type certification from the Federal Aviation Administration for its Quarterhorse Mk 2.1, enabling the company to proceed with supersonic flight testing at Spaceport America in New Mexico.  Analysis    ### Airbus Helicopters sees return of oil and gas demand for H225 amid continued military market momentum    2026-03-...</t>
         </is>
       </c>
     </row>
@@ -4302,30 +4031,30 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Indian Council Advances Rafale, P-8I, Airship Deals - Aviation Week</t>
+          <t>Boeing plans for rate production of operational MQ-28s within two years - FlightGlobal</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/defense/budget-policy-operations/indian-council-advances-rafale-p-8i-airship-deals</t>
+          <t>https://www.flightglobal.com/military-uavs/boeing-plans-for-rate-production-of-operational-mq-28s-within-two-years/166173.article</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>aviationweek.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 09:29:48 GMT</t>
+          <t>Tue, 03 Feb 2026 04:32:10 GMT</t>
         </is>
       </c>
       <c r="F96" s="8" t="n">
-        <v>0.5293</v>
+        <v>0.0094</v>
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>Market Sector    + Aerospace   + Air Transport   + MRO   + Defense   + Space   + Business Aviation  Markets [...] + Services     - Advertising     - Marketing Services     - Fleet, Data &amp; APIs     - Research &amp; Consulting     - Network and Route Planning     - Marketplace  Store    + ## Market Sector [...] “The procurement of the MRFA will enhance the capability to establish air supremacy in all combat scenarios and significantly enhance the Air Force’s deterrence capability with long-range offen...</t>
+          <t>Skip to navigation   Trending now  Singapore Airshow  2026 World Air Forces directory  FlightGlobal has a new podcast - listen now  Site name  Site name  Search our site  Close menu [...] ### Bird Aerosystems wins Asia-Pacific helicopter self-defence contract    2026-02-03T02:07:00Z By Greg Waldron    Israeli defence specialist Bird Aerosystems has secured a multi-million dollar contract to supply directed infrared countermeasures equipment for a helicopter upgrade programme in the Asia-Pacific...</t>
         </is>
       </c>
     </row>
@@ -4335,30 +4064,30 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>India moves to build 1,000-kg bombs as IAF pushes for self-reliance in heavy munitions - Firstpost</t>
+          <t>BAE Systems reports record £84 billion backlog on defence demand - FlightGlobal</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>https://www.firstpost.com/india/india-moves-to-build-1000-kg-bombs-as-iaf-pushes-for-self-reliance-in-heavy-munitions-ws-e-13996599.html</t>
+          <t>https://www.flightglobal.com/fixed-wing/bae-systems-reports-record-84-billion-backlog-on-defence-demand/166369.article</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>firstpost.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>Sat, 04 Apr 2026 13:23:37 GMT</t>
+          <t>Thu, 19 Feb 2026 08:29:03 GMT</t>
         </is>
       </c>
       <c r="F97" s="11" t="n">
-        <v>0.03</v>
+        <v>0.9847</v>
       </c>
       <c r="G97" s="11" t="inlineStr">
         <is>
-          <t>#### Iran Israel War Live News: Iran deploys new air defence system to counter US jets; vows 'full' control over airspace  #### Hide, move, survive: How US fighter pilots are trained to avoid capture in enemy territory  #### Fide Candidates 2026 Chess Round 6 LIVE Updates: Praggnanandhaa showing early aggression against Nakamura  #### War meant to break Iran risks handing it control over global energy chokepoints  advertisement  ### Top Shows  Enjoying the news?  Get the latest stories delivered...</t>
+          <t>2026-02-19T02:32:00Z By Ryan Finnerty    Uruguay has taken delivery of the first two of six Embraer A-29 Super Tucano light attack turboprops ordered to replace its ageing fleet of Cessna A-37 Dragonfly jets, which average over 43 years in service.  News    ### India approves INR3.6 trillion arms package including Rafales, P-8Is    2026-02-13T03:31:00Z By Greg Waldron    India’s Defence Acquisition Council has approved INR3.6 trillion ($39.7 billion) in military purchases, including Dassault Avi...</t>
         </is>
       </c>
     </row>
@@ -4368,30 +4097,30 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Eurofighter, NETMA formally launch Aerodynamic Modification Kit - Janes</t>
+          <t>India Targets 50% Local Supply Chain For Next Rafales - Aviation Week</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>https://www.janes.com/osint-insights/defence-news/defence/eurofighter-netma-formally-launch-aerodynamic-modification-kit</t>
+          <t>https://aviationweek.com/defense/supply-chain/india-targets-50-local-supply-chain-next-rafales</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>janes.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 14:10:04 GMT</t>
+          <t>Fri, 13 Feb 2026 20:43:21 GMT</t>
         </is>
       </c>
       <c r="F98" s="8" t="n">
-        <v>0.0278</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>Read Article  Defence  ### UK in ‘advanced' talks to sell remaining surplus Hercules airlifters  Read Article  ## See how Janes delivers verified defence intelligence for faster, safer decisions   The world's most complete foundational military data asset.  500,000+ analyst hours per year to keep data current.  Easy integration into high and low-side environments. [...] ## Discover how Janes can support your mission  ### Solutions for defence  Delivering trusted intelligence to warfighters to pr...</t>
+          <t>Already a member of AWIN or subscribe to Aerospace Daily &amp; Defense Report through your company? Loginwith your existing email and password.  Not a member?  Learn how you can access the market intelligence and data you need to stay abreast of what's happening in the aerospace and defense community.  |  |  |  --- | | Login | Learn How |  ## Related Content  Debrief: Hexcel Doubles Down On Defense And Space  Hexcel To Focus On Defense, Space Growth, CEO Gentile Says  Hexcel Upbeat On Wide-Ranging D...</t>
         </is>
       </c>
     </row>
@@ -4401,30 +4130,30 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>US Air Force tests new, rapidly developed cruise missile - Defense News</t>
+          <t>Leonardo targets fresh contract opportunities with Eurofighter and M-346 platforms - FlightGlobal</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>https://www.defensenews.com/air/2026/02/04/us-air-force-tests-new-rapidly-developed-cruise-missile/</t>
+          <t>https://www.flightglobal.com/defence/leonardo-targets-fresh-contract-opportunities-with-eurofighter-and-m-346-platforms/166326.article</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>defensenews.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 21:42:09 GMT</t>
+          <t>Fri, 13 Feb 2026 17:37:14 GMT</t>
         </is>
       </c>
       <c r="F99" s="11" t="n">
-        <v>0.0254</v>
+        <v>0.3028</v>
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
-          <t>###### Trending Now  1. ###### Russian cargo plane arrives in Cuba, echoing frantic Caracas buildup 2. ###### Staccato debuts new handgun, and firearms makers show off short-barreled rifles at SHOT Show 2026 3. ###### Ukraine’s Gripen jets likely to come with long-reach Meteor missiles 4. ###### Pentagon taps 25 firms for small, cheap attack drone competition 5. ###### ‘Madness’: Italy’s Crosetto slams British secrecy on GCAP fighter jet [...] ###### In a training first, an Army National Guardsm...</t>
+          <t>+ Southwest not ‘copying’ rival US airlines with assigned seating and baggage fees: CEO Jordan   + American expects profit jump in 2026 despite early weather-related setback   + Delta forecasts strong 2026 as demand for air travel rebounds   + Air Transat’s search for profitability continues into 2026  More from navigation items  Defence  # Leonardo targets fresh contract opportunities with Eurofighter and M-346 platforms  By Craig Hoyle2026-02-13T17:25:00+00:00  With campaigns under way in Bang...</t>
         </is>
       </c>
     </row>
@@ -4434,30 +4163,30 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Pratt &amp; Whitney wins follow-on AGM-190A engine contract - FlightGlobal</t>
+          <t>GKN Delivers First Upgraded RM12 Engine For Swedish Gripen Fighters - Aviation Week</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/fixed-wing/pratt-and-whitney-wins-follow-on-agm-190a-engine-contract/166606.article</t>
+          <t>https://aviationweek.com/defense/aircraft-propulsion/gkn-delivers-first-upgraded-rm12-engine-swedish-gripen-fighters</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar 2026 00:00:00 GMT</t>
+          <t>Tue, 24 Mar 2026 17:39:39 GMT</t>
         </is>
       </c>
       <c r="F100" s="8" t="n">
-        <v>0.012</v>
+        <v>0.0315</v>
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>The TJ150 is a one-stage turbojet generally for use in missiles and drones.  “Meeting today’s mission demands requires speed and reliable performance, and the TJ150 engine delivers on both,” says Jessica Villardi, vice president of Fighter and Mobility Programs at Pratt &amp; Whitney.  “The engine’s performance and availability make it an ideal fit for effectors, as it provides consistent thrust and supports seamless vehicle integration.”  weekly  ## Sign-up to the Defence Briefing  Dedicated weekly...</t>
+          <t>- Aerospace     - Air Transport     - MRO     - Defense     - Space     - Business Aviation   + Type View All Products     - Intelligence Bundles         AWIN - Premium        AWIN - Aerospace and Defense        AWIN - Business Aviation        AWIN - Commercial Aviation     - Market Briefings         Aerospace Daily &amp; Defense Report        Aviation Daily        SpeedNews        Business Aviation &amp; AAM Report     - Directories         Air Charter Guide        Aviation Week Marketplace        Rout...</t>
         </is>
       </c>
     </row>
@@ -4467,30 +4196,30 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>UK opts for efficiency and battlefield commonality over power in AW149 engine selection - Janes</t>
+          <t>Indonesia could obtain fifth KF-21 prototype - FlightGlobal</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>https://www.janes.com/osint-insights/defence-news/defence/uk-opts-for-efficiency-and-battlefield-commonality-over-power-in-aw149-engine-selection</t>
+          <t>https://www.flightglobal.com/fixed-wing/2026/04/indonesia-could-obtain-fifth-kf-21-prototype/</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>janes.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 22:38:11 GMT</t>
+          <t>Wed, 08 Apr 2026 06:33:37 GMT</t>
         </is>
       </c>
       <c r="F101" s="11" t="n">
-        <v>0.0043</v>
+        <v>0.0288</v>
       </c>
       <c r="G101" s="11" t="inlineStr">
         <is>
-          <t>### More news articles  Defence  ### UK opts for efficiency and battlefield commonality over power in AW149 engine selection  Read Article  Defence  ### GKN Aerospace delivers first upgraded Gripen engine to Swedish Armed Forces  Read Article  Defence  ### First production KF-21 rolled out  Read Article  ## See how Janes delivers verified defence intelligence for faster, safer decisions   The world's most complete foundational military data asset.  500,000+ analyst hours per year to keep data cu...</t>
+          <t>Menu  search  Trending now:  Fixed-Wing  # Indonesia could obtain fifth KF-21 prototype  By Greg Waldron |  Indonesia could receive a Korea Aerospace Industries KF-21 prototype, although a firm commitment from Jakarta for production examples has yet to emerge.  As the KF-21 development programme winds down pending service entry in late 2006, Jakarta stands to obtain the fifth prototype in the six-aircraft test fleet, according to South Korean media reports, citing a lawmaker.  The reports come s...</t>
         </is>
       </c>
     </row>
@@ -4500,30 +4229,30 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>India to acquire more air defense systems and drones for modern warfare - Defense News</t>
+          <t>Dassault Gears Up For Rafale Output Uptick, Indian Production - Aviation Week</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>https://www.defensenews.com/global/asia-pacific/2026/04/03/india-to-acquire-more-air-defense-systems-and-drones-for-modern-warfare/</t>
+          <t>https://aviationweek.com/defense/aircraft-propulsion/dassault-gears-rafale-output-uptick-indian-production</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>defensenews.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Fri, 03 Apr 2026 15:43:12 GMT</t>
+          <t>Wed, 04 Mar 2026 18:07:57 GMT</t>
         </is>
       </c>
       <c r="F102" s="8" t="n">
-        <v>0.3168</v>
+        <v>0.0272</v>
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>By Anjana Pasricha  The defense ministry said in a statement that the approvals are intended to strengthen both offensive and defensive air capabilities. “The S-400 system will counter enemy long-range air vectors targeting vital areas, while remotely piloted strike aircraft will enable offensive counter and coordinated air operations, along with intelligence, surveillance and reconnaissance roles.”  India recently signed a $47 million contract for procurement of the Tunguska air defense missile...</t>
+          <t>- Aerospace     - Air Transport     - MRO     - Defense     - Space     - Business Aviation   + Type View All Products     - Intelligence Bundles         AWIN - Premium        AWIN - Aerospace and Defense        AWIN - Business Aviation        AWIN - Commercial Aviation     - Market Briefings         Aerospace Daily &amp; Defense Report        Aviation Daily        SpeedNews        The Weekly of Business Aviation     - Directories         Air Charter Guide        Aviation Week Marketplace        Rou...</t>
         </is>
       </c>
     </row>
@@ -4533,30 +4262,30 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>US To Develop Next Generation Stealth Fighter Jet: What To Know - Newsweek</t>
+          <t>UK looks to demonstrate ‘generation after next' radar technologies - Janes</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>https://www.newsweek.com/us-develop-next-generation-stealth-fighter-what-know-11570702</t>
+          <t>https://www.janes.com/osint-insights/defence-news/c4isr/uk-looks-to-demonstrate-generation-after-next-radar-technologies</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>newsweek.com</t>
+          <t>janes.com</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>Tue, 24 Feb 2026 15:17:00 GMT</t>
+          <t>Mon, 19 Jan 2026 06:54:28 GMT</t>
         </is>
       </c>
       <c r="F103" s="11" t="n">
-        <v>0.0418</v>
+        <v>0.0223</v>
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>...  No sixth-generation jets are currently in use. The most sophisticated fighter jets available for militaries at the moment are fifth-generation aircraft, like the U.S.' F-35 and F-22. The new wave of aircraft will be the next major leap forward for fighter jets, and help determine which militaries have the most formidable air forces.  U.S. officials had prioritized the USAF's quest for sixth-generation capabilities over the Navy's F/A-XX carrier-based program, arguing defense companies would...</t>
+          <t>Known as the Hyperion Core Demonstrator, the programme is being funded by the UK Missile Defence Centre (MDC) using money allocated through the MoD's chief scientific adviser. A prototype array, exploiting technology previously developed by BAE Systems' Project Theia, was shown to UK media for the first time in the fourth quarter of 2025. [...] Read Article  ## See how Janes delivers verified defence intelligence for faster, safer decisions   The world's most complete foundational military data...</t>
         </is>
       </c>
     </row>
@@ -4566,30 +4295,30 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>India’s Export Momentum Strengthens on Rising Services, Strategic Manufacturing, and Policy Reforms - A2Z Taxcorp LLP</t>
+          <t>GA-ASI, Calidus sign UAE co-production pact for MQ-9B, Gambit - FlightGlobal</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>https://a2ztaxcorp.net/indias-export-momentum-strengthens-on-rising-services-strategic-manufacturing-and-policy-reforms/</t>
+          <t>https://www.flightglobal.com/military-uavs/ga-asi-calidus-sign-uae-co-production-pact-for-mq-9b-gambit/166009.article</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>a2ztaxcorp.net</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Tue, 03 Mar 2026 10:32:43 GMT</t>
+          <t>Wed, 21 Jan 2026 04:50:39 GMT</t>
         </is>
       </c>
       <c r="F104" s="8" t="n">
-        <v>0.0402</v>
+        <v>0.0177</v>
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>Development of the Uttar Pradesh Defence Industrial Corridor (UPDIC) and Tamil Nadu Defence Industrial Corridor (TNDIC), which together have attracted investments exceeding ₹9,145 crore, with 289 MoUs signed and potential investment opportunities worth ₹66,423 crore as of October 2025.  Strengthening defence innovation through DRDO-led initiatives, including a ₹500 crore corpus approved under the Technology Development Fund (TDF) for deep-tech and cutting-edge projects, along with Technology Tra...</t>
+          <t>### US Army awards $13m contract to AV for P550 drones    2025-12-09T20:06:00Z By Ryan Finnerty    The US Army has awarded uncrewed aircraft manufacturer AV a $13 million contract to supply P550 drones for training soldiers on aerial reconnaissance tactics under its Long Range Reconnaissance programme.  News    ### Boeing MQ-28A Ghost Bat destroys drone in air-to-air weapons test    2025-12-09T03:38:00Z By Greg Waldron    Australia’s Boeing MQ-28A Ghost Bat has successfully destroyed a drone tar...</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4328,12 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>US Navy seeks advanced anti-radiation missile for contested environments - FlightGlobal</t>
+          <t>Leonardo to demonstrate M-346 commanding two Baykar uncrewed fighters by mid-year - FlightGlobal</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/fixed-wing/us-navy-seeks-advanced-anti-radiation-missile-for-contested-environments/166380.article</t>
+          <t>https://www.flightglobal.com/defence/leonardo-to-demonstrate-m-346-commanding-two-baykar-uncrewed-fighters-by-mid-year/166638.article</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
@@ -4614,15 +4343,15 @@
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>Fri, 20 Feb 2026 04:33:44 GMT</t>
+          <t>Thu, 12 Mar 2026 00:00:00 GMT</t>
         </is>
       </c>
       <c r="F105" s="11" t="n">
-        <v>0.029</v>
+        <v>0.0042</v>
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
-          <t>The solicitation comes as the USN transitions from Northrop Grumman’s AGM-88E Advanced Anti-Radiation Guided Missile (AARGM) to the higher-performance AGM-88G AARGM-Extended Range, which doubles the effective range and features a “straked” airframe designed for internal carriage on the F-35C.  Following a successful January 2026 live-fire test in a GPS-denied environment, the AARGM-ER is set for Initial Operational Capability (IOC) later this year, providing USN aircraft with an enhanced ability...</t>
+          <t>Privacy Notice: By signing up to the newsletter you consent to our Terms and Conditions and our  Privacy Policy . This site is protected by reCAPTCHA and the Google Privacy Policy and Terms of Service apply.  ## Topics   Europe  Fixed-wing  Military UAVs   Save article    Please Sign in to your account to use this feature  Advert  Marketplace Recommendations  Ads Powered By Volantis Digital Media  Become a FlightGlobal member today and enjoy these benefits [...] Skip to main content  Skip to nav...</t>
         </is>
       </c>
     </row>
@@ -4632,30 +4361,30 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>New funding programme aims to strengthen Brazilian defence industry - Janes</t>
+          <t>United Aircraft agrees to supply Il-114-300s to Indian aerospace firm - FlightGlobal</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>https://www.janes.com/osint-insights/defence-news/defence/new-funding-programme-aims-to-strengthen-brazilian-defence-industry</t>
+          <t>https://www.flightglobal.com/aerospace/united-aircraft-agrees-to-supply-il-114-300s-to-indian-aerospace-firm/166117.article</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>janes.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 04:10:12 GMT</t>
+          <t>Thu, 29 Jan 2026 10:47:08 GMT</t>
         </is>
       </c>
       <c r="F106" s="8" t="n">
-        <v>0.0069</v>
+        <v>0.981</v>
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>#### Go beyond the headlines — with direct links to interconnected entities  Get full access to validated equipment, military capabilities, and market insights.  Subscribe to Janes  ## Discover how Janes can support your mission  ### Solutions for defence  Delivering trusted intelligence to warfighters to protect national interests, support readiness, and deter aggression.  ### Solutions for the intelligence community  Providing mission users with faster access to quality data to pre-empt threat...</t>
+          <t>Home  News    + Back to parent navigation item   + News   + Aerospace      - Back to parent navigation item     - Aerospace     - MRO     - Systems &amp; Interiors     - Helicopters     - Space     - Civil UAVs   + Air transport      - Back to parent navigation item     - Air transport     - Airframers     - Engines     - Programmes     - Orders &amp; Deliveries   + Safety   + Business aviation   + Region      - Back to parent navigation item     - Region     - Europe     - Africa     - North America...</t>
         </is>
       </c>
     </row>
@@ -4665,30 +4394,30 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>First production KF-21 rolled out - Janes</t>
+          <t>Defence, self-reliance, and budgetary priorities: Sectoral opportunities in a shifting strategic landscape - The Economic Times</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>https://www.janes.com/osint-insights/defence-news/defence/first-production-kf-21-rolled-out</t>
+          <t>https://m.economictimes.com/markets/stocks/news/defence-self-reliance-and-budgetary-priorities-sectoral-opportunities-in-a-shifting-strategic-landscape/articleshow/127367486.cms</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>janes.com</t>
+          <t>m.economictimes.com</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 13:51:16 GMT</t>
+          <t>Sat, 24 Jan 2026 05:43:00 GMT</t>
         </is>
       </c>
       <c r="F107" s="11" t="n">
-        <v>0.0064</v>
+        <v>0.8963</v>
       </c>
       <c r="G107" s="11" t="inlineStr">
         <is>
-          <t>### Solutions for defence  Delivering trusted intelligence to warfighters to protect national interests, support readiness, and deter aggression.  ### Solutions for the intelligence community  Providing mission users with faster access to quality data to pre-empt threats and protect national security.  ### Describe the operating environment  A trusted holistic view of threat, stability, and capability across the globe.  ### Inform decision making  Assured interconnected OSINT to deliver informed...</t>
+          <t>Our house view is where we believe that the Atmanirbhar Bharat initiative has transformed India's defence manufacturing landscape. The indigenous defence production reached a record Rs. 1.54 lakh crore in 2025, while defence exports grew approximately 12% to Rs. 24,000 crore. Besides this over 65% of India's defence equipment is now produced domestically showcasing a remarkable shift for a nation that was once among the world's largest arms importers. [...] ### Live Events      ## Atmanirbhar Bh...</t>
         </is>
       </c>
     </row>
@@ -4698,30 +4427,30 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Vietjet sticks with P&amp;W for next batch of A320neo-family jets - FlightGlobal</t>
+          <t>Beyond Aero Conducts Wind Tunnel Tests For Hydrogen-Electric Bizjet - Aviation Week Network</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/airlines/vietjet-sticks-with-pandw-for-next-batch-of-a320neo-family-jets/166222.article</t>
+          <t>https://aviationweek.com/business-aviation/aircraft-propulsion/beyond-aero-conducts-wind-tunnel-tests-hydrogen-electric</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 04:07:34 GMT</t>
+          <t>Mon, 19 Jan 2026 11:04:15 GMT</t>
         </is>
       </c>
       <c r="F108" s="8" t="n">
-        <v>0.0058</v>
+        <v>0.8559</v>
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>Skip to navigation   Trending now  Singapore Airshow  2026 World Air Forces directory  FlightGlobal has a new podcast - listen now  Site name  Site name  Search our site  Close menu [...] 2026-02-04T14:39:00Z By David Kaminski-Morrow    Russian operator S7 Group has signed a tentative agreement with state lessor GTLK covering the intent to supply 100 Tupolev Tu-214s to the airline. The memorandum of co-operation has also been signed by aerospace firm United Aircraft which is overseeing the reviv...</t>
+          <t>Market Sector    + Aerospace   + Air Transport   + MRO   + Defense   + Space   + Business Aviation  Markets [...] 4Air, Cambridge ‘Stress-Test’ Electric Aviation With Velis Flights  Business Aviation Predictions: What Lies Ahead In 2026? (Part 4) [...] ## Share  Thierry Dubois January 19, 2026  LYON—Beyond Aero has successfully tested a model of its BYA-1 hydrogen-electric business aircraft at the DNW wind tunnel in Marknesse, Netherlands, the Toulouse-based startup company announced Jan. 19. Th...</t>
         </is>
       </c>
     </row>
@@ -4731,30 +4460,30 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>Trusted Development Tools for Mission- and Safety-Critical Drone Software - Unmanned Systems Technology</t>
+          <t>Airbus Opens Bengaluru Tech Hub To Support Engineering, Maintenance - Aviation Week</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>https://www.unmannedsystemstechnology.com/2026/03/trusted-development-tools-for-mission-and-safety-critical-drone-software/</t>
+          <t>https://aviationweek.com/mro/aircraft-propulsion/airbus-opens-bengaluru-tech-hub-support-engineering-maintenance</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>unmannedsystemstechnology.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 13:52:43 GMT</t>
+          <t>Fri, 06 Mar 2026 19:59:16 GMT</t>
         </is>
       </c>
       <c r="F109" s="11" t="n">
-        <v>0.8387</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G109" s="11" t="inlineStr">
         <is>
-          <t>In addition to commercial UAV applications, AdaCore’s solutions support the development of defense-grade unmanned systems designed to operate in demanding and contested environments. The development toolkits enable the creation of resilient software capable of supporting AI-enabled systems, advanced sensors, and evolving mission requirements across platforms that may remain in service for decades.  To learn more about AdaCore’s trusted UAV software development solutions, visit their full profile...</t>
+          <t>Beyond engineering development, the Airbus India Technology Center is also expected to play a role in strengthening India’s aviation talent base, particularly in areas related to aircraft maintenance engineering and technical services. The OEM aims to use the center as a hub where Indian engineers and technical professionals can gain exposure to global aircraft programs, advanced maintenance technologies and complex engineering challenges. [...] Airbus has opened a new technology center in Benga...</t>
         </is>
       </c>
     </row>
@@ -4764,12 +4493,12 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Poland eyes benefits of joining GCAP sixth-generation fighter project - Defense News</t>
+          <t>India buys fighter jets and Lockheed Martin unveils the ‘Lamprey’ | Defense Dollars - Defense News</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>https://www.defensenews.com/global/europe/2026/03/23/poland-eyes-benefits-of-joining-gcap-sixth-generation-fighter-project/</t>
+          <t>https://www.defensenews.com/video/2026/02/23/india-buys-fighter-jets-and-lockheed-martin-unveils-the-lamprey-defense-dollars/</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
@@ -4779,15 +4508,15 @@
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Mon, 23 Mar 2026 15:21:29 GMT</t>
+          <t>Mon, 23 Feb 2026 14:34:49 GMT</t>
         </is>
       </c>
       <c r="F110" s="8" t="n">
-        <v>0.5226</v>
+        <v>0.4663</v>
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>Featured:  Coverage: Iran  2026 Tech Disruptors List  Coverage: Singapore Airshow  #### Europe  # Poland eyes benefits of joining GCAP sixth-generation fighter project  By Jaroslaw Adamowski  Delegates look at the GCAP 6th-generation fighter jet concept design at the Farnborough International Airshow 2024 near London. (Justin Tallis/AFP via Getty Images)  WARSAW, Poland — Polish Deputy State Assets Minister Konrad Gołota has announced that Poland is considering to join the Global Combat Air Prog...</t>
+          <t>### India buys fighter jets and Lockheed Martin unveils the ‘Lamprey’ | Defense Dollars  ### India buys fighter jets and Lockheed Martin unveils the ‘Lamprey’ | Defense Dollars  ###### Who’s providing drone defense at the World Cup? And what fighters did India buy recently? Plus: a new submersible that attaches to hulls of ships to recharge.  ###### Latest Videos  ###### Leaders look to new methods to retain Navy talent | Defense News Weekly Full Episode 2.24.26  ###### Quality-of-life improveme...</t>
         </is>
       </c>
     </row>
@@ -4797,30 +4526,30 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>South Korea to expand KF-21 AESA radar operational modes - FlightGlobal</t>
+          <t>Airbus: India’s Fleet Boom Will Triple Demand For MRO Engineers And Capacity - Aviation Week Network</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/fixed-wing/south-korea-to-expand-kf-21-aesa-radar-operational-modes/166158.article</t>
+          <t>https://aviationweek.com/mro/supply-chain/airbus-indias-fleet-boom-will-triple-demand-mro-engineers-capacity</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:04:50 GMT</t>
+          <t>Fri, 30 Jan 2026 18:09:30 GMT</t>
         </is>
       </c>
       <c r="F111" s="11" t="n">
-        <v>0.0513</v>
+        <v>0.1975</v>
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>### UK signs ECRS Mk2 radar production deal for Royal Air Force’s Tranche 3 Typhoon upgrade    2026-01-22T10:52:00Z By Craig Hoyle    The UK Royal Air Force will operationally field an active electronically scanned array radar on a portion of its Eurofighter Typhoon fleet from late this decade, via an integration contract announced on 22 January.  News    ### Boeing secures $2bn contract to continue work on B-52 re-engining    2025-12-26T12:04:00Z By Ryan Finnerty    The US Air Force funding wil...</t>
+          <t>+ Aerospace     - Aircraft &amp; Propulsion     - Connected Aerospace     - Emerging Technologies     - Manufacturing &amp; Supply Chain     - Advanced Air Mobility     - Sustainability   + Air Transport     - Aircraft &amp; Propulsion     - Interiors &amp; Connectivity     - Airports &amp; Networks     - Airlines &amp; Lessors     - Safety, Ops &amp; Regulation     - Maintenance &amp; Training     - Sustainability   + MRO     - Aircraft &amp; Propulsion     - Interiors &amp; Connectivity     - Emerging Technologies     - Supply Chain...</t>
         </is>
       </c>
     </row>
@@ -4830,30 +4559,30 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>India’s DAC clears $25.1bn military procurement proposals - Army Technology</t>
+          <t>Embraer and Adani aim to seek orders which would justify Indian E175 final assembly line - FlightGlobal</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>https://www.army-technology.com/news/india-dac-military-procurement/</t>
+          <t>https://www.flightglobal.com/aerospace/embraer-and-adani-aim-to-seek-orders-which-would-justify-indian-e175-final-assembly-line/166393.article</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>army-technology.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 13:40:49 GMT</t>
+          <t>Sun, 22 Feb 2026 11:00:48 GMT</t>
         </is>
       </c>
       <c r="F112" s="8" t="n">
-        <v>0.0279</v>
+        <v>0.15</v>
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>Skip to site menu Skip to page content   News  # India’s DAC clears $25.1bn military procurement proposals  In the financial year 2025-26, DAC approved 55 proposals amounting to Rs6.73bn.  Jangoulun Singsit March 30, 2026  Share   Copy Link  Share on X  Share on Linkedin  Share on Facebook  India’s Defence Acquisition Council (DAC) has approved military procurement proposals valued at approximately Rs2,380bn ($25.14bn) on 27 March 2026.  The council cleared acquisitions for the Indian Army, Air...</t>
+          <t>Skip to navigation   Trending now  Singapore Airshow  2026 World Air Forces directory  FlightGlobal has a new podcast - listen now  Site name  Site name  Search our site  Close menu [...] Announcements  FAQs  Topics A-Z  Terms and conditions  Cookie policy  Privacy policy  © ProMedia Group UK Ltd  Follow us on social media   Connect with us on Facebook  Connect with us on Twitter  Connect with us on Linked in  Email us  Connect with us on Youtube  Site powered by Webvision Cloud [...] 2026-02-21...</t>
         </is>
       </c>
     </row>
@@ -4863,30 +4592,30 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>Fuchs JAGM Tank Destroyer, Germany - Army Technology</t>
+          <t>U.S. Air Force Plans To Reactivate Unique Hypersonic Wind Tunnel - Aviation Week</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>https://www.army-technology.com/projects/fuchs-jagm-tank-destroyer-germany/</t>
+          <t>https://aviationweek.com/defense/missile-defense-weapons/us-air-force-plans-reactivate-unique-hypersonic-wind-tunnel</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>army-technology.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>Fri, 06 Mar 2026 22:30:39 GMT</t>
+          <t>Mon, 02 Mar 2026 23:43:06 GMT</t>
         </is>
       </c>
       <c r="F113" s="11" t="n">
-        <v>0.0273</v>
+        <v>0.1303</v>
       </c>
       <c r="G113" s="11" t="inlineStr">
         <is>
-          <t>The platform includes a spacious internal volume of 12m2, with an interior height of 1.6m. It is operated by a crew of two personnel.  Maintenance support is provided through built-in test equipment that assists in vehicle servicing procedures while also providing external diagnostics of the vehicle.  ## Fuchs JAGM tank destroyer payload  The Fuchs JAGM can be equipped with the AGM-179 JAGM, which is suitable for both surface-to-surface and surface-to-air deployment. The missile can engage targe...</t>
+          <t>## Share  Graham Warwick March 02, 2026  The U.S. Air Force has initiated its plan to reactivate a wind tunnel capable of testing hypersonic vehicles and engines in real atmospheric conditions at speeds up to Mach 7 and altitudes up to 120,000 ft. The Air Force Test Center has issued a source sought notice for a contractor to lead...  Graham Warwick  Graham leads Aviation Week's coverage of technology, focusing on engineering and technology across the aerospace industry, with a special focus on...</t>
         </is>
       </c>
     </row>
@@ -4896,30 +4625,30 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Shield AI to supply V-BAT drones to Indian Army - Army Technology</t>
+          <t>Indian Army tests new tactical vehicle at military exercise - Janes</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>https://www.army-technology.com/news/indian-army-shieldai-drones/</t>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/indian-army-tests-new-tactical-vehicle-at-military-exercise</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>army-technology.com</t>
+          <t>janes.com</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>Thu, 29 Jan 2026 17:55:46 GMT</t>
+          <t>Wed, 04 Mar 2026 13:20:32 GMT</t>
         </is>
       </c>
       <c r="F114" s="8" t="n">
-        <v>0.027</v>
+        <v>0.0988</v>
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>Skip to site menu Skip to page content   News  # Shield AI to supply V-BAT drones to Indian Army  The deal includes the procurement of V-BAT aircraft, and access to Shield AI’s Hivemind autonomy SDK.  Jangoulun Singsit January 29, 2026  Share   Copy Link  Share on X  Share on Linkedin  Share on Facebook  India has chosen Shield AI to supply V-BAT uncrewed aerial systems (UAS) and licences for the company’s Hivemind autonomy software, which will be integrated into the V-BAT platform for the India...</t>
+          <t>### Describe the operating environment  A trusted holistic view of threat, stability, and capability across the globe.  ### Inform decision making  Assured interconnected OSINT to deliver informed, accurate, and reliable mission intelligence.  ### More news articles  Air  ### Update: UK selects AW149 for NMH  Read Article  Defence  ### Pentagon developing homeland defence C-UAS sensors  Read Article  Sea  ### Iran conflict 2026: Israel claims over 150 ballistic missiles, 200 air-defence systems...</t>
         </is>
       </c>
     </row>
@@ -4929,30 +4658,30 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>AH-64 Apache conducts live fire with new XM1225 APEX ammo - Army Technology</t>
+          <t>Indra To Boost Meteor Missile With Enhanced Communication Link - Aviation Week Network</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>https://www.army-technology.com/news/ah64-helicopter-us-army-test/</t>
+          <t>https://aviationweek.com/defense/missile-defense-weapons/indra-boost-meteor-missile-enhanced-communication-link</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>army-technology.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 16:29:13 GMT</t>
+          <t>Tue, 10 Feb 2026 09:50:21 GMT</t>
         </is>
       </c>
       <c r="F115" s="11" t="n">
-        <v>0.0228</v>
+        <v>0.0663</v>
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
-          <t>The design allows use against a range of modern threats including UAS, exposed personnel, and small boats without requiring any modifications to the Apache’s M230 Area Weapon System or its fire control system.  The Armaments Center supplied the proximity fuze technology and partnered with PdM MCA to share data with Northrup Grumman for production decisions, rapid delivery, and achieving Urgent Materiel Release status.  Personnel from Project Manager Apache, Army Evaluation Center, US Army Combat...</t>
+          <t>- Aerospace     - Air Transport     - MRO     - Defense     - Space     - Business Aviation   + Type View All Products     - Intelligence Bundles         AWIN - Premium        AWIN - Aerospace and Defense        AWIN - Business Aviation        AWIN - Commercial Aviation     - Market Briefings         Aerospace Daily &amp; Defense Report        Aviation Daily        SpeedNews        The Weekly of Business Aviation     - Directories         Air Charter Guide        Aviation Week Marketplace        Rou...</t>
         </is>
       </c>
     </row>
@@ -4962,30 +4691,30 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>Tamilan Launches High-Pressure Drone Cleaning Solutions &amp; Eco-Friendly Building Care - Unmanned Systems Technology</t>
+          <t>South Korea to expand KF-21 AESA radar operational modes - FlightGlobal</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>https://www.unmannedsystemstechnology.com/2026/02/tamilan-launches-high-pressure-drone-cleaning-solutions-eco-friendly-building-care/</t>
+          <t>https://www.flightglobal.com/fixed-wing/south-korea-to-expand-kf-21-aesa-radar-operational-modes/166158.article</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>unmannedsystemstechnology.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 06:13:00 GMT</t>
+          <t>Mon, 02 Feb 2026 10:04:50 GMT</t>
         </is>
       </c>
       <c r="F116" s="8" t="n">
-        <v>0.0179</v>
+        <v>0.0227</v>
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>Saito EFI 120  Four-stroke EFI engine with 12,000 ft max altitude  ## More from Tamilan  Tamilan to Showcase High-Volume Drone Manufacturing at DSEI 2025  Tamilan, a developer of advanced drone airframes and complete unmanned solutions, will be attending DSEI 2025, taking place from September 9–12 at ExCeL London, UK  Sep 02, 2025  Versatile Drone Airframes &amp; Complete Solutions for Civil &amp; Military Applications  Tamilan's products are ideal for enterprises and governments looking to massively sc...</t>
+          <t>2026-01-29T08:05:00Z By Greg Waldron    The People’s Liberation Army Air Force’s August 1st display team has arrived in Singapore with seven Chengdu J-10C fighters, marking the type’s debut at the biennial show following recent combat success with Pakistan.   Contact us  About us  Advertise with us  Jobs  Conferences and Events  Newsletters  Paid content  Reports  FlightGlobal is the global aviation community’s primary source of news, data, insight, knowledge and expertise. We provide news, data...</t>
         </is>
       </c>
     </row>
@@ -4995,30 +4724,30 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>​Ukraine Moves From Arms Buyer to Co-Producer of Mirage Jets and Crotale Systems - Defense Express</t>
+          <t>Swedish air force receives first upgraded RM12EP engine for Gripen C/D fleet - FlightGlobal</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>https://en.defence-ua.com/industries/ukraine_moves_from_arms_buyer_to_co_producer_of_mirage_jets_and_crotale_systems-17447.html</t>
+          <t>https://www.flightglobal.com/defence/swedish-air-force-receives-first-upgraded-rm12ep-engine-for-gripen-c/d-fleet/166763.article</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>en.defence-ua.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 18:01:57 GMT</t>
+          <t>Tue, 24 Mar 2026 11:40:21 GMT</t>
         </is>
       </c>
       <c r="F117" s="11" t="n">
-        <v>0.0153</v>
+        <v>0.0208</v>
       </c>
       <c r="G117" s="11" t="inlineStr">
         <is>
-          <t>Latest  Most viewed  February 10, 2026  ### U.S. Delivers New F-35 Fighters Without Radars Due to Upgrade Delays, Mounting Issues  February 10, 2026  ### India Plans Additional Order for SCALP Cruise Missiles, This Could Be Problem for Ukraine  February 9, 2026  ### Assessing Cost of 150 Gripens, 100 Rafales in Ukraine's Ambition to Reach Global Air Power Top 10  February 6, 2026  ### Over 1,000 Tomahawks, 1,900 AIM-120s, 500 SM-6s per Year: U.S. Moves to Multiply Missile Production  January 31,...</t>
+          <t>Performed at the company’s Trollhattan site, the work spans “improved turbine hardware and updated engine control software designed to increase engine thrust, extend operating time and reduce life‑cycle costs”, it says.  The Swedish air force operates almost 100 examples of the Gripen C/D, which aviation analytics company Cirium records as aged between 11 and 23 years. They are powered by the RM12 – a derivative of GE Aerospace’s F404 turbofan.  Source: Saab  The Gripen C/D’s upgraded RM12EP eng...</t>
         </is>
       </c>
     </row>
@@ -5028,30 +4757,30 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>India doubles down on state-backed venture capital, approving $1.1B fund - TechCrunch</t>
+          <t>ST Engineering Unveils Business Aviation Thrust Reverser Demonstrator - Aviation International News</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/02/14/india-doubles-down-on-state-backed-venture-capital-approving-1-1b-fund/</t>
+          <t>https://www.ainonline.com/aviation-news/business-aviation/2026-02-01/st-engineering-unveils-business-aviation-thrust-reversal</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>ainonline.com</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 16:23:22 GMT</t>
+          <t>Mon, 02 Feb 2026 07:07:58 GMT</t>
         </is>
       </c>
       <c r="F118" s="8" t="n">
-        <v>0.9105</v>
+        <v>0.0133</v>
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>First outlined in the January 2025 budget speech by India’s finance minister, the ₹100 billion fund won cabinet approval this week (more than a year after the speech), allowing the government to move ahead with deployment. A previous iteration of the program, launched in 2016, committed ₹100 billion to 145 private funds that have invested more than ₹255 billion (about $2.8 billion) in over 1,370 startups, according to official data released on Saturday. [...] Skip to content  Startups  # India d...</t>
+          <t>Email  By Charlotte Bailey • Writer  February 2, 2026  ## In this article  ## ST Engineering  Company  ## More In Engines  ## Pratt’s Eagle Services Asia Engine MRO Leverages Automation  ### Robots cut time and man-hours for inspections and engine core and compressor stacking  Engines  ## GE Completes Hybrid-electric Engine Demonstrator Ground Test  ### Work is aimed at developing future narrowbody airliner powertrains  Engines  ## Billion-dollar Settlement Ends Honeywell, Flexjet Fight  ### Agr...</t>
         </is>
       </c>
     </row>
@@ -5061,30 +4790,30 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>Special Report: India's IG Defence advances UAV manufacturing capabilities - Janes</t>
+          <t>US Navy seeks advanced anti-radiation missile for contested environments - FlightGlobal</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>https://www.janes.com/osint-insights/defence-news/industry/special-report-indias-ig-defence-advances-uav-manufacturing-capabilities</t>
+          <t>https://www.flightglobal.com/fixed-wing/us-navy-seeks-advanced-anti-radiation-missile-for-contested-environments/166380.article</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>janes.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 08:51:21 GMT</t>
+          <t>Fri, 20 Feb 2026 04:33:44 GMT</t>
         </is>
       </c>
       <c r="F119" s="11" t="n">
-        <v>0.9933</v>
+        <v>0.0131</v>
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
-          <t>The company's portfolio includes strike-capable unmanned platforms; intelligence, surveillance, and reconnaissance (ISR) systems; logistic UAV swarms; and training simulators.  Major General R C Padhi (retd), senior vice-president at IG Defence, told Janes in February that the proposed facility in Odisha, along with a new facility in Jhansi, Uttar Pradesh, would enhance IG Defence's manufacturing capabilities.  IG Defence commissioned another facility in Noida, Uttar Pradesh, in December 2025 to...</t>
+          <t>Skip to navigation   Trending now  Singapore Airshow  2026 World Air Forces directory  FlightGlobal has a new podcast - listen now  Site name  Site name  Search our site  Close menu [...] Home  News    + Back to parent navigation item   + News   + Aerospace      - Back to parent navigation item     - Aerospace     - MRO     - Systems &amp; Interiors     - Helicopters     - Space     - Civil UAVs   + Air transport      - Back to parent navigation item     - Air transport     - Airframers     - Engine...</t>
         </is>
       </c>
     </row>
@@ -5094,12 +4823,12 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>India approves INR3.6 trillion arms package including Rafales, P-8Is - FlightGlobal</t>
+          <t>Aurora completes fuselage for X-65 ‘active flow control’ demonstrator - FlightGlobal</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/fixed-wing/india-approves-inr36-trillion-arms-package-including-rafales-p-8is/166308.article</t>
+          <t>https://www.flightglobal.com/fixed-wing/aurora-completes-fuselage-for-x-65-active-flow-control-demonstrator/166542.article</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
@@ -5109,15 +4838,15 @@
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 03:36:22 GMT</t>
+          <t>Thu, 05 Mar 2026 19:06:54 GMT</t>
         </is>
       </c>
       <c r="F120" s="8" t="n">
-        <v>0.3881</v>
+        <v>0.0125</v>
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>2026-02-12T05:49:00Z By Greg Waldron    The US Marine Corps will retire its Boeing AV-8B Harrier II fleet in June 2026, a year earlier than previously planned, as it accelerates transition to the Lockheed Martin F-35B and focuses on aggressive modernisation for future threats.  News    ### Mitchell Institute calls for doubled B-21 fleet amid China concerns    A US Air Force-associated think tank is calling for a vastly expanded fighter and bomber fleet, warning that current force levels are insu...</t>
+          <t>Skip to navigation   Trending now  Singapore Airshow  2026 World Air Forces directory  FlightGlobal has a new podcast - listen now  Site name  Site name  Search our site  Close menu [...] Announcements  FAQs  Topics A-Z  Terms and conditions  Cookie policy  Privacy policy  © ProMedia Group UK Ltd  Follow us on social media   Connect with us on Facebook  Connect with us on Twitter  Connect with us on Linked in  Email us  Connect with us on Youtube  Site powered by Webvision Cloud [...] Home  News...</t>
         </is>
       </c>
     </row>
@@ -5127,30 +4856,30 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>Uttar Pradesh govt to expand ambit of defence manufacturing corridor - Business Standard</t>
+          <t>Collins powers up tests of 1MW electric motors for hybridised PW1100G engine - FlightGlobal</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/external-affairs-defence-security/news/uttar-pradesh-govt-to-expand-ambit-of-defence-manufacturing-corridor-126020501022_1.html</t>
+          <t>https://www.flightglobal.com/engines/collins-powers-up-tests-of-1mw-electric-motors-for-hybridised-pw1100g-engine/166677.article</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>business-standard.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 10:22:32 GMT</t>
+          <t>Mon, 16 Mar 2026 18:16:30 GMT</t>
         </is>
       </c>
       <c r="F121" s="11" t="n">
-        <v>0.2814</v>
+        <v>0.0102</v>
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
-          <t>Presenting sponsor  Associate Sponsors  Thursday, February 05, 2026 | 05:23 AM IST हिंदी में पढें  Home / External Affairs Defence Security / News / Uttar Pradesh govt to expand ambit of defence manufacturing corridor  # Uttar Pradesh govt to expand ambit of defence manufacturing corridor  ## With investor interest surging, Uttar Pradesh plans to expand its Defence Industrial Corridor beyond six nodes to accommodate new defence manufacturing projects  premium  UP Chief Minister Yogi Adityanath s...</t>
+          <t>Taking place at the company’s electric power systems lab in Rockford, Illinois – also known as “The Grid” – the trials will validate the electric motor-generators, controllers and power distribution systems for the SWITCH engine.  These will later be installed onto the PW1100G for a later round of ground testing, as the MTU Aero Engines-led project wraps up later this year.  Source: Collins Aerospace  Tests of the integrated electrical power system have been taking place at Collins Aerospace’s f...</t>
         </is>
       </c>
     </row>
@@ -5160,30 +4889,30 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>AI for investors - MLQ.ai</t>
+          <t>BAE demonstrates scalable electronic attack system - FlightGlobal</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>https://mlq.ai/news/india-approves-11-billion-government-fund-to-boost-deep-tech-startups/</t>
+          <t>https://www.flightglobal.com/fixed-wing/bae-demonstrates-scalable-electronic-attack-system/166416.article</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>mlq.ai</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 09:37:42 GMT</t>
+          <t>Tue, 24 Feb 2026 08:33:07 GMT</t>
         </is>
       </c>
       <c r="F122" s="8" t="n">
-        <v>0.1624</v>
+        <v>0.0097</v>
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>TECH  # India Approves $1.1 Billion Government Fund to Boost Deep Tech Startups  February 15, 2026 at 9:31 AM • by  MLQ Editorial  #### Key Points   India's cabinet approved Startup India Fund of Funds 2.0 with a ₹10,000 crore ($1.1 billion) corpus to support deep tech and manufacturing startups through private VCs.  The 2016 program committed ₹10,000 crore to 145 funds, leveraging over ₹25,500 crore in investments to 1,370 startups.  Private funding in India's startups fell 17% to $10.5 billion...</t>
+          <t>Announcements  FAQs  Topics A-Z  Terms and conditions  Cookie policy  Privacy policy  © ProMedia Group UK Ltd  Follow us on social media   Connect with us on Facebook  Connect with us on Twitter  Connect with us on Linked in  Email us  Connect with us on Youtube  Site powered by Webvision Cloud [...] Home  News    + Back to parent navigation item   + News   + Aerospace      - Back to parent navigation item     - Aerospace     - MRO     - Systems &amp; Interiors     - Helicopters     - Space     - Ci...</t>
         </is>
       </c>
     </row>
@@ -5193,30 +4922,30 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>India, UAE Agree To Tighten Defense Cooperation - Aviation Week Network</t>
+          <t>Elbit picks Lowental Hybrid to provide extended-endurance UAV propulsion systems - FlightGlobal</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/defense/budget-policy-operations/india-uae-agree-tighten-defense-cooperation</t>
+          <t>https://www.flightglobal.com/defence/elbit-picks-lowental-hybrid-to-provide-extended-endurance-uav-propulsion-systems/166099.article</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>aviationweek.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 16:52:04 GMT</t>
+          <t>Wed, 28 Jan 2026 12:11:15 GMT</t>
         </is>
       </c>
       <c r="F123" s="11" t="n">
-        <v>0.1581</v>
+        <v>0.0042</v>
       </c>
       <c r="G123" s="11" t="inlineStr">
         <is>
-          <t>## Subscription Required  India, UAE Agree To Tighten Defense Cooperation is published in Aerospace Daily &amp; Defense Report, an Aviation Week Intelligence Network (AWIN) Market Briefing and is included with your AWIN membership.  Already a member of AWIN or subscribe to Aerospace Daily &amp; Defense Report through your company? Loginwith your existing email and password.  Not a member?  Learn how you can access the market intelligence and data you need to stay abreast of what's happening in the aeros...</t>
+          <t>Home  News    + Back to parent navigation item   + News   + Aerospace      - Back to parent navigation item     - Aerospace     - MRO     - Systems &amp; Interiors     - Helicopters     - Space     - Civil UAVs   + Air transport      - Back to parent navigation item     - Air transport     - Airframers     - Engines     - Programmes     - Orders &amp; Deliveries   + Safety   + Business aviation   + Region      - Back to parent navigation item     - Region     - Europe     - Africa     - North America...</t>
         </is>
       </c>
     </row>
@@ -5226,30 +4955,30 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>GCAP advances as Edgewing lands first joint contract from partner nations - flightglobal.com</t>
+          <t>New 'MedTech Advance' Sourcing Directory Launches to Streamline Global Medical Device Manufacturing - The Manila Times</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/defence/2026/04/gcap-advances-as-edgewing-lands-first-joint-contract-from-partner-nations/</t>
+          <t>https://www.manilatimes.net/2026/01/27/tmt-newswire/pr-newswire/new-medtech-advance-sourcing-directory-launches-to-streamline-global-medical-device-manufacturing/2265627</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>manilatimes.net</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 11:08:18 GMT</t>
+          <t>Tue, 27 Jan 2026 01:16:14 GMT</t>
         </is>
       </c>
       <c r="F124" s="8" t="n">
-        <v>0.1484</v>
+        <v>0.0036</v>
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>Menu  search  Trending now:  CONTRACT  # GCAP advances as Edgewing lands first joint contract from partner nations  By Craig Hoyle |  The three-nation Global Combat Air Programme (GCAP) is moving into its next phase of activity, following the award of a contract worth £686 million ($904 million).  Placed with design and development authority Edgewing and announced on 2 April, the contract “invests in key design and engineering activities and enables the trilateral partnership to build momentum a...</t>
+          <t>Tuesday, January 27, 2026    Today's Paper  New "MedTech Advance" Sourcing Directory Launches to Streamline Global Medical Device Manufacturing  Sign In  New user? Click Here  Subscribe   Sign In  New user? Click Here  OPINION  NEWS  REGIONS  WORLD  BUSINESS  SPORTS  ENTERTAINMENT  LIFESTYLE  THE SUNDAY TIMES  SPECIAL FEATURES  SPECIAL SECTIONS  TMT NEWSWIRE  Media OutReach Newswire  PR Newswire  GlobeNewswire  Plentisoft  FAST TIMES  LEGAL ADVICE  CAMPUS PRESS  VIDEOS  EXPATS &amp; DIPLOMATS  PHOTO...</t>
         </is>
       </c>
     </row>
@@ -5259,30 +4988,30 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>Bosch and Tata AutoComp plan Indian e-mobility JV - Automotive World</t>
+          <t>India has moved to self-reliance in defence, says Defence Research and Development Organisation officer - The Times of India</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>https://www.automotiveworld.com/news/bosch-and-tata-autocomp-plan-indian-e-mobility-jv/</t>
+          <t>https://timesofindia.indiatimes.com/city/bengaluru/india-has-moved-to-self-reliance-in-defence-says-defence-research-and-development-organisation-officer/amp_articleshow/130025592.cms</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>automotiveworld.com</t>
+          <t>timesofindia.indiatimes.com</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 05:10:14 GMT</t>
+          <t>Sat, 04 Apr 2026 20:16:00 GMT</t>
         </is>
       </c>
       <c r="F125" s="11" t="n">
-        <v>0.0435</v>
+        <v>0.9789</v>
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
-          <t>Skip to content   Bosch and Tata AutoComp plan Indian e-mobility JV Škoda brings V2L and digital key to Elroq and Enyaq Tougher crash avoidance rules shape 2026 IIHS awards Xpeng formalises robotaxi push with dedicated business unit Blume holds up China as template, “clear progress” on VW cuts US auto groups press Trump to hold the line on China EVs Musk unveils Terafab as Tesla-SpaceX joint chip venture SK Signet targets US and Europe with 400 kW SiC charger Daimler Buses launches electric inte...</t>
+          <t>Bengaluru: India has moved from being an "import denial nation" to a self-reliant country in defence, with expanding opportunities in the sector, said Binay Kumar Das, director general (Electronics and Communication System), Defence Research and Development Organisation (DRDO). Speaking at the fifth convocation of Dr Manmohan Singh Bengaluru City University, he said with more than 500 negative import lists, India is strengthening domestic defence manufacturing. He urged students to contribute to...</t>
         </is>
       </c>
     </row>
@@ -5292,30 +5021,30 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Draper-Powered Missile Demonstrator Stages First Flight - Aviation Week</t>
+          <t>Pakistan, Venezuela &amp; now Iran: How China has become laughingstock of the global stage - The Times of India</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>https://aviationweek.com/defense/missile-defense-weapons/draper-powered-missile-demonstrator-stages-first-flight</t>
+          <t>https://timesofindia.indiatimes.com/defence/international/china-has-become-the-laughingstock-of-the-international-community/articleshow/129560285.cms</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>aviationweek.com</t>
+          <t>timesofindia.indiatimes.com</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 17:28:39 GMT</t>
+          <t>Sat, 14 Mar 2026 15:24:00 GMT</t>
         </is>
       </c>
       <c r="F126" s="8" t="n">
-        <v>0.0256</v>
+        <v>0.9167</v>
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>## Subscription Required  Draper-Powered Missile Demonstrator Stages First Flight is published in Aerospace Daily &amp; Defense Report, an Aviation Week Intelligence Network (AWIN) Market Briefing and is included with your AWIN membership.  Already a member of AWIN or subscribe to Aerospace Daily &amp; Defense Report through your company? Loginwith your existing email and password.  Not a member?  Learn how you can access the market intelligence and data you need to stay abreast of what's happening in t...</t>
+          <t>## Venezuela operation exposes radar vulnerabilities  The doubts surrounding Chinese defence technology deepened further during a dramatic American military operation in Venezuela.During the mission, US forces carried out a large-scale operation involving stealth aircraft, electronic warfare platforms and special forces units.The operation reportedly succeeded in capturing Venezuelan leader Nicolás Maduro without any US fatalities.The mission also exposed vulnerabilities in Venezuela’s radar and...</t>
         </is>
       </c>
     </row>
@@ -5325,30 +5054,30 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>Jaykay Enterprises Acquires Defence Manufacturing Business to Strengthen Missile Systems Capabilities - Machine Maker</t>
+          <t>MRO facility set to boost self-reliance in aircraft maintenance - The Times of India</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>https://themachinemaker.com/news/jaykay-enterprises-acquires-defence-manufacturing-business-to-strengthen-missile-systems-capabilities/</t>
+          <t>https://timesofindia.indiatimes.com/city/lucknow/mro-facility-set-to-boost-self-reliance-in-aircraft-maintenance/amp_articleshow/129871824.cms</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>themachinemaker.com</t>
+          <t>timesofindia.indiatimes.com</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 04:13:14 GMT</t>
+          <t>Sun, 29 Mar 2026 01:09:00 GMT</t>
         </is>
       </c>
       <c r="F127" s="11" t="n">
-        <v>0.025</v>
+        <v>0.8103</v>
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>09 Apr 2026   Show Reports  How a Culture of Respect at Motherson Shaped Kalpna’s Confidence in Manufacturing    08 Apr 2026   Womanufacturing  Callington to Showcase High-Performance Chemical Solutions at AeroDef India Manufacturing Expo 2026    08 Apr 2026   Show Reports   Jaykay Enterprises, MAKE IN INDIA, MANUFACTURING  #### MM Desk   All Posts  PrevPreviousToyota Kirloskar Motor Shines at IndiaSkills National Competition 2025–26 with 9 Medals  ## Related post  ### Live turning insight for s...</t>
+          <t>Lucknow: The state-of-the-art maintenance, repair and overhaul (MRO) hub, the foundation stone for which was laid by Prime Minister Narendra Modi at Noida International Airport on Saturday, is a step towards making Uttar Pradesh as well as the country self-reliant in the field of aircraft maintenance. "India currently depends heavily on foreign countries for aircraft maintenance. Around 85% of the country's aircraft are sent abroad for MRO, leading to significant outflow of foreign exchange," th...</t>
         </is>
       </c>
     </row>
@@ -5358,30 +5087,30 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>Embraer Exploring Aluminum Manufacturing in India - Aviation International News</t>
+          <t>Leonardo says new JV could treble size of aerostructures business - FlightGlobal</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>https://www.ainonline.com/aviation-news/aerospace/2026-02-20/embraer-exploring-aluminium-manufacturing-india</t>
+          <t>https://www.flightglobal.com/aerospace/leonardo-says-new-jv-could-treble-size-of-aerostructures-business/166442.article</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>ainonline.com</t>
+          <t>flightglobal.com</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Fri, 20 Feb 2026 18:58:10 GMT</t>
+          <t>Wed, 25 Feb 2026 18:29:31 GMT</t>
         </is>
       </c>
       <c r="F128" s="8" t="n">
-        <v>0.0227</v>
+        <v>0.7655</v>
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>Regulations and Government  ## EASA Part-IS Regulations To Bolster Data Security  ### Safety-focused European Information Security Management Systems requirement comes fully into effect later this month  Regulations and Government  ## AirX To Expand Middle Eastern Ops after GACA Approval  ### Malta-based operator receives regulatory approval from Saudi Arabia  Regulations and Government  ## Surprise FAA Notams Wreak Havoc in Texas and New Mexico  ### Questions swirl regarding their purpose  Regu...</t>
+          <t>Last June, it established an unmanned technologies joint venture with Baykar of Turkey called LBA Systems. It is also teaming with India’s Adani to set up a helicopter manufacturing ecosystem in that country, including potential final assembly facilities for the AW169M and AW190.  On space, a proposed merger with the non-launcher activities of Airbus and Thales is going through European regulatory approval, while Leonardo also expects to close in March its acquisition of the defence land systems...</t>
         </is>
       </c>
     </row>
@@ -5391,30 +5120,30 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>France, India inaugurate H125 line as potential Rafale deal looms - FlightGlobal</t>
+          <t>MRO Memo: India, U.S. Regulators And OEMs Seek Streamlined Cooperation - Aviation Week</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/helicopters/france-india-inaugurate-h125-line-as-potential-rafale-deal-looms/166349.article</t>
+          <t>https://aviationweek.com/mro/safety-ops-regulation/mro-memo-india-us-regulators-oems-seek-streamlined-cooperation</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>aviationweek.com</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 05:53:24 GMT</t>
+          <t>Fri, 06 Mar 2026 21:05:44 GMT</t>
         </is>
       </c>
       <c r="F129" s="11" t="n">
-        <v>0.0171</v>
+        <v>0.1755</v>
       </c>
       <c r="G129" s="11" t="inlineStr">
         <is>
-          <t>“They expressed their wish to further strengthen their partnership in defence aeronautics, especially in the field of manufacturing of fighter aircraft and combat aircraft engines under the Make in India initiative, and welcomed recent positive developments in this regard,” reads the joint statement.  An AoN from the Defence Acquisition Council is a formal approval that a military purchase is justified, allowing the government to move forward into detailed tendering, vendor selection, and eventu...</t>
+          <t>The arrangement, announced March 5, has been established under the regulators’ Bilateral Aviation Safety Agreement and complements the existing Implementation Procedures for Airworthiness already in place between the two agencies. The new cooperation is designed to streamline certification processes and enhance transparency in the management of aircraft and engine approvals between India and the U.S.  A notable feature of the new framework is the inclusion of major aerospace manufacturers such a...</t>
         </is>
       </c>
     </row>
@@ -5424,30 +5153,30 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>Space Budget 2026-27: Rs 13,705 Crore Allocated - Rediff MoneyWiz</t>
+          <t>India Pushes Defense Self-Reliance Amid Middle East Conflict - Bloomberg.com</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/space-budget-2026-27-rs-13-705-crore-allocated/41195920260201</t>
+          <t>https://www.bloomberg.com/news/articles/2026-04-09/india-pushes-defense-self-reliance-amid-middle-east-conflict</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>money.rediff.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>Sun, 01 Feb 2026 18:12:00 GMT</t>
+          <t>Thu, 09 Apr 2026 14:19:23 GMT</t>
         </is>
       </c>
       <c r="F130" s="8" t="n">
-        <v>0.0153</v>
+        <v>0.1475</v>
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>RediffmailMoneyBill PaymentsBusiness EmailrediffGURUSRediff-TV  Hi Guest   Feedback  |  Sign In  |  Sign-up  News Forex Indices Sectors Mutual Funds Insurance Gainers Losers Trends Star Portfolios My Portfolio My Watchlist  Follow Rediff on:   Market News  Latest  International Market  Economy  Mutual Fund  IPO  Industries  Home  » Market News » Space Budget 2026-27: Rs 13,705 Crore Allocated  # Space Budget 2026-27: Rs 13,705 Crore Allocated  By Rediff Money Desk, New Delhi  1 Minute Read Liste...</t>
+          <t>Politics  # India Pushes Defense Self-Reliance Amid Middle East Conflict  Contact us:  Provide news feedback or report an error  Confidential tip?  Send a tip to our reporters  Site feedback:  Take our Survey  By Sudhi Ranjan Sen  India needs to localize its defense production and build capacity to rapidly scale up in times of conflict, a key lesson from the Iran war, according to senior military officials.  “In this 36-day war, it is a resilience, supply chains, which have been demonstrated by...</t>
         </is>
       </c>
     </row>
@@ -5457,30 +5186,30 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>Pratt &amp; Whitney targets end of decade for full GTF recovery - FlightGlobal</t>
+          <t>Hensoldt secures EUR100 million order for TRML-4D radars from Diehl Defence - Janes</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/engines/pratt-and-whitney-targets-end-of-decade-for-full-gtf-recovery/166201.article</t>
+          <t>https://www.janes.com/osint-insights/defence-news/c4isr/hensoldt-secures-eur100-million-order-for-trml-4d-radars-from-diehl-defence</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>janes.com</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 06:43:02 GMT</t>
+          <t>Tue, 03 Feb 2026 12:07:37 GMT</t>
         </is>
       </c>
       <c r="F131" s="11" t="n">
-        <v>0.0117</v>
+        <v>0.1246</v>
       </c>
       <c r="G131" s="11" t="inlineStr">
         <is>
-          <t>2026-01-30T08:02:00Z By Dominic Perry    Rolls-Royce is promising a further time-on-wing boost for the Trent 1000 with the roll-out of a second phase of its durability enhancement package for the engine, an option on the Boeing 787, after obtaining certification for the latest high-pressure turbine (HPT) upgrades in late 2025.  News    ### Pratt &amp; Whitney’s GTF deliveries increased 6% in 2025, while recall recovery progresses    2026-01-28T13:57:00Z By Jon Hemmerdinger    Pratt &amp; Whitney deliver...</t>
+          <t>### More news articles  C4iSR  ### Hensoldt secures EUR100 million order for TRML-4D radars from Diehl Defence  Read Article  Air  ### Singapore Airshow 2026: Singapore acquires used C-130H aircraft to refresh airlift capabilities  Read Article  C4iSR  ### Singapore Airshow 2026: Singapore begins search for successor to FPS-117 radar  Read Article  ## See how Janes delivers verified defence intelligence for faster, safer decisions   The world's most complete foundational military data asset.  50...</t>
         </is>
       </c>
     </row>
@@ -5490,12 +5219,12 @@
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Singapore Airshow 2026: KAI moves to boost Malaysia's FA-50 package with proposed AMRAAM integration - janes.com</t>
+          <t>UK MoD orders Giraffe 1X radars - janes.com</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>https://www.janes.com/osint-insights/defence-news/industry/singapore-airshow-2026-kai-moves-to-boost-malaysias-fa-50-package-with-proposed-amraam-integration</t>
+          <t>https://www.janes.com/osint-insights/defence-news/c4isr/uk-mod-orders-giraffe-1x-radars</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
@@ -5505,15 +5234,15 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 08:50:47 GMT</t>
+          <t>Tue, 07 Apr 2026 13:37:36 GMT</t>
         </is>
       </c>
       <c r="F132" s="8" t="n">
-        <v>0.0114</v>
+        <v>0.1153</v>
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t>skip to main content  Search Janes  # Singapore Airshow 2026: KAI moves to boost Malaysia's FA-50 package with proposed AMRAAM integration  By Ridzwan Rahmat |  A model of the FA-50 on display at Singapore Airshow 2026. (Janes/Ridzwan Rahmat)  Korea Aerospace Industries (KAI) is seeking to reinforce its position in Malaysia's light combat aircraft programme by proposing expanded weapons integration for a planned second batch of FA‑50s.  A company representative told Janes at Singapore Airshow 20...</t>
+          <t>skip to main content  Search Janes  # UK MoD orders Giraffe 1X radars  By Tamara Rozouvan |  A Saab Giraffe 1X radar being manufactured at Saab UK's Centre of Radar Excellence in Fareham. (Saab)  The UK Ministry of Defence (MoD) has ordered an undisclosed number of Giraffe 1X radar systems from Saab UK valued at nearly GBP24 million (USD31.84 million), according to a 1 April Saab press release.  The order was made with funding from the NATO Security Assistance and Training Ukraine (NSATU) Trust...</t>
         </is>
       </c>
     </row>
@@ -5523,30 +5252,30 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>The Open Fan Revolution: Why Airbus Is Stripping The Cowling Off - Simple Flying</t>
+          <t>Indian Army, Navy to procure domestically built handheld C-UAS - Janes</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>https://simpleflying.com/open-fan-revolution-why-airbus-stripping-cowling-off/</t>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/indian-army-navy-to-procure-domestically-built-handheld-c-uas</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>simpleflying.com</t>
+          <t>janes.com</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 18:39:56 GMT</t>
+          <t>Wed, 21 Jan 2026 12:06:51 GMT</t>
         </is>
       </c>
       <c r="F133" s="11" t="n">
-        <v>0.0104</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
-          <t>## Why Airbus Is Betting On Open-Fan Propulsion  The RISE open-fan engine is built around moving a far greater mass of air at lower speeds than today’s enclosed turbofans, a key driver of efficiency. CFM estimates the design could deliver at least a 20% reduction in fuel burn and CO₂ emissions compared with the most advanced engines currently in service. This gain comes from an extremely high bypass ratio, potentially well above 50:1, versus roughly 11:1 on the LEAP family. Eliminating the nacel...</t>
+          <t>skip to main content  Search Janes  # Indian Army, Navy to procure domestically built handheld C-UAS  By Oishee Majumdar |  IG Defence will supply its IG T-Shul Pulse handheld C-UAS (pictured) to the Indian Army and the Navy. (IG Defence)  The Indian Army and the Navy have each awarded a contract to Noida-based IG Defence to procure an undisclosed number of units of a counter-unmanned aircraft system (C-UAS).  Speaking to Janes, senior vice-president at IG Defence Major General R C Padhi (retd)...</t>
         </is>
       </c>
     </row>
@@ -5556,30 +5285,30 @@
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Lockheed wins RAAF C-130J training systems upgrade contract - FlightGlobal</t>
+          <t>VODCAST: Karl Robin Joakim Landholm, SVP, Commercial and Operations Development, SKF - Manufacturing Today India</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/fixed-wing/lockheed-wins-raaf-c-130j-training-systems-upgrade-contract/166370.article</t>
+          <t>https://www.manufacturingtodayindia.com/videos/vodcast-karl-robin-joakim-landholm-svp-commercial-and-operations-development-skf</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>flightglobal.com</t>
+          <t>manufacturingtodayindia.com</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>Thu, 19 Feb 2026 08:59:03 GMT</t>
+          <t>Thu, 02 Apr 2026 06:40:37 GMT</t>
         </is>
       </c>
       <c r="F134" s="8" t="n">
-        <v>0.0074</v>
+        <v>0.0626</v>
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>2026-02-19T02:32:00Z By Ryan Finnerty    Uruguay has taken delivery of the first two of six Embraer A-29 Super Tucano light attack turboprops ordered to replace its ageing fleet of Cessna A-37 Dragonfly jets, which average over 43 years in service.  News    ### India approves INR3.6 trillion arms package including Rafales, P-8Is    2026-02-13T03:31:00Z By Greg Waldron    India’s Defence Acquisition Council has approved INR3.6 trillion ($39.7 billion) in military purchases, including Dassault Avi...</t>
+          <t>A candid conversation on India’s rising role in SKF’s global ecosystem, Industry 4.0 in action, and the road to net-zero operations by 2030. A must-watch for anyone tracking industrial transformation in Asia and beyond.  Posted inAerospace &amp; Defence  ## HAL-IAF review Tejas Mk1A delays as induction timeline hinges on key trials  Posted inMaterials &amp; Components  ## Gulf war disrupts Firozabad glass industry as output falls 40% amid gas shortages  Posted inAutomotive &amp; Transportation  ## Royal Enf...</t>
         </is>
       </c>
     </row>
@@ -5589,30 +5318,30 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>IACMI Workforce Development Program Advances Talent Pipeline for Manufacturing Industry - Modern Machine Shop</t>
+          <t>Feature: UK submarine production faces uphill climb - Janes</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>https://www.mmsonline.com/news/iacmi-workforce-development-program-advances-talent-pipeline-for-manufacturing-industry-</t>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/feature-uk-submarine-production-faces-uphill-climb</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>mmsonline.com</t>
+          <t>janes.com</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>Fri, 20 Mar 2026 04:43:51 GMT</t>
+          <t>Wed, 18 Mar 2026 14:22:44 GMT</t>
         </is>
       </c>
       <c r="F135" s="11" t="n">
-        <v>0.0064</v>
+        <v>0.0473</v>
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
-          <t>##### Featured Content   View More  ##### Featured Videos   View More  VISIT SITE   VISIT SHOWROOM  #### Phillips Corporation  ##### Featured Content   View More  Source: IACMI  IACMI – The Composites Institute announces its manufacturing and machining workforce training program, America’s Cutting Edge (ACE), has surpassed 20,000 online students and 5,000 in-person bootcamp participants. Since its launch in 2020, ACE has grown steadily each year, reaching a record number of enrollments in 2025....</t>
+          <t>The UK Ministry of Defence (MoD) awarded the original Astute prime contract in March 1997. As of February 2026 only five of the seven submarines had left the BAE Systems Submarines' facility in Barrow-in-Furness, northwest England. Of the two still to depart, HMS Agamemnon was in the test and commissioning berth and planned to exit for sea trials during 2026; the final boat, Achilles , remained in the Devonshire Dock Hall (DDH) assembly building. Its final delivery date remained uncertain follow...</t>
         </is>
       </c>
     </row>
@@ -5622,30 +5351,30 @@
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>IACMI Workforce Development Program advances talent pipeline for manufacturing industry - CompositesWorld</t>
+          <t>Jindal Stainless Q3 FY26 revenue up 6%, PAT rises 27% - Manufacturing Today India</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>https://www.compositesworld.com/news/iacmi-workforce-development-program-advances-talent-pipeline-for-manufacturing-industry--3</t>
+          <t>https://www.manufacturingtodayindia.com/jindal-stainless-q3-fy26-revenue-up</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>compositesworld.com</t>
+          <t>manufacturingtodayindia.com</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 00:54:46 GMT</t>
+          <t>Thu, 22 Jan 2026 08:05:09 GMT</t>
         </is>
       </c>
       <c r="F136" s="8" t="n">
-        <v>0.005</v>
+        <v>0.028</v>
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t>Joby 2025 financial results show strong liquidity, supporting near-term eVTOL launch plans  Cutting/Kitting    Laser tech investment builds up Web Industries’ Denton production capacity  Sustainability    Composites sustainability wins: ISO 14001 certification, Platinum EcoVadis rating, emissions reports  Published  # IACMI Workforce Development Program advances talent pipeline for manufacturing industry  America’s Cutting Edge (ACE) eclipses 20,000 online students and 5,000 in-person participan...</t>
+          <t>1.   Other developments: JSL introduced advanced stainless steel grades for a sustainable Salt Tipper Trailer and launched its first fabrication unit in Mumbai focusing on critical infrastructure components, and through its strategic arm Jindal Defence and Aerospace (JDA), secured orders for alloys for India’s Gaganyaan manned spaceship. JDA also established an Electro Slag Remelting facility for high-performance alloys.  1.   Category awareness and skill development: JSL trained over 9,500 fabr...</t>
         </is>
       </c>
     </row>
@@ -5655,35 +5384,3434 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
+          <t>Roketsan opens new missile production facilities - Janes</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/roketsan-opens-new-missile-production-facilities</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>Fri, 10 Apr 2026 23:53:17 GMT</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="G137" s="11" t="inlineStr">
+        <is>
+          <t>Read Article  Defence  ### Mali takes delivery of short-range air defence systems  Read Article  ## See how Janes delivers verified defence intelligence for faster, safer decisions   The world's most complete foundational military data asset.  500,000+ analyst hours per year to keep data current.  Easy integration into high and low-side environments. [...] Subscribe to Janes  ## Discover how Janes can support your mission  ### Solutions for defence  Delivering trusted intelligence to warfighters...</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="8" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="8" t="inlineStr">
+        <is>
+          <t>MRO Industry Rolling Daily Updates (February 2026) - Aviation Week Network</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>https://aviationweek.com/mro/mro-industry-rolling-daily-updates-february-2026</t>
+        </is>
+      </c>
+      <c r="D138" s="8" t="inlineStr">
+        <is>
+          <t>aviationweek.com</t>
+        </is>
+      </c>
+      <c r="E138" s="8" t="inlineStr">
+        <is>
+          <t>Mon, 02 Feb 2026 09:39:49 GMT</t>
+        </is>
+      </c>
+      <c r="F138" s="8" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="G138" s="8" t="inlineStr">
+        <is>
+          <t>Skip to main content  ## Share  # MRO Industry Rolling Daily Updates (February 2026)  ## Share  Aviation Week Network Staff February 02, 2026  February 02, 2026  GATES SPAH Adds New Leap Services  GA Telesis Engine Services’ (GATES) Specialized Procedures Aeroengine Hospital (SPAH) in Wilmington, Ohio, is introducing third-party return and recertification, borescope and preservation services for CFM International Leap-1A and -1B engines. The SPAH will also now start offering reverse bleed system...</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="11" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>Singapore Airshow 2026: KAI moves to boost Malaysia's FA-50 package with proposed AMRAAM integration - janes.com</t>
+        </is>
+      </c>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/industry/singapore-airshow-2026-kai-moves-to-boost-malaysias-fa-50-package-with-proposed-amraam-integration</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>Fri, 06 Feb 2026 08:50:47 GMT</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>0.0041</v>
+      </c>
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>Read Article  C4iSR  ### US Army sets technology goals for IDX 2026  Read Article  Industry  ### Sig Sauer to begin flight tests of armed UAS quadcopter  Read Article  ## See how Janes delivers verified defence intelligence for faster, safer decisions   The world's most complete foundational military data asset.  500,000+ analyst hours per year to keep data current.  Easy integration into high and low-side environments. [...] Malaysia's first 18 FA‑50 Block 20s will be equipped with Raytheon's P...</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="8" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="8" t="inlineStr">
+        <is>
+          <t>Tytan Technologies and Hensoldt sign MoU for C-UAS development - Janes</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/security/tytan-technologies-and-hensoldt-sign-mou-for-c-uas-development</t>
+        </is>
+      </c>
+      <c r="D140" s="8" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E140" s="8" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 14:53:24 GMT</t>
+        </is>
+      </c>
+      <c r="F140" s="8" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="G140" s="8" t="inlineStr">
+        <is>
+          <t>### Solutions for the intelligence community  Providing mission users with faster access to quality data to pre-empt threats and protect national security.  ### Describe the operating environment  A trusted holistic view of threat, stability, and capability across the globe.  ### Inform decision making  Assured interconnected OSINT to deliver informed, accurate, and reliable mission intelligence.  ### More news articles  Air  ### Eurofighter marks one million flight hour milestone  Read Article...</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="11" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="11" t="inlineStr">
+        <is>
+          <t>AerSale Grows South Florida Aerostructures MRO Capacity - Aviation Week Network</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>https://aviationweek.com/mro/aircraft-propulsion/aersale-grows-south-florida-aerostructures-mro-capacity</t>
+        </is>
+      </c>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>aviationweek.com</t>
+        </is>
+      </c>
+      <c r="E141" s="11" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 16:07:24 GMT</t>
+        </is>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>0.9958</v>
+      </c>
+      <c r="G141" s="11" t="inlineStr">
+        <is>
+          <t>The company has moved to a new, expanded facility in Hialeah Gardens, between Miami International Airport and Fort Lauderdale-Hollywood International Airport. The 90,000-ft.2 facility is approximately three times the size of its previous aerostructures MRO location in Medley. AerSale says the new facility will significantly increase its throughput and expand its capabilities for larger components.  The facility features a new heating oven, paint booth and sanding booth, which can accommodate lar...</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="8" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="8" t="inlineStr">
+        <is>
+          <t>Industry reactions to Union Budget 2026-27 - Manufacturing Today India</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="inlineStr">
+        <is>
+          <t>https://www.manufacturingtodayindia.com/industry-reactions-to-union-budget-2026</t>
+        </is>
+      </c>
+      <c r="D142" s="8" t="inlineStr">
+        <is>
+          <t>manufacturingtodayindia.com</t>
+        </is>
+      </c>
+      <c r="E142" s="8" t="inlineStr">
+        <is>
+          <t>Sun, 01 Feb 2026 18:05:02 GMT</t>
+        </is>
+      </c>
+      <c r="F142" s="8" t="n">
+        <v>0.7249</v>
+      </c>
+      <c r="G142" s="8" t="inlineStr">
+        <is>
+          <t>The tabling of the Union Budget 2026–27 has elicited a broad spectrum of responses from industry leaders across manufacturing, infrastructure, energy, logistics, chemicals, and technology. Industry leaders have characterised the fiscal roadmap as a “definitive statement of intent,” emphasising the government’s unwavering commitment to infrastructure-led growth, manufacturing depth, and sustainable development. Key highlights such as the India Semiconductor Mission 2.0, the ₹10,000 crore MSME Gro...</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="11" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t>Design Flaws in B-21 Raider? China Claims Its Software Exposed Issues in U.S. $203B Stealth Bomber – Reality Check - EurAsian Times</t>
+        </is>
+      </c>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>https://www.eurasiantimes.com/design-flaws-in-b-21-raider-china/</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>eurasiantimes.com</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 15:24:48 GMT</t>
+        </is>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>0.6549</v>
+      </c>
+      <c r="G143" s="11" t="inlineStr">
+        <is>
+          <t>“PADJ-X, which boasts full intellectual property rights, integrates five major disciplines: aerodynamics, propulsion, electromagnetics, infrared signature, and sonic boom. It enables comprehensive optimisation of aircraft aerodynamic configurations,” the Hong Kong-based South China Morning Post reported, quoting the paper.  Similarly, the team ran simulations on the US Navy’s X-47B stealth drone, which was cancelled in 2015 but remains classified, like the B-21.  The paper claimed that the PADJ-...</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="8" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t>Submarine maker TKMS hits record $22 billion order backlog, raises sales outlook - Reuters</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>https://www.reuters.com/business/submarine-maker-tkms-raises-sales-outlook-hits-new-high-order-backlog-2026-02-11/</t>
+        </is>
+      </c>
+      <c r="D144" s="8" t="inlineStr">
+        <is>
+          <t>reuters.com</t>
+        </is>
+      </c>
+      <c r="E144" s="8" t="inlineStr">
+        <is>
+          <t>Wed, 11 Feb 2026 07:42:57 GMT</t>
+        </is>
+      </c>
+      <c r="F144" s="8" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="G144" s="8" t="inlineStr">
+        <is>
+          <t>Like many of its peers, TKMS has been riding a surge in investor demand for shares in defence companies triggered by the war in Ukraine as well as U.S. pressure on Europe to step up its military capabilities.  Get a daily digest of breaking business news straight to your inbox with the Reuters Business newsletter. Sign up here.  Advertisement · Scroll to continue  That boost was among former parent Thyssenkrupp's (TKAG.DE), opens new tab primary motivations for spinning off TKMS last year, allow...</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="11" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="11" t="inlineStr">
+        <is>
+          <t>India progresses ramjet booster testing for air-to-air missile - Janes</t>
+        </is>
+      </c>
+      <c r="C145" s="12" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/india-progresses-ramjet-booster-testing-for-air-to-air-missile</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 08:51:03 GMT</t>
+        </is>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="G145" s="11" t="inlineStr">
+        <is>
+          <t>skip to main content  Search Janes  # India progresses ramjet booster testing for air-to-air missile  By Akhil Kadidal |  India's Solid Fuel Ducted Ramjet technology is intended to power the country's long-range Astra Mk III air-to-air missile. (DRDO)  India's Defence Research &amp; Development Organisation (DRDO) has again test flown its Solid Fuel Ducted Ramjet (SFDR) technology, which is to be integrated into the country's Astra Mk III long-range air-to-air missile programme.  The test flight was...</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="8" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="8" t="inlineStr">
+        <is>
+          <t>‘Some countries have monopolized them’: G Kishan Reddy eyes self-reliance in critical minerals; says rare - Times of India</t>
+        </is>
+      </c>
+      <c r="C146" s="9" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/business/india-business/some-countries-have-monopolized-them-g-kishan-reddy-eyes-self-reliance-in-critical-minerals-says-rareearth-permanent-magnet-production-by-year-end/articleshow/128551300.cms</t>
+        </is>
+      </c>
+      <c r="D146" s="8" t="inlineStr">
+        <is>
+          <t>timesofindia.indiatimes.com</t>
+        </is>
+      </c>
+      <c r="E146" s="8" t="inlineStr">
+        <is>
+          <t>Thu, 19 Feb 2026 09:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="F146" s="8" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="G146" s="8" t="inlineStr">
+        <is>
+          <t>Stressing on the importance of self-reliance, Union Minister of Mines and Coal G Kishan Reddy on Thursday said that India aims to begin domestic production of rare earth permanent magnets by year-end through collaboration with private industry.Reddy stressed on the strategic significance of critical minerals for India’s economic progress and geopolitical standing, urging coordinated efforts to safeguard supply chains.Reddy said the ministry, along with a state-owned enterprise, has developed the...</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="11" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="11" t="inlineStr">
+        <is>
+          <t>UK's Windracers to establish T&amp;E, MRO facility in Ukraine by January 2027 - Janes</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/air/uks-windracers-to-establish-te-mro-facility-in-ukraine-by-january-2027</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E147" s="11" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 15:53:20 GMT</t>
+        </is>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="G147" s="11" t="inlineStr">
+        <is>
+          <t>Air  ### France orders VSR700 unmanned helicopters  Read Article  Air  ### China Coast Guard acquires Wing Loong-2 UAVs  Read Article  ## See how Janes delivers verified defence intelligence for faster, safer decisions   The world's most complete foundational military data asset.  500,000+ analyst hours per year to keep data current.  Easy integration into high and low-side environments. [...] Subscribe to Janes  ## Discover how Janes can support your mission  ### Solutions for defence  Deliveri...</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="8" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="8" t="inlineStr">
+        <is>
+          <t>Shield AI to supply V-BAT drones to Indian Army - Army Technology</t>
+        </is>
+      </c>
+      <c r="C148" s="9" t="inlineStr">
+        <is>
+          <t>https://www.army-technology.com/news/indian-army-shieldai-drones/</t>
+        </is>
+      </c>
+      <c r="D148" s="8" t="inlineStr">
+        <is>
+          <t>army-technology.com</t>
+        </is>
+      </c>
+      <c r="E148" s="8" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 17:55:46 GMT</t>
+        </is>
+      </c>
+      <c r="F148" s="8" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="G148" s="8" t="inlineStr">
+        <is>
+          <t>##### Go deeper with GlobalData  The gold standard of business intelligence.  Find out more  #### Discover B2B Marketing That Performs  Combine business intelligence and editorial excellence to reach engaged professionals across 36 leading media platforms.  Find out more  Shield AI stated that the SDK will allow selected partners in India to build autonomous solutions suited for local requirements.  The Hivemind software enables platforms to sense, decide, and act autonomously, adapting to chang...</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="11" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="11" t="inlineStr">
+        <is>
+          <t>GA-ASI Pauses Flight Ops Following YFQ-42A CCA Test Incident &amp; Investigation Launch - Unmanned Systems Technology</t>
+        </is>
+      </c>
+      <c r="C149" s="12" t="inlineStr">
+        <is>
+          <t>https://www.unmannedsystemstechnology.com/2026/04/ga-asi-pauses-flight-ops-following-yfq-42a-cca-test-incident-investigation-launch/</t>
+        </is>
+      </c>
+      <c r="D149" s="11" t="inlineStr">
+        <is>
+          <t>unmannedsystemstechnology.com</t>
+        </is>
+      </c>
+      <c r="E149" s="11" t="inlineStr">
+        <is>
+          <t>Wed, 08 Apr 2026 05:09:00 GMT</t>
+        </is>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G149" s="11" t="inlineStr">
+        <is>
+          <t>Share this  Posted by Olivia Hannam Olivia is a Junior Editor and Copywriter at Unmanned Systems Technology. She graduated with First-Class Honours in History from the University of Exeter, where she developed a passion for research and clear communication. Since joining UST in 2025, Olivia’s focus lies in creating well-crafted content that highlights the latest innovations and technologies shaping the unmanned sector. Connect   E:  T:  LinkedIn  General Atomics Aeronautical Systems, Inc  Leadin...</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="8" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="8" t="inlineStr">
+        <is>
+          <t>India unveils ground-based directed energy weapon - Janes</t>
+        </is>
+      </c>
+      <c r="C150" s="9" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/india-unveils-ground-based-directed-energy-weapon</t>
+        </is>
+      </c>
+      <c r="D150" s="8" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E150" s="8" t="inlineStr">
+        <is>
+          <t>Wed, 21 Jan 2026 11:21:39 GMT</t>
+        </is>
+      </c>
+      <c r="F150" s="8" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="G150" s="8" t="inlineStr">
+        <is>
+          <t>Read Article  Weapons  ### IAV 2026: Ajax Nemo mortar carrier unveiled  Read Article  ## See how Janes delivers verified defence intelligence for faster, safer decisions   The world's most complete foundational military data asset.  500,000+ analyst hours per year to keep data current.  Easy integration into high and low-side environments. [...] “Our goal is to achieve a kill range of up to 5 km,” the project member added. “The plan is to conclude all testing by June 2026.”  According to informa...</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="11" t="inlineStr">
+        <is>
+          <t>MTU snaps UAV engine maker AeroDesignWorks - FlightGlobal</t>
+        </is>
+      </c>
+      <c r="C151" s="12" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/archive/2026/04/mtu-snaps-uav-engine-maker-aerodesignworks/</t>
+        </is>
+      </c>
+      <c r="D151" s="11" t="inlineStr">
+        <is>
+          <t>flightglobal.com</t>
+        </is>
+      </c>
+      <c r="E151" s="11" t="inlineStr">
+        <is>
+          <t>Wed, 08 Apr 2026 14:07:50 GMT</t>
+        </is>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="G151" s="11" t="inlineStr">
+        <is>
+          <t>#### Author: Dominic Perry  Dominic Perry is Aerospace Editor, Europe contributing extensively to flightglobal.com. Although specialising in the coverage of the helicopter industry, he has written on most topics in aerospace – be they commercial, defence or business aviation. In addition, there has been an increasing focus on the decarbonisation of the industry and zero-emission flight initiatives. He also helps to edit Flight International.  E-mail  ### Related posts  BAE Systems test fires APK...</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="8" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="8" t="inlineStr">
+        <is>
+          <t>Capital goods: 4 stocks converting record orders into real profits - The Financial Express</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>https://www.financialexpress.com/market/stock-insights/capital-goods-4-stocks-converting-record-orders-into-real-profits/4118250/</t>
+        </is>
+      </c>
+      <c r="D152" s="8" t="inlineStr">
+        <is>
+          <t>financialexpress.com</t>
+        </is>
+      </c>
+      <c r="E152" s="8" t="inlineStr">
+        <is>
+          <t>Sun, 25 Jan 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F152" s="8" t="n">
+        <v>0.1766</v>
+      </c>
+      <c r="G152" s="8" t="inlineStr">
+        <is>
+          <t>#1 Larsen &amp; Toubro: Massive Order Book vs. Execution Lag  Larsen &amp; Toubro (L&amp;T) is a multinational conglomerate which is primarily engaged in providing engineering, procurement and construction (EPC) solutions in key sectors such as infrastructure, hydrocarbon, power, process industries and defence, information technology, and financial services in domestic and international markets.  Larsen &amp; Toubro reported a steady Q2 FY26, with execution holding up across most businesses.  Consolidated reven...</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="11" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="11" t="inlineStr">
+        <is>
+          <t>Rolls-Royce Begins Next Trent 1000 Upgrade Phase - Aviation Week Network</t>
+        </is>
+      </c>
+      <c r="C153" s="12" t="inlineStr">
+        <is>
+          <t>https://aviationweek.com/air-transport/aircraft-propulsion/rolls-royce-begins-next-trent-1000-upgrade-phase</t>
+        </is>
+      </c>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>aviationweek.com</t>
+        </is>
+      </c>
+      <c r="E153" s="11" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 11:37:20 GMT</t>
+        </is>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="G153" s="11" t="inlineStr">
+        <is>
+          <t>Market Sector    + Aerospace   + Air Transport   + MRO   + Defense   + Space   + Business Aviation  Markets [...] “The advantage that Phase 1 gives us is a 40% increase in the cooling flow,” says Rachel Walker, Trent 1000 program director. “Our experience on that so far on the Trent 7000 is we're seeing up to triple the time on wing for some of our high-pressure (HP) turbine blades, which is really encouraging. As of year-end in 2025 we'd already rolled 50 of our engines through the fleet, so th...</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="8" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="8" t="inlineStr">
+        <is>
+          <t>Singapore Signals Aero Ambitions With RTX, Rolls-Royce Pacts - Aviation Week Network</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>https://aviationweek.com/aerospace/aircraft-propulsion/singapore-signals-aero-ambitions-rtx-rolls-royce-pacts</t>
+        </is>
+      </c>
+      <c r="D154" s="8" t="inlineStr">
+        <is>
+          <t>aviationweek.com</t>
+        </is>
+      </c>
+      <c r="E154" s="8" t="inlineStr">
+        <is>
+          <t>Tue, 03 Feb 2026 07:37:30 GMT</t>
+        </is>
+      </c>
+      <c r="F154" s="8" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="G154" s="8" t="inlineStr">
+        <is>
+          <t>The agreements also include the addition of new production capabilities and added MRO expansion at Pratt sites on the island. As part of its ongoing efforts to ramp PW1000G geared turbofan MRO capacity around the world, Pratt says it will add capabilities to service the engine’s fan drive gear system at its Seletar facility. The company’s thermal coating capability in Tuas will also be expanded.  Rolls-Royce’s Singapore and Solutions Asia units have meanwhile signed an MOU with the EDB “to explo...</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="11" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="11" t="inlineStr">
+        <is>
+          <t>Airbus closes on key milestones for A380 flying testbed as COMPANION project nears design freeze - FlightGlobal</t>
+        </is>
+      </c>
+      <c r="C155" s="12" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/engines/airbus-closes-on-key-milestones-for-a380-flying-testbed-as-companion-project-nears-design-freeze/166018.article</t>
+        </is>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>flightglobal.com</t>
+        </is>
+      </c>
+      <c r="E155" s="11" t="inlineStr">
+        <is>
+          <t>Wed, 21 Jan 2026 18:53:10 GMT</t>
+        </is>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="G155" s="11" t="inlineStr">
+        <is>
+          <t>The superjumbo will also make its first flight post-modification with four Trent 900s installed as Airbus seeks to capture baseline performance data prior to embarking on the RISE tests.  “Then we will be able to compare, back to back, the demonstrator configuration versus the reference,” says Perrin Decroux.  Dominic Perry   Follow  Dominic Perry is Aerospace Editor, Europe contributing extensively to flightglobal.com. Although specialising in the coverage of the helicopter industry, he has wri...</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="8" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="8" t="inlineStr">
+        <is>
+          <t>Sonair to debut ultrasonic 3D sensor at Modex event - Robotics &amp; Automation News</t>
+        </is>
+      </c>
+      <c r="C156" s="9" t="inlineStr">
+        <is>
+          <t>https://roboticsandautomationnews.com/2026/03/26/sonair-to-debut-ultrasonic-3d-sensor-at-modex-event/100148/</t>
+        </is>
+      </c>
+      <c r="D156" s="8" t="inlineStr">
+        <is>
+          <t>roboticsandautomationnews.com</t>
+        </is>
+      </c>
+      <c r="E156" s="8" t="inlineStr">
+        <is>
+          <t>Thu, 26 Mar 2026 08:41:47 GMT</t>
+        </is>
+      </c>
+      <c r="F156" s="8" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="G156" s="8" t="inlineStr">
+        <is>
+          <t>Key technical advantages include:   Full 180° x 180° field of view: Provides total spatial awareness to eliminate blind spots.  Enhanced operational uptime: By detecting obstacles at all heights and reducing “false positives” from environmental factors, the sensor minimizes unnecessary stops.  Safe human-robot interaction: Designed specifically for dynamic environments where humans and autonomous mobile robots (AMRs) must share space closely and safely.  Privacy-first operation in secure environ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="11" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="11" t="inlineStr">
+        <is>
+          <t>GKN Aerospace delivers first upgraded Gripen engine to Swedish Armed Forces - Janes</t>
+        </is>
+      </c>
+      <c r="C157" s="12" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/gkn-aerospace-delivers-first-upgraded-gripen-engine-to-swedish-armed-forces</t>
+        </is>
+      </c>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E157" s="11" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 14:21:14 GMT</t>
+        </is>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G157" s="11" t="inlineStr">
+        <is>
+          <t>### More news articles  Defence  ### GKN Aerospace delivers first upgraded Gripen engine to Swedish Armed Forces  Read Article  Defence  ### First production KF-21 rolled out  Read Article  Defence  ### US officials tout USS Nimitz presence in Southern Command for Western Hemisphere defence  Read Article  ## See how Janes delivers verified defence intelligence for faster, safer decisions   The world's most complete foundational military data asset.  500,000+ analyst hours per year to keep data c...</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="8" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="8" t="inlineStr">
+        <is>
+          <t>Liebherr-Aerospace Plans Lindenberg MRO Expansion - Aviation Week</t>
+        </is>
+      </c>
+      <c r="C158" s="9" t="inlineStr">
+        <is>
+          <t>https://aviationweek.com/mro/aircraft-propulsion/liebherr-aerospace-plans-lindenberg-mro-expansion</t>
+        </is>
+      </c>
+      <c r="D158" s="8" t="inlineStr">
+        <is>
+          <t>aviationweek.com</t>
+        </is>
+      </c>
+      <c r="E158" s="8" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 11:55:19 GMT</t>
+        </is>
+      </c>
+      <c r="F158" s="8" t="n">
+        <v>0.9983</v>
+      </c>
+      <c r="G158" s="8" t="inlineStr">
+        <is>
+          <t>Market Sector    + Aerospace   + Air Transport   + MRO   + Defense   + Space   + Business Aviation  Markets [...] As part of its expansion plans, Toulouse-headquartered Liebherr will increase its facility by around 65,000 ft.2 by expanding customer service and assembly areas linked to repair and refurbishment throughput. At Lindenberg, located in Allgau in Germany’s Bavaria region, the company repairs landing gear systems, flight control and actuation systems, air management systems, and deploys...</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="11" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="11" t="inlineStr">
+        <is>
+          <t>India moves to build 1,000-kg bombs as IAF pushes for self-reliance in heavy munitions - Firstpost</t>
+        </is>
+      </c>
+      <c r="C159" s="12" t="inlineStr">
+        <is>
+          <t>https://www.firstpost.com/india/india-moves-to-build-1000-kg-bombs-as-iaf-pushes-for-self-reliance-in-heavy-munitions-ws-e-13996599.html</t>
+        </is>
+      </c>
+      <c r="D159" s="11" t="inlineStr">
+        <is>
+          <t>firstpost.com</t>
+        </is>
+      </c>
+      <c r="E159" s="11" t="inlineStr">
+        <is>
+          <t>Sat, 04 Apr 2026 13:23:37 GMT</t>
+        </is>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="G159" s="11" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh ATS arrested four men linked to Pakistan-based handlers, foiling a terror plot targeting railway and sensitive sites. The accused, motivated by money, conducted reconnaissance and sent videos to handlers. Further investigation is ongoing.More Quick Reads  ### Top Stories  #### Iran Israel War Live News: Iran deploys new air defence system to counter US jets; vows 'full' control over airspace  #### Hide, move, survive: How US fighter pilots are trained to avoid capture in enemy terr...</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="8" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="8" t="inlineStr">
+        <is>
+          <t>New shipbuilding entrants secure US navy work commitments - Janes</t>
+        </is>
+      </c>
+      <c r="C160" s="9" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/industry/new-shipbuilding-entrants-secure-us-navy-work-commitments</t>
+        </is>
+      </c>
+      <c r="D160" s="8" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E160" s="8" t="inlineStr">
+        <is>
+          <t>Thu, 02 Apr 2026 13:55:01 GMT</t>
+        </is>
+      </c>
+      <c r="F160" s="8" t="n">
+        <v>0.09950000000000001</v>
+      </c>
+      <c r="G160" s="8" t="inlineStr">
+        <is>
+          <t>Get full access to validated equipment, military capabilities, and market insights.  Subscribe to Janes  ## Discover how Janes can support your mission  ### Solutions for defence  Delivering trusted intelligence to warfighters to protect national interests, support readiness, and deter aggression.  ### Solutions for the intelligence community  Providing mission users with faster access to quality data to pre-empt threats and protect national security.  ### Describe the operating environment  A t...</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="11" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="11" t="inlineStr">
+        <is>
+          <t>Feature: Zen Technologies expands beyond simulators into C-UAS, weapons, and robotics - Janes</t>
+        </is>
+      </c>
+      <c r="C161" s="12" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/feature-zen-technologies-expands-beyond-simulators-into-c-uas-weapons-and-robotics</t>
+        </is>
+      </c>
+      <c r="D161" s="11" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E161" s="11" t="inlineStr">
+        <is>
+          <t>Fri, 20 Mar 2026 10:21:22 GMT</t>
+        </is>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="G161" s="11" t="inlineStr">
+        <is>
+          <t>As part of this push, the company is developing new systems and upgrading existing products with the intent to offer increasingly advanced capabilities to the Indian military and foreign customers. These include remote weapon stations (RWSs), a micro-missile launcher, a naval counter-unmanned aerial systems (C-UASs), and artificial-intelligence (AI)-based shooting ranges.  To facilitate the diversification of its product portfolio, Zen Technologies has recently acquired several companies. These...</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="8" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="8" t="inlineStr">
+        <is>
+          <t>Eurofighter, NETMA formally launch Aerodynamic Modification Kit - Janes</t>
+        </is>
+      </c>
+      <c r="C162" s="9" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/eurofighter-netma-formally-launch-aerodynamic-modification-kit</t>
+        </is>
+      </c>
+      <c r="D162" s="8" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E162" s="8" t="inlineStr">
+        <is>
+          <t>Thu, 05 Feb 2026 14:10:04 GMT</t>
+        </is>
+      </c>
+      <c r="F162" s="8" t="n">
+        <v>0.0268</v>
+      </c>
+      <c r="G162" s="8" t="inlineStr">
+        <is>
+          <t>Read Article  Defence  ### UK in ‘advanced' talks to sell remaining surplus Hercules airlifters  Read Article  ## See how Janes delivers verified defence intelligence for faster, safer decisions   The world's most complete foundational military data asset.  500,000+ analyst hours per year to keep data current.  Easy integration into high and low-side environments. [...] ## Discover how Janes can support your mission  ### Solutions for defence  Delivering trusted intelligence to warfighters to pr...</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="11" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="11" t="inlineStr">
+        <is>
+          <t>Allcargo logs highest-ever volumes in Q3, profit soars 28% - Manufacturing Today India</t>
+        </is>
+      </c>
+      <c r="C163" s="12" t="inlineStr">
+        <is>
+          <t>https://www.manufacturingtodayindia.com/allcargos-highest-ever-volumes</t>
+        </is>
+      </c>
+      <c r="D163" s="11" t="inlineStr">
+        <is>
+          <t>manufacturingtodayindia.com</t>
+        </is>
+      </c>
+      <c r="E163" s="11" t="inlineStr">
+        <is>
+          <t>Wed, 11 Feb 2026 04:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="G163" s="11" t="inlineStr">
+        <is>
+          <t>Allcargo logs highest-ever volumes in Q3, profit soars 28%   Close Search for:  Search     Products        Machinery &amp; Equipment        Software Solutions        Materials &amp; Components        Industrial Tools     Sectors        Aerospace &amp; Defence        Automotive &amp; Transportation        Electronics &amp; Semiconductors        Chemical &amp; Pharmaceuticals        Energy &amp; Utilities        Metals &amp; Mining        Engineering, Machinery &amp; Tooling        Automation &amp; Robotics        SCM &amp; Logistics...</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="8" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="8" t="inlineStr">
+        <is>
+          <t>Pratt &amp; Whitney wins follow-on AGM-190A engine contract - FlightGlobal</t>
+        </is>
+      </c>
+      <c r="C164" s="9" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/fixed-wing/pratt-and-whitney-wins-follow-on-agm-190a-engine-contract/166606.article</t>
+        </is>
+      </c>
+      <c r="D164" s="8" t="inlineStr">
+        <is>
+          <t>flightglobal.com</t>
+        </is>
+      </c>
+      <c r="E164" s="8" t="inlineStr">
+        <is>
+          <t>Wed, 11 Mar 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F164" s="8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="G164" s="8" t="inlineStr">
+        <is>
+          <t>The TJ150 is a one-stage turbojet generally for use in missiles and drones.  “Meeting today’s mission demands requires speed and reliable performance, and the TJ150 engine delivers on both,” says Jessica Villardi, vice president of Fighter and Mobility Programs at Pratt &amp; Whitney.  “The engine’s performance and availability make it an ideal fit for effectors, as it provides consistent thrust and supports seamless vehicle integration.”  weekly  ## Sign-up to the Defence Briefing  Dedicated weekly...</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="11" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="11" t="inlineStr">
+        <is>
+          <t>IFGL Refractories rises after plastic refractories manufacturing segment commences operations - Business Standard</t>
+        </is>
+      </c>
+      <c r="C165" s="12" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/markets/capital-market-news/ifgl-refractories-rises-after-plastic-refractories-manufacturing-segment-commences-operations-126022000241_1.html</t>
+        </is>
+      </c>
+      <c r="D165" s="11" t="inlineStr">
+        <is>
+          <t>business-standard.com</t>
+        </is>
+      </c>
+      <c r="E165" s="11" t="inlineStr">
+        <is>
+          <t>Fri, 20 Feb 2026 05:01:59 GMT</t>
+        </is>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="G165" s="11" t="inlineStr">
+        <is>
+          <t>TOP SECTIONS    Latest NewsCompany NewsMarket NewsIPO NewsCommodity NewsImmigration NewsCricket NewsPersonal FinanceTechnology NewsWorld NewsIndustry NewsEducation NewsOpinionHealth NewsEconomy NewsIndia NewsPolitics NewsBudget 2026     Today's PaperAbout UsT&amp;CPrivacy PolicyCookie PolicyDisclaimerInvestor CommunicationGST registration number ListComplianceContact UsAdvertise with UsSitemapSubscribeCareersBS Apps  Copyrights © 2026 Business Standard Private Ltd. All rights reserved  []( 47: Linke...</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="8" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="8" t="inlineStr">
+        <is>
+          <t>MBDA To ‘Intensify’ Production Output In 2026 - Aviation Week</t>
+        </is>
+      </c>
+      <c r="C166" s="9" t="inlineStr">
+        <is>
+          <t>https://aviationweek.com/defense/missile-defense-weapons/mbda-intensify-production-output-2026</t>
+        </is>
+      </c>
+      <c r="D166" s="8" t="inlineStr">
+        <is>
+          <t>aviationweek.com</t>
+        </is>
+      </c>
+      <c r="E166" s="8" t="inlineStr">
+        <is>
+          <t>Thu, 26 Mar 2026 17:35:32 GMT</t>
+        </is>
+      </c>
+      <c r="F166" s="8" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="G166" s="8" t="inlineStr">
+        <is>
+          <t>+ Services     - Advertising     - Marketing Services     - Fleet, Data &amp; APIs     - Research &amp; Consulting     - Network and Route Planning     - Marketplace  Store    + ## Market Sector [...] Market Sector    + Aerospace   + Air Transport   + MRO   + Defense   + Space   + Business Aviation  Markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="11" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="11" t="inlineStr">
+        <is>
+          <t>Russian regulator approves domestic composite fin and stabiliser for MC-21 - FlightGlobal</t>
+        </is>
+      </c>
+      <c r="C167" s="12" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/aerospace/russian-regulator-approves-domestic-composite-fin-and-stabiliser-for-mc-21/166298.article</t>
+        </is>
+      </c>
+      <c r="D167" s="11" t="inlineStr">
+        <is>
+          <t>flightglobal.com</t>
+        </is>
+      </c>
+      <c r="E167" s="11" t="inlineStr">
+        <is>
+          <t>Thu, 12 Feb 2026 10:23:06 GMT</t>
+        </is>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="G167" s="11" t="inlineStr">
+        <is>
+          <t>Certification of this import-substituted version of the MC-21 is still under way.  Russian transport minister Andrei Nikitin says the aircraft will “soon begin to be delivered to airlines” and enable them to establish operations that are “completely independent of foreign technology”.  ## Topics   Air Transport  Aircraft programmes  Airframers  Europe  ### Related articles   News    ### Lufthansa City Airlines opens services from Frankfurt hub    2026-02-12T09:37:00Z By David Kaminski-Morrow [.....</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="8" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="8" t="inlineStr">
+        <is>
+          <t>SNC, Specter Detail Low-Cost Plasma Ramjet Missile Plan - Aviation Week</t>
+        </is>
+      </c>
+      <c r="C168" s="9" t="inlineStr">
+        <is>
+          <t>https://aviationweek.com/defense/missile-defense-weapons/snc-specter-detail-low-cost-plasma-ramjet-missile-plan</t>
+        </is>
+      </c>
+      <c r="D168" s="8" t="inlineStr">
+        <is>
+          <t>aviationweek.com</t>
+        </is>
+      </c>
+      <c r="E168" s="8" t="inlineStr">
+        <is>
+          <t>Wed, 04 Mar 2026 01:08:42 GMT</t>
+        </is>
+      </c>
+      <c r="F168" s="8" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="G168" s="8" t="inlineStr">
+        <is>
+          <t>Market Sector    + Aerospace   + Air Transport   + MRO   + Defense   + Space   + Business Aviation  Markets [...] + Services     - Advertising     - Marketing Services     - Fleet, Data &amp; APIs     - Research &amp; Consulting     - Network and Route Planning     - Marketplace  Store    + ## Market Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="11" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="11" t="inlineStr">
+        <is>
+          <t>UK opts for efficiency and battlefield commonality over power in AW149 engine selection - Janes</t>
+        </is>
+      </c>
+      <c r="C169" s="12" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/uk-opts-for-efficiency-and-battlefield-commonality-over-power-in-aw149-engine-selection</t>
+        </is>
+      </c>
+      <c r="D169" s="11" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E169" s="11" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 22:38:11 GMT</t>
+        </is>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="G169" s="11" t="inlineStr">
+        <is>
+          <t>### More news articles  Defence  ### UK opts for efficiency and battlefield commonality over power in AW149 engine selection  Read Article  Defence  ### GKN Aerospace delivers first upgraded Gripen engine to Swedish Armed Forces  Read Article  Defence  ### First production KF-21 rolled out  Read Article  ## See how Janes delivers verified defence intelligence for faster, safer decisions   The world's most complete foundational military data asset.  500,000+ analyst hours per year to keep data cu...</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="8" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="8" t="inlineStr">
+        <is>
+          <t>India targets chip design self-reliance, eyes Indian MNC talent - Mint</t>
+        </is>
+      </c>
+      <c r="C170" s="9" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/industry/manufacturing/india-semiconductor-mission-critical-minerals-self-reliance-private-nuclear-defence-11772952324772.html</t>
+        </is>
+      </c>
+      <c r="D170" s="8" t="inlineStr">
+        <is>
+          <t>livemint.com</t>
+        </is>
+      </c>
+      <c r="E170" s="8" t="inlineStr">
+        <is>
+          <t>Mon, 09 Mar 2026 00:30:37 GMT</t>
+        </is>
+      </c>
+      <c r="F170" s="8" t="n">
+        <v>0.9917</v>
+      </c>
+      <c r="G170" s="8" t="inlineStr">
+        <is>
+          <t>Saraswat also said that in the past five to seven years, there has been significant emphasis on promoting defence equipment manufacturing within the private sector in India. This has led to the establishment of numerous aerospace and defence companies and the development of defence corridors. Private companies are now actively involved in major combat aircraft development programs.  “The growth of the private sector is expected to substantially increase indigenous production, thereby reducing ou...</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="11" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="11" t="inlineStr">
+        <is>
+          <t>India doubles down on state-backed venture capital, approving $1.1B fund - TechCrunch</t>
+        </is>
+      </c>
+      <c r="C171" s="12" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/02/14/india-doubles-down-on-state-backed-venture-capital-approving-1-1b-fund/</t>
+        </is>
+      </c>
+      <c r="D171" s="11" t="inlineStr">
+        <is>
+          <t>techcrunch.com</t>
+        </is>
+      </c>
+      <c r="E171" s="11" t="inlineStr">
+        <is>
+          <t>Sat, 14 Feb 2026 16:23:22 GMT</t>
+        </is>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="G171" s="11" t="inlineStr">
+        <is>
+          <t>First outlined in the January 2025 budget speech by India’s finance minister, the ₹100 billion fund won cabinet approval this week (more than a year after the speech), allowing the government to move ahead with deployment. A previous iteration of the program, launched in 2016, committed ₹100 billion to 145 private funds that have invested more than ₹255 billion (about $2.8 billion) in over 1,370 startups, according to official data released on Saturday. [...] At the announcement on Saturday, IT...</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="8" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="8" t="inlineStr">
+        <is>
+          <t>DIMDEX 2026: Kongsberg progressing networked CUI protection testbed - Janes</t>
+        </is>
+      </c>
+      <c r="C172" s="9" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/sea/dimdex-2026-kongsberg-progressing-networked-cui-protection-testbed</t>
+        </is>
+      </c>
+      <c r="D172" s="8" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E172" s="8" t="inlineStr">
+        <is>
+          <t>Wed, 21 Jan 2026 06:51:26 GMT</t>
+        </is>
+      </c>
+      <c r="F172" s="8" t="n">
+        <v>0.0722</v>
+      </c>
+      <c r="G172" s="8" t="inlineStr">
+        <is>
+          <t>### More news articles  Sea  ### DIMDEX 2026: Kongsberg progressing networked CUI protection testbed  Read Article  Sea  ### UMEX 2026: Al Seer Marine unveils Argos XL USV  Read Article  Security  ### IAV 2026: Leonardo DRS continuing work to extend Morpheus and Bowman capability  Read Article  ## See how Janes delivers verified defence intelligence for faster, safer decisions   The world's most complete foundational military data asset.  500,000+ analyst hours per year to keep data current.  Ea...</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="11" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="11" t="inlineStr">
+        <is>
+          <t>Angolan patrol boat production inaugurated - Janes</t>
+        </is>
+      </c>
+      <c r="C173" s="12" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/sea/angolan-patrol-boat-production-inaugurated</t>
+        </is>
+      </c>
+      <c r="D173" s="11" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E173" s="11" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 12:40:01 GMT</t>
+        </is>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>0.0313</v>
+      </c>
+      <c r="G173" s="11" t="inlineStr">
+        <is>
+          <t>CMN has delivered numerous vessels to the MGA since 2018, including DV15 and HSI32 interceptors, Ocean Eagle 43 long-range surveillance vessels, and most recently two LCT 200-70 landing ships. It is currently building the first of three BR71 Mk II corvettes for Angola as part of a collaboration with Abu Dhabi Shipbuilding (ADSB).  While Angop did not report what vessels will be produced at Lobinave, television news coverage of the event showed a mould for the DV15 in a new shed at the yard and a...</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="8" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="8" t="inlineStr">
+        <is>
+          <t>UK, US, set to seal vertical launcher deal for SSN-AUKUS submarine - janes.com</t>
+        </is>
+      </c>
+      <c r="C174" s="9" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/uk-us-set-to-seal-vertical-launcher-deal-for-ssn-aukus-submarine</t>
+        </is>
+      </c>
+      <c r="D174" s="8" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E174" s="8" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 20:22:22 GMT</t>
+        </is>
+      </c>
+      <c r="F174" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G174" s="8" t="inlineStr">
+        <is>
+          <t>### Solutions for defence  Delivering trusted intelligence to warfighters to protect national interests, support readiness, and deter aggression.  ### Solutions for the intelligence community  Providing mission users with faster access to quality data to pre-empt threats and protect national security.  ### Describe the operating environment  A trusted holistic view of threat, stability, and capability across the globe.  ### Inform decision making  Assured interconnected OSINT to deliver informed...</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="11" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="11" t="inlineStr">
+        <is>
+          <t>Pratt &amp; Whitney Gets Partial Exemption For PW4000 Redesign Approval - Aviation Week</t>
+        </is>
+      </c>
+      <c r="C175" s="12" t="inlineStr">
+        <is>
+          <t>https://aviationweek.com/air-transport/safety-ops-regulation/pratt-whitney-gets-partial-exemption-pw4000-redesign-approval</t>
+        </is>
+      </c>
+      <c r="D175" s="11" t="inlineStr">
+        <is>
+          <t>aviationweek.com</t>
+        </is>
+      </c>
+      <c r="E175" s="11" t="inlineStr">
+        <is>
+          <t>Fri, 03 Apr 2026 01:44:36 GMT</t>
+        </is>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>0.0142</v>
+      </c>
+      <c r="G175" s="11" t="inlineStr">
+        <is>
+          <t>Pratt in August 2025 asked the FAA for an exemption to the test for its modified engine design, proposing instead to use a model assuming a failure farther from the root, along the airfoil.  The FAA’s exemption says Pratt does not have to conduct new physical tests that the original design passed in 1994 during its certification program. But the manufacturer must use modeling to show its new design both corrects the unsafe conditions, including engine flange separation and fire, and meets Part 3...</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="8" t="inlineStr">
+        <is>
+          <t>Australian audit raises concerns over Land 400 Phase 3 programme - Janes</t>
+        </is>
+      </c>
+      <c r="C176" s="9" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/land/australian-audit-raises-concerns-over-land-400-phase-3-programme</t>
+        </is>
+      </c>
+      <c r="D176" s="8" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E176" s="8" t="inlineStr">
+        <is>
+          <t>Fri, 03 Apr 2026 06:07:01 GMT</t>
+        </is>
+      </c>
+      <c r="F176" s="8" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="G176" s="8" t="inlineStr">
+        <is>
+          <t>Get full access to validated equipment, military capabilities, and market insights.  Subscribe to Janes  ## Discover how Janes can support your mission  ### Solutions for defence  Delivering trusted intelligence to warfighters to protect national interests, support readiness, and deter aggression.  ### Solutions for the intelligence community  Providing mission users with faster access to quality data to pre-empt threats and protect national security.  ### Describe the operating environment  A t...</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="11" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="11" t="inlineStr">
+        <is>
+          <t>New funding programme aims to strengthen Brazilian defence industry - Janes</t>
+        </is>
+      </c>
+      <c r="C177" s="12" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/new-funding-programme-aims-to-strengthen-brazilian-defence-industry</t>
+        </is>
+      </c>
+      <c r="D177" s="11" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E177" s="11" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 04:10:12 GMT</t>
+        </is>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="G177" s="11" t="inlineStr">
+        <is>
+          <t>#### Go beyond the headlines — with direct links to interconnected entities  Get full access to validated equipment, military capabilities, and market insights.  Subscribe to Janes  ## Discover how Janes can support your mission  ### Solutions for defence  Delivering trusted intelligence to warfighters to protect national interests, support readiness, and deter aggression.  ### Solutions for the intelligence community  Providing mission users with faster access to quality data to pre-empt threat...</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="8" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="8" t="inlineStr">
+        <is>
+          <t>Decarbonising heavy industries: The role of sustainable steel manufacturing - Manufacturing Today India</t>
+        </is>
+      </c>
+      <c r="C178" s="9" t="inlineStr">
+        <is>
+          <t>https://www.manufacturingtodayindia.com/decarbonising-heavy-industries</t>
+        </is>
+      </c>
+      <c r="D178" s="8" t="inlineStr">
+        <is>
+          <t>manufacturingtodayindia.com</t>
+        </is>
+      </c>
+      <c r="E178" s="8" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 08:40:22 GMT</t>
+        </is>
+      </c>
+      <c r="F178" s="8" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="G178" s="8" t="inlineStr">
+        <is>
+          <t>### India’s growing steel demand and emissions challenge  India’s steel demand is expected to increase significantly over the coming decades as infrastructure, housing, renewable energy installations, and transport networks expand. Steel consumption in the country has already grown rapidly, reflecting the broader phase of industrialisation and urban development. However, the current production model relies heavily on coal-based blast furnaces, resulting in relatively high carbon intensity. The e...</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="11" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="11" t="inlineStr">
+        <is>
+          <t>Rheinmetall and Boeing partner MQ-28 Ghost Bat for Germany - Janes</t>
+        </is>
+      </c>
+      <c r="C179" s="12" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/air/rheinmetall-and-boeing-partner-mq-28-ghost-bat-for-germany</t>
+        </is>
+      </c>
+      <c r="D179" s="11" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E179" s="11" t="inlineStr">
+        <is>
+          <t>Thu, 02 Apr 2026 22:05:41 GMT</t>
+        </is>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="G179" s="11" t="inlineStr">
+        <is>
+          <t>### More news articles  Air  ### Rheinmetall and Boeing partner MQ-28 Ghost Bat for Germany  Read Article  C4iSR  ### Sweden signs air defence contracts to improve C-UAS capabilities  Read Article  Air  ### Russian company unveils new interceptor UAV  Read Article  ## See how Janes delivers verified defence intelligence for faster, safer decisions   The world's most complete foundational military data asset.  500,000+ analyst hours per year to keep data current.  Easy integration into high and l...</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="8" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="8" t="inlineStr">
+        <is>
+          <t>Poland eyes benefits of joining GCAP sixth-generation fighter project - Defense News</t>
+        </is>
+      </c>
+      <c r="C180" s="9" t="inlineStr">
+        <is>
+          <t>https://www.defensenews.com/global/europe/2026/03/23/poland-eyes-benefits-of-joining-gcap-sixth-generation-fighter-project/</t>
+        </is>
+      </c>
+      <c r="D180" s="8" t="inlineStr">
+        <is>
+          <t>defensenews.com</t>
+        </is>
+      </c>
+      <c r="E180" s="8" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar 2026 15:21:29 GMT</t>
+        </is>
+      </c>
+      <c r="F180" s="8" t="n">
+        <v>0.8933</v>
+      </c>
+      <c r="G180" s="8" t="inlineStr">
+        <is>
+          <t>“Over the past few months, I have spoken to representatives of the defense industries of both Italy and Japan,” Gołota said. “They are showing an understanding of our proposal, and willingness to have further talks.”  The discussions come amid a delay in the signing of a deal between the three countries, represented by the GCAP International Government Organisation (GIGO), and the Edgewing joint venture which represents national players Leonardo, BAE Systems, and Japan Aircraft Industrial Enhanc...</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="11" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="11" t="inlineStr">
+        <is>
+          <t>Trusted Development Tools for Mission- and Safety-Critical Drone Software - Unmanned Systems Technology</t>
+        </is>
+      </c>
+      <c r="C181" s="12" t="inlineStr">
+        <is>
+          <t>https://www.unmannedsystemstechnology.com/2026/03/trusted-development-tools-for-mission-and-safety-critical-drone-software/</t>
+        </is>
+      </c>
+      <c r="D181" s="11" t="inlineStr">
+        <is>
+          <t>unmannedsystemstechnology.com</t>
+        </is>
+      </c>
+      <c r="E181" s="11" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 13:52:43 GMT</t>
+        </is>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>0.8387</v>
+      </c>
+      <c r="G181" s="11" t="inlineStr">
+        <is>
+          <t>In addition to commercial UAV applications, AdaCore’s solutions support the development of defense-grade unmanned systems designed to operate in demanding and contested environments. The development toolkits enable the creation of resilient software capable of supporting AI-enabled systems, advanced sensors, and evolving mission requirements across platforms that may remain in service for decades.  To learn more about AdaCore’s trusted UAV software development solutions, visit their full profile...</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="8" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="8" t="inlineStr">
+        <is>
+          <t>India's budget - what is expected on debt, military, infrastructure? - Reuters</t>
+        </is>
+      </c>
+      <c r="C182" s="9" t="inlineStr">
+        <is>
+          <t>https://www.reuters.com/sustainability/boards-policy-regulation/indias-budget-what-is-expected-debt-military-infrastructure-2026-02-01/</t>
+        </is>
+      </c>
+      <c r="D182" s="8" t="inlineStr">
+        <is>
+          <t>reuters.com</t>
+        </is>
+      </c>
+      <c r="E182" s="8" t="inlineStr">
+        <is>
+          <t>Sun, 01 Feb 2026 00:34:48 GMT</t>
+        </is>
+      </c>
+      <c r="F182" s="8" t="n">
+        <v>0.4033</v>
+      </c>
+      <c r="G182" s="8" t="inlineStr">
+        <is>
+          <t>New Delhi is likely to ease conditions for foreign investments into defence units. The Federation of Indian Chambers of Commerce and Industry, which has 250,000 companies as members, has suggested setting up defence-industrial corridors and an export-promotion council to meet the country's defence-export target of $5.5 billion by 2029.  Advertisement · Scroll to continue  ## INFRASTRUCTURE SPENDING  Economists expect the government to maintain capital spending around 3.1% of GDP.  Income- and co...</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="11" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="11" t="inlineStr">
+        <is>
+          <t>Lockheed wins RAAF C-130J training systems upgrade contract - FlightGlobal</t>
+        </is>
+      </c>
+      <c r="C183" s="12" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/fixed-wing/lockheed-wins-raaf-c-130j-training-systems-upgrade-contract/166370.article</t>
+        </is>
+      </c>
+      <c r="D183" s="11" t="inlineStr">
+        <is>
+          <t>flightglobal.com</t>
+        </is>
+      </c>
+      <c r="E183" s="11" t="inlineStr">
+        <is>
+          <t>Thu, 19 Feb 2026 08:59:03 GMT</t>
+        </is>
+      </c>
+      <c r="F183" s="11" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="G183" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-19T02:32:00Z By Ryan Finnerty    Uruguay has taken delivery of the first two of six Embraer A-29 Super Tucano light attack turboprops ordered to replace its ageing fleet of Cessna A-37 Dragonfly jets, which average over 43 years in service.  News    ### India approves INR3.6 trillion arms package including Rafales, P-8Is    2026-02-13T03:31:00Z By Greg Waldron    India’s Defence Acquisition Council has approved INR3.6 trillion ($39.7 billion) in military purchases, including Dassault Avi...</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="8" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="8" t="inlineStr">
+        <is>
+          <t>Rolls-Royce teases UltraFan 30 features as demonstrator heads for design freeze - FlightGlobal</t>
+        </is>
+      </c>
+      <c r="C184" s="9" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/aerospace/rolls-royce-teases-ultrafan-30-features-as-demonstrator-heads-for-design-freeze/166474.article</t>
+        </is>
+      </c>
+      <c r="D184" s="8" t="inlineStr">
+        <is>
+          <t>flightglobal.com</t>
+        </is>
+      </c>
+      <c r="E184" s="8" t="inlineStr">
+        <is>
+          <t>Mon, 02 Mar 2026 07:50:53 GMT</t>
+        </is>
+      </c>
+      <c r="F184" s="8" t="n">
+        <v>0.2568</v>
+      </c>
+      <c r="G184" s="8" t="inlineStr">
+        <is>
+          <t>He also says that Rolls-Royce has a “large chest” of technologies which have come through from its work on the powerplant for the tri-national military Global Combat Air Programme.  “What gives you power density on a combat engine gives you fuel efficiency on a commercial engine,” says Burr. “And some of it’s about manufacturing techniques that enable interesting geometries from an airflow perspective, cooling geometry perspective, and so on.  “There’s a sort of synthesis of different things tha...</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="11" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="11" t="inlineStr">
+        <is>
+          <t>UK MoD contracts full production of ECRS Mk 2 radar for Typhoon - Janes</t>
+        </is>
+      </c>
+      <c r="C185" s="12" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/uk-mod-contracts-full-production-of-ecrs-mk-2-radar-for-typhoon</t>
+        </is>
+      </c>
+      <c r="D185" s="11" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E185" s="11" t="inlineStr">
+        <is>
+          <t>Thu, 22 Jan 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F185" s="11" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="G185" s="11" t="inlineStr">
+        <is>
+          <t>The world's most complete foundational military data asset.  500,000+ analyst hours per year to keep data current.  Easy integration into high and low-side environments. [...] “The contract follows a successful programme of development and testing, enabled through long-term UK investment, and marks a major step forward in the RAF's Typhoon capability,” BAE Systems said. “The state-of-the-art radar, known as the ECRS Mk 2, will deliver enhanced electronic warfare capability, allowing the aircraft...</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="8" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="8" t="inlineStr">
+        <is>
+          <t>Astra Ships 110 Satellite Engines, Eyes 2026 Rocket Test - Aviation Week Network</t>
+        </is>
+      </c>
+      <c r="C186" s="9" t="inlineStr">
+        <is>
+          <t>https://aviationweek.com/space/satellites/astra-ships-110-satellite-engines-eyes-2026-rocket-test</t>
+        </is>
+      </c>
+      <c r="D186" s="8" t="inlineStr">
+        <is>
+          <t>aviationweek.com</t>
+        </is>
+      </c>
+      <c r="E186" s="8" t="inlineStr">
+        <is>
+          <t>Wed, 21 Jan 2026 23:14:15 GMT</t>
+        </is>
+      </c>
+      <c r="F186" s="8" t="n">
+        <v>0.1038</v>
+      </c>
+      <c r="G186" s="8" t="inlineStr">
+        <is>
+          <t>Commercial Space  ## Subscription Required  Astra Ships 110 Satellite Engines, Eyes 2026 Rocket Test is published in Aerospace Daily &amp; Defense Report, an Aviation Week Intelligence Network (AWIN) Market Briefing and is included with your AWIN membership.  Already a member of AWIN or subscribe to Aerospace Daily &amp; Defense Report through your company? Loginwith your existing email and password.  Not a member?  Learn how you can access the market intelligence and data you need to stay abreast of wh...</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="11" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="11" t="inlineStr">
+        <is>
+          <t>Indra upgrades Meteor missile with improved datalink - janes.com</t>
+        </is>
+      </c>
+      <c r="C187" s="12" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/defence/indra-upgrades-meteor-missile-with-improved-datalink</t>
+        </is>
+      </c>
+      <c r="D187" s="11" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E187" s="11" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 12:08:16 GMT</t>
+        </is>
+      </c>
+      <c r="F187" s="11" t="n">
+        <v>0.1026</v>
+      </c>
+      <c r="G187" s="11" t="inlineStr">
+        <is>
+          <t>The world's most complete foundational military data asset.  500,000+ analyst hours per year to keep data current.  Easy integration into high and low-side environments. [...] “The latest advancement introduced by Indra is related to the development of a particularly critical element: the datalink between the missile and the launch platform, which is responsible for the guidance and control of the weapon,” the company said.  As noted by Indra, a redesigned datalink design has been presented to t...</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="8" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="8" t="inlineStr">
+        <is>
+          <t>​Ukraine Moves From Arms Buyer to Co-Producer of Mirage Jets and Crotale Systems - Defense Express</t>
+        </is>
+      </c>
+      <c r="C188" s="9" t="inlineStr">
+        <is>
+          <t>https://en.defence-ua.com/industries/ukraine_moves_from_arms_buyer_to_co_producer_of_mirage_jets_and_crotale_systems-17447.html</t>
+        </is>
+      </c>
+      <c r="D188" s="8" t="inlineStr">
+        <is>
+          <t>en.defence-ua.com</t>
+        </is>
+      </c>
+      <c r="E188" s="8" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 18:01:57 GMT</t>
+        </is>
+      </c>
+      <c r="F188" s="8" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="G188" s="8" t="inlineStr">
+        <is>
+          <t>Latest  Most viewed  February 10, 2026  ### U.S. Delivers New F-35 Fighters Without Radars Due to Upgrade Delays, Mounting Issues  February 10, 2026  ### India Plans Additional Order for SCALP Cruise Missiles, This Could Be Problem for Ukraine  February 9, 2026  ### Assessing Cost of 150 Gripens, 100 Rafales in Ukraine's Ambition to Reach Global Air Power Top 10  February 6, 2026  ### Over 1,000 Tomahawks, 1,900 AIM-120s, 500 SM-6s per Year: U.S. Moves to Multiply Missile Production  January 31,...</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="11" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="11" t="inlineStr">
+        <is>
+          <t>Extra Mirage 2000-5 fighters to boost Ukrainian air force’s defences - FlightGlobal</t>
+        </is>
+      </c>
+      <c r="C189" s="12" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/defence/extra-mirage-2000-5-fighters-to-boost-ukrainian-air-forces-defences/166554.article</t>
+        </is>
+      </c>
+      <c r="D189" s="11" t="inlineStr">
+        <is>
+          <t>flightglobal.com</t>
+        </is>
+      </c>
+      <c r="E189" s="11" t="inlineStr">
+        <is>
+          <t>Fri, 06 Mar 2026 12:11:26 GMT</t>
+        </is>
+      </c>
+      <c r="F189" s="11" t="n">
+        <v>0.0844</v>
+      </c>
+      <c r="G189" s="11" t="inlineStr">
+        <is>
+          <t>2026-03-04T17:08:00Z By Dominic Perry    Dassault Aviation is hopeful that a new order from India for 114 Rafale combat aircraft can be wrapped up this year, as it looks to further extend the backlog of the fourth-generation jet.  News    ### BAE launches Silver Link conformal antenna solution for ‘air dominance’ platforms    2026-03-04T14:30:00Z By Craig Hoyle    BAE Systems has launched its Silver Link range of conformal antennas, which it says is suitable for a range of applications, inlcudin...</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="8" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="8" t="inlineStr">
+        <is>
+          <t>UK Royal Air Force Eurofighters To Receive AESA Radar - Aviation Week Network</t>
+        </is>
+      </c>
+      <c r="C190" s="9" t="inlineStr">
+        <is>
+          <t>https://aviationweek.com/defense/sensors-electronic-warfare/uk-royal-air-force-eurofighters-receive-aesa-radar</t>
+        </is>
+      </c>
+      <c r="D190" s="8" t="inlineStr">
+        <is>
+          <t>aviationweek.com</t>
+        </is>
+      </c>
+      <c r="E190" s="8" t="inlineStr">
+        <is>
+          <t>Thu, 22 Jan 2026 16:40:11 GMT</t>
+        </is>
+      </c>
+      <c r="F190" s="8" t="n">
+        <v>0.0649</v>
+      </c>
+      <c r="G190" s="8" t="inlineStr">
+        <is>
+          <t>Hensoldt Sees Space, Air Defense Cooperation Deals  Leonardo Wins Swiss Radar Deal To Fill Air Surveillance Gap [...] ## Subscription Required  UK Royal Air Force Eurofighters To Receive AESA Radar is published in Aerospace Daily &amp; Defense Report, an Aviation Week Intelligence Network (AWIN) Market Briefing and is included with your AWIN membership.  Already a member of AWIN or subscribe to Aerospace Daily &amp; Defense Report through your company? Loginwith your existing email and password.  Not a...</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="11" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="11" t="inlineStr">
+        <is>
+          <t>IMFA completes Tata Steel ferro chrome plant acquisition - Manufacturing Today India</t>
+        </is>
+      </c>
+      <c r="C191" s="12" t="inlineStr">
+        <is>
+          <t>https://www.manufacturingtodayindia.com/imfa-completes-tata-steel-ferro-chrome-plant-acquisition</t>
+        </is>
+      </c>
+      <c r="D191" s="11" t="inlineStr">
+        <is>
+          <t>manufacturingtodayindia.com</t>
+        </is>
+      </c>
+      <c r="E191" s="11" t="inlineStr">
+        <is>
+          <t>Sat, 28 Feb 2026 12:40:01 GMT</t>
+        </is>
+      </c>
+      <c r="F191" s="11" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="G191" s="11" t="inlineStr">
+        <is>
+          <t>The expansion comes at a time when infrastructure growth, construction activity and industrial manufacturing are driving demand for stainless steel products. By increasing production capacity and optimising operations, IMFA aims to reinforce its role in the global ferro alloys supply chain.  The acquisition underlines a clear strategy of consolidation, scale enhancement and long term value creation in India’s ferro chrome industry.  Posted inOil &amp; Gas   ## INOX Air Products signs MoU for new air...</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="8" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="8" t="inlineStr">
+        <is>
+          <t>Malaysia launches third Maharaja Lela-class ship - Janes</t>
+        </is>
+      </c>
+      <c r="C192" s="9" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/sea/malaysia-launches-third-maharaja-lela-class-ship</t>
+        </is>
+      </c>
+      <c r="D192" s="8" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E192" s="8" t="inlineStr">
+        <is>
+          <t>Wed, 11 Feb 2026 07:37:44 GMT</t>
+        </is>
+      </c>
+      <c r="F192" s="8" t="n">
+        <v>0.0429</v>
+      </c>
+      <c r="G192" s="8" t="inlineStr">
+        <is>
+          <t>Like the earlier vessels, Sharif Mashor measures 111 m in overall length and displaces around 3,000 tonnes.  The ceremony for Sharif Mashor comes slightly more than six months after Raja Muda Nala's formal launch on 3 July 2025, an event that followed the ship's technical down slip on 8 May 2025.  Maharaja Lela underwent its technical down slip on 23 May 2024, nearly seven years after an earlier “launch”ceremony in 2017 that did not place the ship in the water.  As with the first two hulls, Shar...</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="11" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="11" t="inlineStr">
+        <is>
+          <t>India’s DAC clears $25.1bn military procurement proposals - Army Technology</t>
+        </is>
+      </c>
+      <c r="C193" s="12" t="inlineStr">
+        <is>
+          <t>https://www.army-technology.com/news/india-dac-military-procurement/</t>
+        </is>
+      </c>
+      <c r="D193" s="11" t="inlineStr">
+        <is>
+          <t>army-technology.com</t>
+        </is>
+      </c>
+      <c r="E193" s="11" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 13:40:49 GMT</t>
+        </is>
+      </c>
+      <c r="F193" s="11" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="G193" s="11" t="inlineStr">
+        <is>
+          <t>Skip to site menu Skip to page content   News  # India’s DAC clears $25.1bn military procurement proposals  In the financial year 2025-26, DAC approved 55 proposals amounting to Rs6.73bn.  Jangoulun Singsit March 30, 2026  Share   Copy Link  Share on X  Share on Linkedin  Share on Facebook  India’s Defence Acquisition Council (DAC) has approved military procurement proposals valued at approximately Rs2,380bn ($25.14bn) on 27 March 2026.  The council cleared acquisitions for the Indian Army, Air...</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="8" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="8" t="inlineStr">
+        <is>
+          <t>BAE Systems test fires APKWS rockets from RAF Typhoon - FlightGlobal</t>
+        </is>
+      </c>
+      <c r="C194" s="9" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/archive/2026/04/bae-systems-test-fires-apkws-rockets-from-raf-typhoon/</t>
+        </is>
+      </c>
+      <c r="D194" s="8" t="inlineStr">
+        <is>
+          <t>flightglobal.com</t>
+        </is>
+      </c>
+      <c r="E194" s="8" t="inlineStr">
+        <is>
+          <t>Wed, 08 Apr 2026 13:19:11 GMT</t>
+        </is>
+      </c>
+      <c r="F194" s="8" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="G194" s="8" t="inlineStr">
+        <is>
+          <t>E-mailFacebook𝕏TwitterLinkedInWhatsApp  #### Author: Dominic Perry  Dominic Perry is Aerospace Editor, Europe contributing extensively to flightglobal.com. Although specialising in the coverage of the helicopter industry, he has written on most topics in aerospace – be they commercial, defence or business aviation. In addition, there has been an increasing focus on the decarbonisation of the industry and zero-emission flight initiatives. He also helps to edit Flight International.  E-mail  ### R...</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="11" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="11" t="inlineStr">
+        <is>
+          <t>Proteus RWUAS demonstrator performs first flight - Janes</t>
+        </is>
+      </c>
+      <c r="C195" s="12" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/air/proteus-rwuas-demonstrator-performs-first-flight</t>
+        </is>
+      </c>
+      <c r="D195" s="11" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E195" s="11" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F195" s="11" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="G195" s="11" t="inlineStr">
+        <is>
+          <t>Read Article  Air  ### UK's Windracers to establish T&amp;E, MRO facility in Ukraine by January 2027  Read Article  ## See how Janes delivers verified defence intelligence for faster, safer decisions   The world's most complete foundational military data asset.  500,000+ analyst hours per year to keep data current.  Easy integration into high and low-side environments. [...] skip to main content    Search Janes     # Proteus RWUAS demonstrator performs first flight  By Richard Scott |  Leonardo's Pr...</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="8" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="8" t="inlineStr">
+        <is>
+          <t>Why air forces must target their CCA doctrine deficit - FlightGlobal</t>
+        </is>
+      </c>
+      <c r="C196" s="9" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/defence/why-air-forces-must-target-their-cca-doctrine-deficit/165910.article</t>
+        </is>
+      </c>
+      <c r="D196" s="8" t="inlineStr">
+        <is>
+          <t>flightglobal.com</t>
+        </is>
+      </c>
+      <c r="E196" s="8" t="inlineStr">
+        <is>
+          <t>Mon, 26 Jan 2026 09:36:50 GMT</t>
+        </is>
+      </c>
+      <c r="F196" s="8" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="G196" s="8" t="inlineStr">
+        <is>
+          <t>Skip to navigation   Trending now  FlightGlobal has a new podcast - listen now  2026 World Air Forces directory  Dubai Airshow  Singapore Airshow  Site name  Site name  Search our site  Close menu [...] 2026-01-22T10:52:00Z By Craig Hoyle    The UK Royal Air Force will operationally field an active electronically scanned array radar on a portion of its Eurofighter Typhoon fleet from late this decade, via an integration contract announced on 22 January.   Contact us  About us  Advertise with us...</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="11" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="11" t="inlineStr">
+        <is>
+          <t>Automotive metal forming market to reach $95 billion by FY30: Report - Business Standard</t>
+        </is>
+      </c>
+      <c r="C197" s="12" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/amp/industry/news/automotive-metal-forming-market-to-reach-95-billion-by-fy30-report-126040100360_1.html</t>
+        </is>
+      </c>
+      <c r="D197" s="11" t="inlineStr">
+        <is>
+          <t>business-standard.com</t>
+        </is>
+      </c>
+      <c r="E197" s="11" t="inlineStr">
+        <is>
+          <t>Wed, 01 Apr 2026 06:36:44 GMT</t>
+        </is>
+      </c>
+      <c r="F197" s="11" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="G197" s="11" t="inlineStr">
+        <is>
+          <t>हिंदी में पढें  Hi, {{firstName}}  Edit Logout   Login / Sign Up   My Reads  Subscribe to Business Standard digital subscription  My Account  Newsletters  Blueprint Defence MagazineNew  Today's Paper  Blueprint  Opinion  E-Magazine  News  Insights  Photo Story  Reports  Data  THE PODCAST  All Issues  Features  Books  Finance  News  Analysis  Personal Finance  Income Tax Calculator ToolEmi Calculator Tool  Markets  IPO  Recent IPOS List  Stock Market News  The Smart Investor  Commodities  Cryptoc...</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="8" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="8" t="inlineStr">
+        <is>
+          <t>BAE Systems launches Silver Link conformal antenna solution for ‘air dominance’ platforms - FlightGlobal</t>
+        </is>
+      </c>
+      <c r="C198" s="9" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/defence/bae-launches-silver-link-conformal-antenna-solution-for-air-dominance-platforms/166520.article</t>
+        </is>
+      </c>
+      <c r="D198" s="8" t="inlineStr">
+        <is>
+          <t>flightglobal.com</t>
+        </is>
+      </c>
+      <c r="E198" s="8" t="inlineStr">
+        <is>
+          <t>Wed, 04 Mar 2026 14:33:05 GMT</t>
+        </is>
+      </c>
+      <c r="F198" s="8" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="G198" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-04T12:23:00Z By Dominic Perry    Dassault Aviation’s pugnacious chief executive Eric Trappier has raised the temperature in his ongoing war of words with Airbus, repeatedly insisting its supposed partner was jeopardising the Future Combat Air System (FCAS) programme as it “does not want to work with us”.  ### More from Defence   News    ### Pilatus announces certification approval for PC-7 MKX trainer    2026-03-03T14:36:00Z By Craig Hoyle    Pilatus has reported achieving initial certif...</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="11" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="11" t="inlineStr">
+        <is>
+          <t>Why decarbonising steel industry is economic and environmental necessity for India - The Indian Express</t>
+        </is>
+      </c>
+      <c r="C199" s="12" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/upsc-current-affairs/upsc-essentials/decarbonising-steel-industry-is-economic-necessity-for-india-10526585/</t>
+        </is>
+      </c>
+      <c r="D199" s="11" t="inlineStr">
+        <is>
+          <t>indianexpress.com</t>
+        </is>
+      </c>
+      <c r="E199" s="11" t="inlineStr">
+        <is>
+          <t>Thu, 12 Feb 2026 08:23:06 GMT</t>
+        </is>
+      </c>
+      <c r="F199" s="11" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="G199" s="11" t="inlineStr">
+        <is>
+          <t>9 min readNew DelhiUpdated: Feb 12, 2026 01:53 PM IST  India’s emphasis on increasing scrap share in steel making aligns with its green steel initiative and emerging global sustainability norms. (File)  Make us preferred source on Google  twitter  Facebook  Reddit  — Renuka  Under the India-European Union Free Trade Agreement concluded last month, Indian trade negotiators had also sought easier access to steel scrap produced in the 27-nation EU as a workaround to soften the impact of the carbon...</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="8" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="8" t="inlineStr">
+        <is>
+          <t>Tamilan Launches High-Pressure Drone Cleaning Solutions &amp; Eco-Friendly Building Care - Unmanned Systems Technology</t>
+        </is>
+      </c>
+      <c r="C200" s="9" t="inlineStr">
+        <is>
+          <t>https://www.unmannedsystemstechnology.com/2026/02/tamilan-launches-high-pressure-drone-cleaning-solutions-eco-friendly-building-care/</t>
+        </is>
+      </c>
+      <c r="D200" s="8" t="inlineStr">
+        <is>
+          <t>unmannedsystemstechnology.com</t>
+        </is>
+      </c>
+      <c r="E200" s="8" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 06:13:00 GMT</t>
+        </is>
+      </c>
+      <c r="F200" s="8" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="G200" s="8" t="inlineStr">
+        <is>
+          <t>Share this  Posted by Summer James Summer is an Editor &amp; Copywriter at Unmanned Systems Technology. She joined in 2025, following a background in Creative Writing and English Literature, and has a strong interest in UAVs as well as imaging and vision systems. Her work centers on making complex technical advances in unmanned systems accessible to a broad audience. Connect   E:  T:  LinkedIn  Tamilan  Quadcopter Airframes and Complete Drone Solutions for Civilian, Commercial, and Military Applicat...</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="11" t="inlineStr">
+        <is>
+          <t>GA-ASI Earns Double Honors at Aviation Week Program Excellence Awards - Unmanned Systems Technology</t>
+        </is>
+      </c>
+      <c r="C201" s="12" t="inlineStr">
+        <is>
+          <t>https://www.unmannedsystemstechnology.com/2026/03/ga-asi-earns-double-honors-at-aviation-week-program-excellence-awards/</t>
+        </is>
+      </c>
+      <c r="D201" s="11" t="inlineStr">
+        <is>
+          <t>unmannedsystemstechnology.com</t>
+        </is>
+      </c>
+      <c r="E201" s="11" t="inlineStr">
+        <is>
+          <t>Thu, 26 Mar 2026 06:26:00 GMT</t>
+        </is>
+      </c>
+      <c r="F201" s="11" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="G201" s="11" t="inlineStr">
+        <is>
+          <t>Share this  Posted by Olivia Hannam Olivia is a Junior Editor and Copywriter at Unmanned Systems Technology. She graduated with First-Class Honours in History from the University of Exeter, where she developed a passion for research and clear communication. Since joining UST in 2025, Olivia’s focus lies in creating well-crafted content that highlights the latest innovations and technologies shaping the unmanned sector. Connect   E:  T:  LinkedIn  General Atomics Aeronautical Systems, Inc  Leadin...</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="8" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="8" t="inlineStr">
+        <is>
+          <t>US Army places $186m order for AeroVironment Switchblades - Army Technology</t>
+        </is>
+      </c>
+      <c r="C202" s="9" t="inlineStr">
+        <is>
+          <t>https://www.army-technology.com/news/us-army-aerovironment-switchblade/</t>
+        </is>
+      </c>
+      <c r="D202" s="8" t="inlineStr">
+        <is>
+          <t>army-technology.com</t>
+        </is>
+      </c>
+      <c r="E202" s="8" t="inlineStr">
+        <is>
+          <t>Fri, 27 Feb 2026 22:17:31 GMT</t>
+        </is>
+      </c>
+      <c r="F202" s="8" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G202" s="8" t="inlineStr">
+        <is>
+          <t>Find out more  #### Sign up for our daily news round-up!  Give your business an edge with our leading industry insights.  Give your business an edge with our leading industry insights.  close  close  #### Sign up to the newsletter: In Brief  ## Thank you for subscribing  View all newsletters from across the GlobalData Media network.  close [...] These systems are intended for use across different unit levels and mission types.  AeroVironment loitering munitions senior vice president Brian Young...</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="11" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="11" t="inlineStr">
+        <is>
+          <t>US federal grants help jumpstart nuclear fuel supply chain - Reuters</t>
+        </is>
+      </c>
+      <c r="C203" s="12" t="inlineStr">
+        <is>
+          <t>https://www.reuters.com/business/energy/us-federal-grants-help-jumpstart-nuclear-fuel-supply-chain--reeii-2026-02-24/</t>
+        </is>
+      </c>
+      <c r="D203" s="11" t="inlineStr">
+        <is>
+          <t>reuters.com</t>
+        </is>
+      </c>
+      <c r="E203" s="11" t="inlineStr">
+        <is>
+          <t>Tue, 24 Feb 2026 15:26:39 GMT</t>
+        </is>
+      </c>
+      <c r="F203" s="11" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="G203" s="11" t="inlineStr">
+        <is>
+          <t>### Information you can trust  Reuters, the news and media division of Thomson Reuters, is the world’s largest multimedia news provider, reaching billions of people worldwide every day. Reuters provides business, financial, national and international news to professionals via desktop terminals, the world's media organizations, industry events and directly to consumers.  ### Follow Us     [](    [](    [](    [](    [](    [](  ### LSEG Products     #### Workspace, opens new tab Access unmatched...</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="8" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="8" t="inlineStr">
+        <is>
+          <t>Special Report: India's IG Defence advances UAV manufacturing capabilities - Janes</t>
+        </is>
+      </c>
+      <c r="C204" s="9" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/industry/special-report-indias-ig-defence-advances-uav-manufacturing-capabilities</t>
+        </is>
+      </c>
+      <c r="D204" s="8" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E204" s="8" t="inlineStr">
+        <is>
+          <t>Thu, 05 Mar 2026 08:51:21 GMT</t>
+        </is>
+      </c>
+      <c r="F204" s="8" t="n">
+        <v>0.9933</v>
+      </c>
+      <c r="G204" s="8" t="inlineStr">
+        <is>
+          <t>The company's portfolio includes strike-capable unmanned platforms; intelligence, surveillance, and reconnaissance (ISR) systems; logistic UAV swarms; and training simulators.  Major General R C Padhi (retd), senior vice-president at IG Defence, told Janes in February that the proposed facility in Odisha, along with a new facility in Jhansi, Uttar Pradesh, would enhance IG Defence's manufacturing capabilities.  IG Defence commissioned another facility in Noida, Uttar Pradesh, in December 2025 to...</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="11" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="11" t="inlineStr">
+        <is>
+          <t>Defence Minister Rajnath Singh Underscores Importance Of India’s Ammunition Self-Reliance - Times of India</t>
+        </is>
+      </c>
+      <c r="C205" s="12" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/short-videos/briefs/defence-minister-rajnath-singh-underscores-importance-of-indias-ammunition-self-reliance/shorttakes/126674600.cms</t>
+        </is>
+      </c>
+      <c r="D205" s="11" t="inlineStr">
+        <is>
+          <t>timesofindia.indiatimes.com</t>
+        </is>
+      </c>
+      <c r="E205" s="11" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 09:37:04 GMT</t>
+        </is>
+      </c>
+      <c r="F205" s="11" t="n">
+        <v>0.9857</v>
+      </c>
+      <c r="G205" s="11" t="inlineStr">
+        <is>
+          <t>reflecting a strategic push towards indigenization and enhanced national security preparedness. [...] # Defence Minister Rajnath Singh Underscores Importance Of India’s Ammunition Self-Reliance [...] Defence Minister Rajnath Singh, speaking at the inauguration of the Medium Calibre Ammunition Facility built by Solar Industries, highlighted India’s focus on achieving self-reliance in ammunition production. He recalled past shortages that had limited the effective use of military platforms and equ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="8" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="8" t="inlineStr">
+        <is>
+          <t>Indian Council Advances Rafale, P-8I, Airship Deals - Aviation Week</t>
+        </is>
+      </c>
+      <c r="C206" s="9" t="inlineStr">
+        <is>
+          <t>https://aviationweek.com/defense/budget-policy-operations/indian-council-advances-rafale-p-8i-airship-deals</t>
+        </is>
+      </c>
+      <c r="D206" s="8" t="inlineStr">
+        <is>
+          <t>aviationweek.com</t>
+        </is>
+      </c>
+      <c r="E206" s="8" t="inlineStr">
+        <is>
+          <t>Fri, 13 Feb 2026 09:29:48 GMT</t>
+        </is>
+      </c>
+      <c r="F206" s="8" t="n">
+        <v>0.5206</v>
+      </c>
+      <c r="G206" s="8" t="inlineStr">
+        <is>
+          <t>“The procurement of the MRFA will enhance the capability to establish air supremacy in all combat scenarios and significantly enhance the Air Force’s deterrence capability with long-range offensive strikes,” India’s Press Information Bureau said in a news release.  The decision comes less than a year after Indian Rafales battled the Pakistani air force during a brief armed conflict. Indian officials have disputed Pakistani claims that three Rafales were shot down during the fighting.  The counci...</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="11" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="11" t="inlineStr">
+        <is>
+          <t>India-US trade deal protects dairy, key agriculture products; no duty for $40 billion exports | India News - Hindustan Times</t>
+        </is>
+      </c>
+      <c r="C207" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/india-news/indiaus-trade-agreement-slashes-duties-on-key-exports-boosts-labor-intensive-sectors-101770160525125.html</t>
+        </is>
+      </c>
+      <c r="D207" s="11" t="inlineStr">
+        <is>
+          <t>hindustantimes.com</t>
+        </is>
+      </c>
+      <c r="E207" s="11" t="inlineStr">
+        <is>
+          <t>Tue, 03 Feb 2026 23:26:23 GMT</t>
+        </is>
+      </c>
+      <c r="F207" s="11" t="n">
+        <v>0.4262</v>
+      </c>
+      <c r="G207" s="11" t="inlineStr">
+        <is>
+          <t>Indian government officials declined to comment on specific details of the deal before the formal joint statement as there could be some last-minute adjustments. They said, requesting anonymity, that the joint statement will formalise the understanding arrived at after lengthy negotiations.  Both Goyal and Greer separately hinted that the final language of the deal was yet to be firmed up.  “We will be shortly issuing a joint statement by both countries, along with the details which we will be s...</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="8" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="8" t="inlineStr">
+        <is>
+          <t>India approves INR3.6 trillion arms package including Rafales, P-8Is - FlightGlobal</t>
+        </is>
+      </c>
+      <c r="C208" s="9" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/fixed-wing/india-approves-inr36-trillion-arms-package-including-rafales-p-8is/166308.article</t>
+        </is>
+      </c>
+      <c r="D208" s="8" t="inlineStr">
+        <is>
+          <t>flightglobal.com</t>
+        </is>
+      </c>
+      <c r="E208" s="8" t="inlineStr">
+        <is>
+          <t>Fri, 13 Feb 2026 03:36:22 GMT</t>
+        </is>
+      </c>
+      <c r="F208" s="8" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="G208" s="8" t="inlineStr">
+        <is>
+          <t>2026-02-12T05:49:00Z By Greg Waldron    The US Marine Corps will retire its Boeing AV-8B Harrier II fleet in June 2026, a year earlier than previously planned, as it accelerates transition to the Lockheed Martin F-35B and focuses on aggressive modernisation for future threats.  News    ### Mitchell Institute calls for doubled B-21 fleet amid China concerns    A US Air Force-associated think tank is calling for a vastly expanded fighter and bomber fleet, warning that current force levels are insu...</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="11" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="11" t="inlineStr">
+        <is>
+          <t>India raises infrastructure spending by 11.4% to record 12.2 trillion rupees for 2026-27 - Reuters</t>
+        </is>
+      </c>
+      <c r="C209" s="12" t="inlineStr">
+        <is>
+          <t>https://www.reuters.com/world/india/india-budget-india-raises-infrastructure-spending-record-122-trillion-rupees-2026-02-01/</t>
+        </is>
+      </c>
+      <c r="D209" s="11" t="inlineStr">
+        <is>
+          <t>reuters.com</t>
+        </is>
+      </c>
+      <c r="E209" s="11" t="inlineStr">
+        <is>
+          <t>Sun, 01 Feb 2026 09:19:58 GMT</t>
+        </is>
+      </c>
+      <c r="F209" s="11" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="G209" s="11" t="inlineStr">
+        <is>
+          <t>"The capex outlay for fiscal year 2027 looks a bit modest and misses market expectations slightly, but overall, a positive for the manufacturing sector. It will also be good for private sector capex," said Amit Anwani, an analyst at Prabhudas Lilladher.  Shares of capital goods companies such as Larsen &amp; Toubro (LART.NS), opens new tab, IRB Infra (IRBI.NS), opens new tab, NBCC (NBCC.NS), opens new tab, Action Construction (ACEL.NS), opens new tab jumped between 1.3% and 4% on higher capex spendi...</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="8" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="8" t="inlineStr">
+        <is>
+          <t>Transformed Leonardo is primed for major growth, CEO Cingolani says - FlightGlobal</t>
+        </is>
+      </c>
+      <c r="C210" s="9" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/defence/transformed-leonardo-is-primed-for-major-growth-ceo-cingolani-says/166656.article</t>
+        </is>
+      </c>
+      <c r="D210" s="8" t="inlineStr">
+        <is>
+          <t>flightglobal.com</t>
+        </is>
+      </c>
+      <c r="E210" s="8" t="inlineStr">
+        <is>
+          <t>Fri, 13 Mar 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F210" s="8" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="G210" s="8" t="inlineStr">
+        <is>
+          <t>This year’s presentation centred on the Michelangelo Dome concept launched by Leonardo late last year. An open-architecture integrated air and missile defence capability, this will combine in-service equipment ranging from anti-aircraft guns to long-range interceptors to guard nations – or even Europe as a whole – against attacks ranging in scale from swarms of small drones to ballistic missiles.  After its launch last October, Cingolani says: “Now we have 20 countries that are in contact with u...</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="11" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="11" t="inlineStr">
+        <is>
+          <t>India, UAE Agree To Tighten Defense Cooperation - Aviation Week Network</t>
+        </is>
+      </c>
+      <c r="C211" s="12" t="inlineStr">
+        <is>
+          <t>https://aviationweek.com/defense/budget-policy-operations/india-uae-agree-tighten-defense-cooperation</t>
+        </is>
+      </c>
+      <c r="D211" s="11" t="inlineStr">
+        <is>
+          <t>aviationweek.com</t>
+        </is>
+      </c>
+      <c r="E211" s="11" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 16:52:04 GMT</t>
+        </is>
+      </c>
+      <c r="F211" s="11" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="G211" s="11" t="inlineStr">
+        <is>
+          <t>## Subscription Required  India, UAE Agree To Tighten Defense Cooperation is published in Aerospace Daily &amp; Defense Report, an Aviation Week Intelligence Network (AWIN) Market Briefing and is included with your AWIN membership.  Already a member of AWIN or subscribe to Aerospace Daily &amp; Defense Report through your company? Loginwith your existing email and password.  Not a member?  Learn how you can access the market intelligence and data you need to stay abreast of what's happening in the aeros...</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="8" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="8" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh govt to expand ambit of defence manufacturing corridor - Business Standard</t>
+        </is>
+      </c>
+      <c r="C212" s="9" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/external-affairs-defence-security/news/uttar-pradesh-govt-to-expand-ambit-of-defence-manufacturing-corridor-126020501022_1.html</t>
+        </is>
+      </c>
+      <c r="D212" s="8" t="inlineStr">
+        <is>
+          <t>business-standard.com</t>
+        </is>
+      </c>
+      <c r="E212" s="8" t="inlineStr">
+        <is>
+          <t>Thu, 05 Feb 2026 10:22:32 GMT</t>
+        </is>
+      </c>
+      <c r="F212" s="8" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="G212" s="8" t="inlineStr">
+        <is>
+          <t>Presenting sponsor  Associate Sponsors  Thursday, February 05, 2026 | 05:23 AM IST हिंदी में पढें  Home / External Affairs Defence Security / News / Uttar Pradesh govt to expand ambit of defence manufacturing corridor  # Uttar Pradesh govt to expand ambit of defence manufacturing corridor  ## With investor interest surging, Uttar Pradesh plans to expand its Defence Industrial Corridor beyond six nodes to accommodate new defence manufacturing projects  premium  UP Chief Minister Yogi Adityanath s...</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="11" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="11" t="inlineStr">
+        <is>
+          <t>Italy’s Leonardo rides high on soaring global defense spending - Defense News</t>
+        </is>
+      </c>
+      <c r="C213" s="12" t="inlineStr">
+        <is>
+          <t>https://www.defensenews.com/global/europe/2026/03/12/italys-leonardo-rides-high-on-soaring-global-defense-spending/</t>
+        </is>
+      </c>
+      <c r="D213" s="11" t="inlineStr">
+        <is>
+          <t>defensenews.com</t>
+        </is>
+      </c>
+      <c r="E213" s="11" t="inlineStr">
+        <is>
+          <t>Thu, 12 Mar 2026 16:40:42 GMT</t>
+        </is>
+      </c>
+      <c r="F213" s="11" t="n">
+        <v>0.2286</v>
+      </c>
+      <c r="G213" s="11" t="inlineStr">
+        <is>
+          <t>During a presentation in Rome, CEO Roberto Cingolani said the company would up its focus on cyber security and digitalization as well its new Michelangelo Dome, a multi-layered air defense system which should yield €21 billion in new business in the next ten years.  Cingolani has previously said Leonardo is working hard to manage its growth as demand grows.  Since 2023 Leonardo has increased its workforce from 51,400 staff to 62,700 last year and expects to have 75,500 on the payroll by 2030, a...</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="8" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="8" t="inlineStr">
+        <is>
+          <t>Rolls-Royce completes altitude, operability testing on F130 engine for B-52J programme - Janes</t>
+        </is>
+      </c>
+      <c r="C214" s="9" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/air/rolls-royce-completes-altitude-operability-testing-on-f130-engine-for-b-52j-programme</t>
+        </is>
+      </c>
+      <c r="D214" s="8" t="inlineStr">
+        <is>
+          <t>janes.com</t>
+        </is>
+      </c>
+      <c r="E214" s="8" t="inlineStr">
+        <is>
+          <t>Fri, 13 Mar 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F214" s="8" t="n">
+        <v>0.1744</v>
+      </c>
+      <c r="G214" s="8" t="inlineStr">
+        <is>
+          <t>Lieutenant Colonel Timothy Cleaver, USAF programme manager of the B-52 Commercial Engine Replacement Program, said that the tests “gathered essential data about how this engine operates across the full spectrum of flight conditions” while giving Rolls-Royce and the USAF confidence the engine will hold up during test aircraft modification and flight testing.  The milestone comes after Rolls-Royce completed the engine's critical design review (CDR) in late 2024, which cleared the way to build the...</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="11" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="11" t="inlineStr">
+        <is>
+          <t>UK taps Leonardo for $1.3 billion medium-lift helicopter deal - Defense News</t>
+        </is>
+      </c>
+      <c r="C215" s="12" t="inlineStr">
+        <is>
+          <t>https://www.defensenews.com/global/europe/2026/03/02/uk-taps-leonardo-for-13-billion-medium-lift-helicopter-deal/</t>
+        </is>
+      </c>
+      <c r="D215" s="11" t="inlineStr">
+        <is>
+          <t>defensenews.com</t>
+        </is>
+      </c>
+      <c r="E215" s="11" t="inlineStr">
+        <is>
+          <t>Mon, 02 Mar 2026 13:20:31 GMT</t>
+        </is>
+      </c>
+      <c r="F215" s="11" t="n">
+        <v>0.1714</v>
+      </c>
+      <c r="G215" s="11" t="inlineStr">
+        <is>
+          <t>Featured:  Coverage: Iran  Coverage: Singapore Airshow  Whitepaper: Modular Open Systems  #### Europe  # UK taps Leonardo for $1.3 billion medium-lift helicopter deal  By Tom Kington  A Leonardo AWHERO drone is displayed in front of a AW149 helicopter during the Farnborough International Airshow 2024 outside of London on July 23, 2024. (John Keeble/Getty Images)  ROME — The U.K. will hand Leonardo a £1 billion ($1.34 billion) contract to build 23 AW149 helicopters at the firm’s Yeovil plant in t...</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="8" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="8" t="inlineStr">
+        <is>
+          <t>Indonesia, Philippines boost maritime surveillance with twin-turboprops - FlightGlobal</t>
+        </is>
+      </c>
+      <c r="C216" s="9" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/fixed-wing/indonesia-philippines-boost-maritime-surveillance-with-twin-turboprops/166385.article</t>
+        </is>
+      </c>
+      <c r="D216" s="8" t="inlineStr">
+        <is>
+          <t>flightglobal.com</t>
+        </is>
+      </c>
+      <c r="E216" s="8" t="inlineStr">
+        <is>
+          <t>Fri, 20 Feb 2026 05:04:54 GMT</t>
+        </is>
+      </c>
+      <c r="F216" s="8" t="n">
+        <v>0.1172</v>
+      </c>
+      <c r="G216" s="8" t="inlineStr">
+        <is>
+          <t>### India approves INR3.6 trillion arms package including Rafales, P-8Is    2026-02-13T03:31:00Z By Greg Waldron    India’s Defence Acquisition Council has approved INR3.6 trillion ($39.7 billion) in military purchases, including Dassault Aviation Rafale fighters under the Multi-Role Fighter Aircraft requirement and additional Boeing P-8I Neptune maritime patrol aircraft for the navy.  Analysis    ### Non-American defence firms gain as US policies reshape markets    2026-02-05T10:05:00Z By Ryan...</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="11" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="11" t="inlineStr">
+        <is>
+          <t>Space Budget 2026-27: Rs 13,705 Crore Allocated - Rediff MoneyWiz</t>
+        </is>
+      </c>
+      <c r="C217" s="12" t="inlineStr">
+        <is>
+          <t>https://money.rediff.com/news/market/space-budget-2026-27-rs-13-705-crore-allocated/41195920260201</t>
+        </is>
+      </c>
+      <c r="D217" s="11" t="inlineStr">
+        <is>
+          <t>money.rediff.com</t>
+        </is>
+      </c>
+      <c r="E217" s="11" t="inlineStr">
+        <is>
+          <t>Sun, 01 Feb 2026 18:12:00 GMT</t>
+        </is>
+      </c>
+      <c r="F217" s="11" t="n">
+        <v>0.0746</v>
+      </c>
+      <c r="G217" s="11" t="inlineStr">
+        <is>
+          <t>© 2026 Rediff.com India Limited. All rights reserved. Disclaimer - Terms of Service - Privacy Policy - Feedback  Home Market News Latest News International Markets Economy Industries Mutual Fund News IPO News Search News My Portfolio My Watchlist      Mutual Funds [...] Source: PTI   By Rediff Money Desk, New Delhi  DISCLAIMER - This article is from a syndicated feed. The original source is responsible for accuracy, views &amp; content ownership. Views expressed may not reflect those of rediff.com I...</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="8" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" s="8" t="inlineStr">
+        <is>
+          <t>French Government Aims To Change Weapons Suppliers’ Business Model - Aviation Week</t>
+        </is>
+      </c>
+      <c r="C218" s="9" t="inlineStr">
+        <is>
+          <t>https://aviationweek.com/defense/supply-chain/french-government-aims-change-weapons-suppliers-business-model</t>
+        </is>
+      </c>
+      <c r="D218" s="8" t="inlineStr">
+        <is>
+          <t>aviationweek.com</t>
+        </is>
+      </c>
+      <c r="E218" s="8" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 23:53:28 GMT</t>
+        </is>
+      </c>
+      <c r="F218" s="8" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="G218" s="8" t="inlineStr">
+        <is>
+          <t>France  Europe  NATO  ## Subscription Required  French Government Aims To Change Weapons Suppliers’ Business Model is published in Aerospace Daily &amp; Defense Report, an Aviation Week Intelligence Network (AWIN) Market Briefing and is included with your AWIN membership.  Already a member of AWIN or subscribe to Aerospace Daily &amp; Defense Report through your company? Loginwith your existing email and password.  Not a member?  Learn how you can access the market intelligence and data you need to stay...</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="11" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" s="11" t="inlineStr">
+        <is>
+          <t>France orders its fifth and final FDI frigate from Naval Group, completing fleet plan - Defense News</t>
+        </is>
+      </c>
+      <c r="C219" s="12" t="inlineStr">
+        <is>
+          <t>https://www.defensenews.com/global/europe/2026/04/03/france-orders-its-fifth-and-final-fdi-frigate-from-naval-group-completing-fleet-plan/</t>
+        </is>
+      </c>
+      <c r="D219" s="11" t="inlineStr">
+        <is>
+          <t>defensenews.com</t>
+        </is>
+      </c>
+      <c r="E219" s="11" t="inlineStr">
+        <is>
+          <t>Fri, 03 Apr 2026 10:57:57 GMT</t>
+        </is>
+      </c>
+      <c r="F219" s="11" t="n">
+        <v>0.0668</v>
+      </c>
+      <c r="G219" s="11" t="inlineStr">
+        <is>
+          <t>Featured:  Coverage: Iran  2026 Tech Disruptors List  Coverage: Singapore Airshow  #### Europe  # France orders its fifth and final FDI frigate from Naval Group, completing fleet plan  By Rudy Ruitenberg  The new French FDI frigate Amiral Ronarc'h docks at Nordre Toldbod in Copenhagen, Denmark, on Jan. 19, 2026. (Thomas Traasdahl / Ritzau Scanpix / AFP via Getty Images)  PARIS — France placed an order with shipbuilder Naval Group for the country’s fifth Defense and Intervention Frigate, known by...</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="8" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" s="8" t="inlineStr">
+        <is>
+          <t>AI for investors - MLQ.ai</t>
+        </is>
+      </c>
+      <c r="C220" s="9" t="inlineStr">
+        <is>
+          <t>https://mlq.ai/news/india-approves-11-billion-government-fund-to-boost-deep-tech-startups/</t>
+        </is>
+      </c>
+      <c r="D220" s="8" t="inlineStr">
+        <is>
+          <t>mlq.ai</t>
+        </is>
+      </c>
+      <c r="E220" s="8" t="inlineStr">
+        <is>
+          <t>Sun, 15 Feb 2026 09:37:42 GMT</t>
+        </is>
+      </c>
+      <c r="F220" s="8" t="n">
+        <v>0.0514</v>
+      </c>
+      <c r="G220" s="8" t="inlineStr">
+        <is>
+          <t>TECH  # India Approves $1.1 Billion Government Fund to Boost Deep Tech Startups  February 15, 2026 at 9:31 AM • by  MLQ Editorial  #### Key Points   India's cabinet approved Startup India Fund of Funds 2.0 with a ₹10,000 crore ($1.1 billion) corpus to support deep tech and manufacturing startups through private VCs.  The 2016 program committed ₹10,000 crore to 145 funds, leveraging over ₹25,500 crore in investments to 1,370 startups.  Private funding in India's startups fell 17% to $10.5 billion...</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="11" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" s="11" t="inlineStr">
+        <is>
+          <t>GCAP advances as Edgewing lands first joint contract from partner nations - flightglobal.com</t>
+        </is>
+      </c>
+      <c r="C221" s="12" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/defence/2026/04/gcap-advances-as-edgewing-lands-first-joint-contract-from-partner-nations/</t>
+        </is>
+      </c>
+      <c r="D221" s="11" t="inlineStr">
+        <is>
+          <t>flightglobal.com</t>
+        </is>
+      </c>
+      <c r="E221" s="11" t="inlineStr">
+        <is>
+          <t>Thu, 02 Apr 2026 11:08:18 GMT</t>
+        </is>
+      </c>
+      <c r="F221" s="11" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="G221" s="11" t="inlineStr">
+        <is>
+          <t>Menu  search  Trending now:  CONTRACT  # GCAP advances as Edgewing lands first joint contract from partner nations  By Craig Hoyle |  The three-nation Global Combat Air Programme (GCAP) is moving into its next phase of activity, following the award of a contract worth £686 million ($904 million).  Placed with design and development authority Edgewing and announced on 2 April, the contract “invests in key design and engineering activities and enables the trilateral partnership to build momentum a...</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="8" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" s="8" t="inlineStr">
+        <is>
+          <t>Bosch and Tata AutoComp plan Indian e-mobility JV - Automotive World</t>
+        </is>
+      </c>
+      <c r="C222" s="9" t="inlineStr">
+        <is>
+          <t>https://www.automotiveworld.com/news/bosch-and-tata-autocomp-plan-indian-e-mobility-jv/</t>
+        </is>
+      </c>
+      <c r="D222" s="8" t="inlineStr">
+        <is>
+          <t>automotiveworld.com</t>
+        </is>
+      </c>
+      <c r="E222" s="8" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 05:10:14 GMT</t>
+        </is>
+      </c>
+      <c r="F222" s="8" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="G222" s="8" t="inlineStr">
+        <is>
+          <t>Skip to content   Bosch and Tata AutoComp plan Indian e-mobility JV Škoda brings V2L and digital key to Elroq and Enyaq Tougher crash avoidance rules shape 2026 IIHS awards Xpeng formalises robotaxi push with dedicated business unit Blume holds up China as template, “clear progress” on VW cuts US auto groups press Trump to hold the line on China EVs Musk unveils Terafab as Tesla-SpaceX joint chip venture SK Signet targets US and Europe with 400 kW SiC charger Daimler Buses launches electric inte...</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="11" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" s="11" t="inlineStr">
+        <is>
+          <t>France, UK Launching Joint Study Into Meteor Missile Successor - Aviation Week</t>
+        </is>
+      </c>
+      <c r="C223" s="12" t="inlineStr">
+        <is>
+          <t>https://aviationweek.com/defense/missile-defense-weapons/france-uk-launching-joint-study-meteor-missile-successor</t>
+        </is>
+      </c>
+      <c r="D223" s="11" t="inlineStr">
+        <is>
+          <t>aviationweek.com</t>
+        </is>
+      </c>
+      <c r="E223" s="11" t="inlineStr">
+        <is>
+          <t>Thu, 02 Apr 2026 08:44:02 GMT</t>
+        </is>
+      </c>
+      <c r="F223" s="11" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="G223" s="11" t="inlineStr">
+        <is>
+          <t>The weapon has also been widely exported and is currently awaiting integration on the Lockheed Martin F-35 Joint Strike Fighter.  As well as the study on the new weapon, the two countries are establishing a joint Complex Weapons Portfolio Office to coordinate this and other missile programs. This will ensure closer alignment between national defense priorities and open opportunities for cooperation with other countries.  France and the UK are already working on a successor to the Scalp/Storm Sha...</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="8" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" s="8" t="inlineStr">
+        <is>
+          <t>Jaykay Enterprises Acquires Defence Manufacturing Business to Strengthen Missile Systems Capabilities - Machine Maker</t>
+        </is>
+      </c>
+      <c r="C224" s="9" t="inlineStr">
+        <is>
+          <t>https://themachinemaker.com/news/jaykay-enterprises-acquires-defence-manufacturing-business-to-strengthen-missile-systems-capabilities/</t>
+        </is>
+      </c>
+      <c r="D224" s="8" t="inlineStr">
+        <is>
+          <t>themachinemaker.com</t>
+        </is>
+      </c>
+      <c r="E224" s="8" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 04:13:14 GMT</t>
+        </is>
+      </c>
+      <c r="F224" s="8" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G224" s="8" t="inlineStr">
+        <is>
+          <t>09 Apr 2026   Show Reports  How a Culture of Respect at Motherson Shaped Kalpna’s Confidence in Manufacturing    08 Apr 2026   Womanufacturing  Callington to Showcase High-Performance Chemical Solutions at AeroDef India Manufacturing Expo 2026    08 Apr 2026   Show Reports   Jaykay Enterprises, MAKE IN INDIA, MANUFACTURING  #### MM Desk   All Posts  PrevPreviousToyota Kirloskar Motor Shines at IndiaSkills National Competition 2025–26 with 9 Medals  ## Related post  ### Live turning insight for s...</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="11" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" s="11" t="inlineStr">
+        <is>
+          <t>Anglo-French study to explore joint successor for MBDA’s Meteor missile - flightglobal.com</t>
+        </is>
+      </c>
+      <c r="C225" s="12" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/defence/2026/04/anglo-french-study-to-explore-joint-successor-for-mbdas-meteor-missile/</t>
+        </is>
+      </c>
+      <c r="D225" s="11" t="inlineStr">
+        <is>
+          <t>flightglobal.com</t>
+        </is>
+      </c>
+      <c r="E225" s="11" t="inlineStr">
+        <is>
+          <t>Thu, 02 Apr 2026 10:12:11 GMT</t>
+        </is>
+      </c>
+      <c r="F225" s="11" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="G225" s="11" t="inlineStr">
+        <is>
+          <t>“This new study aims to be a first step towards achieving similar success, ensuring that the UK, France and prospective partner nations maintain air superiority well into the future,” DE&amp;S says. That will include the future weapon’s use by planned sixth-generation fighters.  “This agreement is a significant step forward in delivering on our Lancaster House 2.0 commitments, demonstrating the strength of our UK-France defence partnership,” says Luke Pollard, the UK’s minister for defence readiness...</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="8" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" s="8" t="inlineStr">
+        <is>
+          <t>Dairy plants get boost in Bundelkhand - The Times of India</t>
+        </is>
+      </c>
+      <c r="C226" s="9" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/lucknow/dairy-plants-get-boost-in-bundelkhand/articleshow/129416640.cms</t>
+        </is>
+      </c>
+      <c r="D226" s="8" t="inlineStr">
+        <is>
+          <t>timesofindia.indiatimes.com</t>
+        </is>
+      </c>
+      <c r="E226" s="8" t="inlineStr">
+        <is>
+          <t>Wed, 11 Mar 2026 03:08:00 GMT</t>
+        </is>
+      </c>
+      <c r="F226" s="8" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="G226" s="8" t="inlineStr">
+        <is>
+          <t>Edition  IN   IN  US  English   English  हिन्दी  मराठी  ಕನ್ನಡ  தமிழ்  বাংলা  മലയാളം  తెలుగు  ગુજરાતી  Sign In  Today's ePaper  Live   News  City News  lucknow News  Dairy plants get boost in Bundelkhand  Revanth Reddy  Uttam Nagar Murder  Punjab Labourer Found Dead  Bengaluru East corporation  Thane Molestation Case  Today weather  Revanth Reddy  Uttam Nagar Murder  Punjab Labourer Found Dead  Bengaluru East corporation  Thane Molestation Case  Today weather  Revanth Reddy  Uttam Nagar Murder  P...</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="11" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" s="11" t="inlineStr">
+        <is>
+          <t>Coupled aerodynamic–electromagnetic modeling for RCS estimation of million-scale chaff clouds with arbitrarily curved 3D geometries - Nature</t>
+        </is>
+      </c>
+      <c r="C227" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/articles/s41598-026-44700-4</t>
+        </is>
+      </c>
+      <c r="D227" s="11" t="inlineStr">
+        <is>
+          <t>nature.com</t>
+        </is>
+      </c>
+      <c r="E227" s="11" t="inlineStr">
+        <is>
+          <t>Sat, 21 Mar 2026 09:36:46 GMT</t>
+        </is>
+      </c>
+      <c r="F227" s="11" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="G227" s="11" t="inlineStr">
+        <is>
+          <t>Reprints and permissions  ## About this article  ### Cite this article  Lee, C.H., Jang, B., Kwon, K. et al. Coupled aerodynamic–electromagnetic modeling for RCS estimation of million-scale chaff clouds with arbitrarily curved 3D geometries. Sci Rep (2026).   Download citation   Received:  Accepted:  Published:  DOI:   ### Share this article  Anyone you share the following link with will be able to read this content:  Sorry, a shareable link is not currently available for this article.  Provided...</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="8" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" s="8" t="inlineStr">
+        <is>
+          <t>India's Titan hits record high on strong fourth-quarter sales - Reuters</t>
+        </is>
+      </c>
+      <c r="C228" s="9" t="inlineStr">
+        <is>
+          <t>https://www.reuters.com/world/india/indias-titan-hits-record-high-strong-fourth-quarter-sales-2026-04-08/</t>
+        </is>
+      </c>
+      <c r="D228" s="8" t="inlineStr">
+        <is>
+          <t>reuters.com</t>
+        </is>
+      </c>
+      <c r="E228" s="8" t="inlineStr">
+        <is>
+          <t>Wed, 08 Apr 2026 04:17:18 GMT</t>
+        </is>
+      </c>
+      <c r="F228" s="8" t="n">
+        <v>0.0173</v>
+      </c>
+      <c r="G228" s="8" t="inlineStr">
+        <is>
+          <t>### Information you can trust  Reuters, the news and media division of Thomson Reuters, is the world’s largest multimedia news provider, reaching billions of people worldwide every day. Reuters provides business, financial, national and international news to professionals via desktop terminals, the world's media organizations, industry events and directly to consumers.  ### Follow Us     [](    [](    [](    [](    [](    [](  ### LSEG Products     #### Workspace, opens new tab Access unmatched...</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="11" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" s="11" t="inlineStr">
+        <is>
+          <t>India's solar manufacturer stocks tank after preliminary US duties on imports - Reuters</t>
+        </is>
+      </c>
+      <c r="C229" s="12" t="inlineStr">
+        <is>
+          <t>https://www.reuters.com/sustainability/climate-energy/indias-solar-manufacturer-stocks-tank-after-preliminary-us-duties-imports-2026-02-25/</t>
+        </is>
+      </c>
+      <c r="D229" s="11" t="inlineStr">
+        <is>
+          <t>reuters.com</t>
+        </is>
+      </c>
+      <c r="E229" s="11" t="inlineStr">
+        <is>
+          <t>Wed, 25 Feb 2026 05:10:50 GMT</t>
+        </is>
+      </c>
+      <c r="F229" s="11" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="G229" s="11" t="inlineStr">
+        <is>
+          <t>Our Standards: The Thomson Reuters Trust Principles., opens new tab  Purchase Licensing Rights  ## Read Next   Climate &amp; Energycategory    Iberdrola posts 12% increase in net profit boosted by networks business  Climate &amp; Energycategory    Statkraft, OX2 in Finland battery deal to iron out wind power volatility  Climate &amp; Energycategory    Renewables firm EDPR's 2025 recurring profit jumps 50% on U.S. growth  Climate &amp; Energycategory    U.S. trade action deals blow to Indian solar makers  Climat...</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="8" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" s="8" t="inlineStr">
+        <is>
+          <t>IndiGo A320neo engine failure traced to maintenance assembly error - FlightGlobal</t>
+        </is>
+      </c>
+      <c r="C230" s="9" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/safety/indigo-a320neo-engine-failure-traced-to-maintenance-assembly-error/166027.article</t>
+        </is>
+      </c>
+      <c r="D230" s="8" t="inlineStr">
+        <is>
+          <t>flightglobal.com</t>
+        </is>
+      </c>
+      <c r="E230" s="8" t="inlineStr">
+        <is>
+          <t>Thu, 22 Jan 2026 07:15:24 GMT</t>
+        </is>
+      </c>
+      <c r="F230" s="8" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="G230" s="8" t="inlineStr">
+        <is>
+          <t>Skip to navigation   Trending now  FlightGlobal has a new podcast - listen now  2026 World Air Forces directory  Dubai Airshow  Singapore Airshow  Site name  Site name  Search our site  Close menu [...] The report says the wire seal was installed incorrectly, causing the HPT air seal to bulge out of position. When normal thermal expansion further reduced the clearance, the air seal struck the turbine intermediate case.  “The engine examination confirmed that the clashing contact between the HPT...</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="11" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" s="11" t="inlineStr">
+        <is>
+          <t>Budget 2026: Manufacturing gets a big push amid global headwinds | Stock Market News - Mint</t>
+        </is>
+      </c>
+      <c r="C231" s="12" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/market/mark-to-market/union-budget-2026-electronics-manufacturing-india-11769950774352.html</t>
+        </is>
+      </c>
+      <c r="D231" s="11" t="inlineStr">
+        <is>
+          <t>livemint.com</t>
+        </is>
+      </c>
+      <c r="E231" s="11" t="inlineStr">
+        <is>
+          <t>Sun, 01 Feb 2026 13:42:23 GMT</t>
+        </is>
+      </c>
+      <c r="F231" s="11" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="G231" s="11" t="inlineStr">
+        <is>
+          <t>Yes, Continue  ## Congratulations!  You are now subscribed to our newsletters. In case you can’t find any email from our side, please check the spam folder.  ×)Get alerts on WhatsApp Gift an article)  Gift a Subscription Set Preferences My Reads Watchlist Feedback Redeem a Gift Card Logout  #### Subscribe to continue  This is a subscriber only feature Subscribe Now to get daily updates on WhatsApp [...] English  हिंदी  Mark to Market  # Budget 2026: Manufacturing gets a big push amid global head...</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="8" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" s="8" t="inlineStr">
+        <is>
+          <t>Pratt &amp; Whitney targets end of decade for full GTF recovery - FlightGlobal</t>
+        </is>
+      </c>
+      <c r="C232" s="9" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/engines/pratt-and-whitney-targets-end-of-decade-for-full-gtf-recovery/166201.article</t>
+        </is>
+      </c>
+      <c r="D232" s="8" t="inlineStr">
+        <is>
+          <t>flightglobal.com</t>
+        </is>
+      </c>
+      <c r="E232" s="8" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 06:43:02 GMT</t>
+        </is>
+      </c>
+      <c r="F232" s="8" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="G232" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-30T08:02:00Z By Dominic Perry    Rolls-Royce is promising a further time-on-wing boost for the Trent 1000 with the roll-out of a second phase of its durability enhancement package for the engine, an option on the Boeing 787, after obtaining certification for the latest high-pressure turbine (HPT) upgrades in late 2025.  News    ### Pratt &amp; Whitney’s GTF deliveries increased 6% in 2025, while recall recovery progresses    2026-01-28T13:57:00Z By Jon Hemmerdinger    Pratt &amp; Whitney deliver...</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="11" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" s="11" t="inlineStr">
+        <is>
+          <t>AH-64 tests proximity-fused ammunition against drones - FlightGlobal</t>
+        </is>
+      </c>
+      <c r="C233" s="12" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/helicopters/ah-64-tests-proximity-fused-ammunition-against-drones/166339.article</t>
+        </is>
+      </c>
+      <c r="D233" s="11" t="inlineStr">
+        <is>
+          <t>flightglobal.com</t>
+        </is>
+      </c>
+      <c r="E233" s="11" t="inlineStr">
+        <is>
+          <t>Tue, 17 Feb 2026 04:49:28 GMT</t>
+        </is>
+      </c>
+      <c r="F233" s="11" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="G233" s="11" t="inlineStr">
+        <is>
+          <t>Skip to navigation   Trending now  Singapore Airshow  2026 World Air Forces directory  FlightGlobal has a new podcast - listen now  Site name  Site name  Search our site  Close menu [...] Follow us on social media   Connect with us on Facebook  Connect with us on Twitter  Connect with us on Linked in  Email us  Connect with us on Youtube  Site powered by Webvision Cloud [...] 2026-02-05T06:20:00Z By Dominic Perry    An early naval operator of the Airbus Helicopters H160 has praised the medium-tw...</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="8" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" s="8" t="inlineStr">
+        <is>
+          <t>Draper-Powered Missile Demonstrator Stages First Flight - Aviation Week</t>
+        </is>
+      </c>
+      <c r="C234" s="9" t="inlineStr">
+        <is>
+          <t>https://aviationweek.com/defense/missile-defense-weapons/draper-powered-missile-demonstrator-stages-first-flight</t>
+        </is>
+      </c>
+      <c r="D234" s="8" t="inlineStr">
+        <is>
+          <t>aviationweek.com</t>
+        </is>
+      </c>
+      <c r="E234" s="8" t="inlineStr">
+        <is>
+          <t>Thu, 12 Mar 2026 17:28:39 GMT</t>
+        </is>
+      </c>
+      <c r="F234" s="8" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="G234" s="8" t="inlineStr">
+        <is>
+          <t>X-Bow Completes Design Review Of Standard Missile Rocket Motors  Ursa Major Gathering More Hypersonic Missile Interest [...] Skip to main content  ## Share  # Draper-Powered Missile Demonstrator Stages First Flight  ## Share  Steve Trimble March 12, 2026  The Air Force Research Laboratory (AFRL) ground launched a liquid-fueled ballistic missile powered by the Ursa Major Draper rocket engine in January, Ursa Major announced on March 12. The Jan. 27 test integrated the Draper liquid rocket engine...</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="11" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" s="11" t="inlineStr">
+        <is>
+          <t>Embraer Exploring Aluminum Manufacturing in India - Aviation International News</t>
+        </is>
+      </c>
+      <c r="C235" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ainonline.com/aviation-news/aerospace/2026-02-20/embraer-exploring-aluminium-manufacturing-india</t>
+        </is>
+      </c>
+      <c r="D235" s="11" t="inlineStr">
+        <is>
+          <t>ainonline.com</t>
+        </is>
+      </c>
+      <c r="E235" s="11" t="inlineStr">
+        <is>
+          <t>Fri, 20 Feb 2026 18:58:10 GMT</t>
+        </is>
+      </c>
+      <c r="F235" s="11" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="G235" s="11" t="inlineStr">
+        <is>
+          <t>Email  By Charlotte Bailey • Writer  February 20, 2026  ## In this article  ## Embraer Defense  Company  ## More In Regulations and Government  ## Industry Leaders Press on Cert, Validation Improvements  ### White House threats over Gulfstream certificates highlight long-standing issue, leaders say  Regulations and Government  ## NBAA, NATA Urge Assistance for Radio Altimeter Mandates  ### FAA is proposing new radio altimeter standards in tandem with spectrum allocations  Regulations and Governm...</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="8" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" s="8" t="inlineStr">
+        <is>
+          <t>Inside the PLA’s push for collaborative combat aircraft - FlightGlobal</t>
+        </is>
+      </c>
+      <c r="C236" s="9" t="inlineStr">
+        <is>
+          <t>https://www.flightglobal.com/military-uavs/inside-the-plas-push-for-collaborative-combat-aircraft/166398.article</t>
+        </is>
+      </c>
+      <c r="D236" s="8" t="inlineStr">
+        <is>
+          <t>flightglobal.com</t>
+        </is>
+      </c>
+      <c r="E236" s="8" t="inlineStr">
+        <is>
+          <t>Tue, 24 Feb 2026 03:53:39 GMT</t>
+        </is>
+      </c>
+      <c r="F236" s="8" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="G236" s="8" t="inlineStr">
+        <is>
+          <t>Skip to navigation   Trending now  Singapore Airshow  2026 World Air Forces directory  FlightGlobal has a new podcast - listen now  Site name  Site name  Search our site  Close menu [...] ## Topics   Asia Pacific  Military UAVs  ### Related articles   News    ### USAF demonstrates interoperable autonomy architecture across competing CCAs    2026-02-13T04:19:00Z By Greg Waldron    The US Air Force has successfully demonstrated its Autonomy Government Reference Architecture on both the General Ato...</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="11" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" s="11" t="inlineStr">
+        <is>
+          <t>India's Jindal Stainless flags possible shipment delays to Middle East - Reuters</t>
+        </is>
+      </c>
+      <c r="C237" s="12" t="inlineStr">
+        <is>
+          <t>https://www.reuters.com/world/india/indias-jindal-stainless-flags-possible-shipment-delays-middle-east-2026-03-06/</t>
+        </is>
+      </c>
+      <c r="D237" s="11" t="inlineStr">
+        <is>
+          <t>reuters.com</t>
+        </is>
+      </c>
+      <c r="E237" s="11" t="inlineStr">
+        <is>
+          <t>Fri, 06 Mar 2026 07:30:01 GMT</t>
+        </is>
+      </c>
+      <c r="F237" s="11" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="G237" s="11" t="inlineStr">
+        <is>
+          <t>Our Standards: The Thomson Reuters Trust Principles., opens new tab  Purchase Licensing Rights  Neha Arora  Thomson Reuters  Neha reports on metals and mining in India. In her time at Reuters, she has reported on the pandemic when she was a finalist in the Breaking News of the Year category for Journalists of the Year Awards. She has also reported on India's trade policy, central bank's monetary policy, FX/debt markets, as well as done a brief stint with the desk and edited stories. She is a pos...</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="8" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" s="8" t="inlineStr">
+        <is>
+          <t>Rare earth corridors to boost country's self-reliance in magnets, says industry - The Economic Times</t>
+        </is>
+      </c>
+      <c r="C238" s="9" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/industry/indl-goods/svs/metals-mining/rare-earth-corridors-to-boost-countrys-self-reliance-in-magnets-says-industry/articleshow/127842807.cms</t>
+        </is>
+      </c>
+      <c r="D238" s="8" t="inlineStr">
+        <is>
+          <t>m.economictimes.com</t>
+        </is>
+      </c>
+      <c r="E238" s="8" t="inlineStr">
+        <is>
+          <t>Sun, 01 Feb 2026 13:53:13 GMT</t>
+        </is>
+      </c>
+      <c r="F238" s="8" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="G238" s="8" t="inlineStr">
+        <is>
+          <t>Nifty24,825.45-495.21  FEATURED FUNDS  ★★★★★  HSBC Large Cap Fund Direct-Growth  5Y Return  15.1 %  Invest NowFEATURED FUNDS  Motilal Oswal Midcap Fund Direct-Growth  5Y Return  27.16 %  Invest Now  Industry  English EditionEnglish Editionहिन्दीગુજરાતીमराठीবাংলাಕನ್ನಡമലയാളംதமிழ்తెలుగు   | Today's ePaper  My Watchlist Subscribe)  Sign In)  Business News›Industry›Ind'l Goods/Svs›Metals &amp; Mining›Rare earth corridors to boost country's self-reliance in magnets, says industry  ##### The Economic Times...</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="11" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" s="11" t="inlineStr">
+        <is>
+          <t>IACMI Workforce Development Program advances talent pipeline for manufacturing industry - CompositesWorld</t>
+        </is>
+      </c>
+      <c r="C239" s="12" t="inlineStr">
+        <is>
+          <t>https://www.compositesworld.com/news/iacmi-workforce-development-program-advances-talent-pipeline-for-manufacturing-industry--3</t>
+        </is>
+      </c>
+      <c r="D239" s="11" t="inlineStr">
+        <is>
+          <t>compositesworld.com</t>
+        </is>
+      </c>
+      <c r="E239" s="11" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 00:54:46 GMT</t>
+        </is>
+      </c>
+      <c r="F239" s="11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G239" s="11" t="inlineStr">
+        <is>
+          <t>Joby 2025 financial results show strong liquidity, supporting near-term eVTOL launch plans  Cutting/Kitting    Laser tech investment builds up Web Industries’ Denton production capacity  Sustainability    Composites sustainability wins: ISO 14001 certification, Platinum EcoVadis rating, emissions reports  Published  # IACMI Workforce Development Program advances talent pipeline for manufacturing industry  America’s Cutting Edge (ACE) eclipses 20,000 online students and 5,000 in-person participan...</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="8" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" s="8" t="inlineStr">
+        <is>
           <t>US Air Force awards CCA engine contracts to Honeywell, GE-Kratos - FlightGlobal</t>
         </is>
       </c>
-      <c r="C137" s="12" t="inlineStr">
+      <c r="C240" s="9" t="inlineStr">
         <is>
           <t>https://www.flightglobal.com/military-uavs/us-air-force-awards-cca-engine-contracts-to-honeywell-ge-kratos/166405.article</t>
         </is>
       </c>
-      <c r="D137" s="11" t="inlineStr">
+      <c r="D240" s="8" t="inlineStr">
         <is>
           <t>flightglobal.com</t>
         </is>
       </c>
-      <c r="E137" s="11" t="inlineStr">
+      <c r="E240" s="8" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 20:26:09 GMT</t>
         </is>
       </c>
-      <c r="F137" s="11" t="n">
+      <c r="F240" s="8" t="n">
         <v>0.0046</v>
       </c>
-      <c r="G137" s="11" t="inlineStr">
+      <c r="G240" s="8" t="inlineStr">
         <is>
           <t>Skip to navigation   Trending now  Singapore Airshow  2026 World Air Forces directory  FlightGlobal has a new podcast - listen now  Site name  Site name  Search our site  Close menu [...] FlightGlobal is the global aviation community’s primary source of news, data, insight, knowledge and expertise. We provide news, data, analytics and advisory services to connect the aviation community globally and help organisations shape their business strategies, identify new opportunities and make better dec...</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G137"/>
+  <autoFilter ref="A1:G240"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -5821,6 +8949,109 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C240" r:id="rId239"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5886,22 +9117,18 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Reuters</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>Thu, 12 Feb 2026 09:01:02 GMT</t>
-        </is>
-      </c>
+          <t>Moneycontrol</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="n"/>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>India backs $40 billion military upgrade with more Rafale fighters, Boeing P-8Is - Reuters</t>
+          <t>Three private firms shortlisted for AMCA fighter jet, HAL reportedly excluded</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/india/india-clears-proposal-buy-114-rafale-fighter-jets-dassault-reports-say-2026-02-12/</t>
+          <t>https://www.moneycontrol.com/world/three-private-firms-shortlisted-for-amca-fighter-jet-hal-reportedly-excluded-article-13811145.html</t>
         </is>
       </c>
     </row>
@@ -5916,22 +9143,22 @@
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>Airforce Technology</t>
+          <t>ETInfra</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>Wed, 18 Feb 2026 13:42:07 GMT</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>India’s Self-Reliance campaign hinges on aircraft propulsion - Airforce Technology</t>
+          <t>5th Generation Fighter Aircraft: L&amp;T Expects 5th-Gen Fighter Jet Project Award by 2027, ETInfra</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>https://www.airforce-technology.com/features/indias-self-reliance-campaign-hinges-on-aircraft-propulsion/</t>
+          <t>https://infra.economictimes.indiatimes.com/news/aviation/lt-expects-5th-gen-fighter-jet-project-award-by-2027/124954751</t>
         </is>
       </c>
     </row>
@@ -5946,22 +9173,18 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>FlightGlobal</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Thu, 05 Mar 2026 08:06:01 GMT</t>
-        </is>
-      </c>
+          <t>BharatShakti</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n"/>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>HAL delivers four Dhruv Mk IIIs to Indian coast guard - FlightGlobal</t>
+          <t>Private Heavyweights Battle for India’s Fifth-Gen Fighter; HAL Eliminated</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>https://www.flightglobal.com/fixed-wing/hal-delivers-four-dhruv-mk-iiis-to-indian-coast-guard/166532.article</t>
+          <t>https://bharatshakti.in/private-heavyweights-battle-for-indias-fifth-gen-fighter-hal-eliminated/</t>
         </is>
       </c>
     </row>
@@ -5976,22 +9199,22 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Defence.in</t>
+          <t>Aviation Week Network</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Sun, 29 Mar 2026 19:15:00 GMT</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>GTRE Concludes EOI Submissions for Development-cum-Production Partner of Indigenous 120kN High Thrust Aero Engine - Defence.in</t>
+          <t>Hindustan Aeronautics Reportedly Knocked Out Of AMCA Production Race - Aviation Week Network</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>https://defence.in/threads/gtre-concludes-eoi-submissions-for-development-cum-production-partner-of-indigenous-120kn-high-thrust-aero-engine.17317/</t>
+          <t>https://aviationweek.com/defense/aircraft-propulsion/hindustan-aeronautics-reportedly-knocked-out-amca-production-race</t>
         </is>
       </c>
     </row>
@@ -6006,22 +9229,22 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>EurAsian Times</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 07:03:48 GMT</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Missile &amp; Radar Success Fuels India’s Defense Self-Reliance &amp; Exports; Ex-IAF Air Marshal Shares Key Details - EurAsian Times</t>
+          <t>India backs $40 billion military upgrade with more Rafale fighters, Boeing P-8Is</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>https://eurasiantimes.com/missile-ex-iaf-air-marshal-shares-key-details/</t>
+          <t>https://www.reuters.com/world/india/india-clears-proposal-buy-114-rafale-fighter-jets-dassault-reports-say-2026-02-12/</t>
         </is>
       </c>
     </row>
